--- a/data/rateBuildUp/File1/RPT_RPT8255149037738UH_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT8255149037738UH_rateBuildUp.xlsx
@@ -2964,7 +2964,7 @@
         <v>24089.16055757216</v>
       </c>
       <c r="F11" s="368" t="n">
-        <v>22910.89281965233</v>
+        <v>22910.89281965234</v>
       </c>
       <c r="G11" s="370" t="n">
         <v>22576.04277835388</v>
@@ -2979,7 +2979,7 @@
         <v>177.8294739110173</v>
       </c>
       <c r="K11" s="372" t="n">
-        <v>176.3444366910915</v>
+        <v>176.3444366910916</v>
       </c>
       <c r="L11" s="373" t="n">
         <v>183.9927999942387</v>
@@ -2994,7 +2994,7 @@
         <v>103.2815800451463</v>
       </c>
       <c r="P11" s="372" t="n">
-        <v>93.68583900106414</v>
+        <v>93.68583900106417</v>
       </c>
       <c r="Q11" s="373" t="n">
         <v>89.87200575626352</v>
@@ -3014,7 +3014,7 @@
         <v>24089.16055757216</v>
       </c>
       <c r="W11" s="375" t="n">
-        <v>22910.89281965233</v>
+        <v>22910.89281965234</v>
       </c>
       <c r="X11" s="376" t="n">
         <v>22576.04277835388</v>
@@ -3029,7 +3029,7 @@
         <v>177.8294739110173</v>
       </c>
       <c r="AB11" s="372" t="n">
-        <v>176.3444366910915</v>
+        <v>176.3444366910916</v>
       </c>
       <c r="AC11" s="378" t="n">
         <v>183.9927999942387</v>
@@ -3044,7 +3044,7 @@
         <v>103.2815800451463</v>
       </c>
       <c r="AG11" s="372" t="n">
-        <v>93.68583900106414</v>
+        <v>93.68583900106417</v>
       </c>
       <c r="AH11" s="378" t="n">
         <v>89.87200575626352</v>
@@ -3064,7 +3064,7 @@
         <v>24089.16055757216</v>
       </c>
       <c r="AN11" s="368" t="n">
-        <v>22910.89281965233</v>
+        <v>22910.89281965234</v>
       </c>
       <c r="AO11" s="380" t="n">
         <v>22576.04277835388</v>
@@ -3079,7 +3079,7 @@
         <v>177.8294739110173</v>
       </c>
       <c r="AS11" s="372" t="n">
-        <v>176.3444366910915</v>
+        <v>176.3444366910916</v>
       </c>
       <c r="AT11" s="382" t="n">
         <v>183.9927999942387</v>
@@ -3094,7 +3094,7 @@
         <v>103.2815799610111</v>
       </c>
       <c r="AX11" s="372" t="n">
-        <v>93.68583890529054</v>
+        <v>93.68583890529057</v>
       </c>
       <c r="AY11" s="382" t="n">
         <v>89.87200586001613</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="BB11" s="383" t="n">
-        <v>26351.48216982735</v>
+        <v>26351.48216982734</v>
       </c>
       <c r="BC11" s="384" t="n">
         <v>25038.33755863324</v>
@@ -3114,7 +3114,7 @@
         <v>26645.81401887292</v>
       </c>
       <c r="BE11" s="384" t="n">
-        <v>26010.40830801734</v>
+        <v>26010.40830801733</v>
       </c>
       <c r="BF11" s="385" t="n">
         <v>26274.64259933642</v>
@@ -3155,79 +3155,79 @@
         </is>
       </c>
       <c r="BS11" s="391" t="n">
-        <v>26203.10727572991</v>
+        <v>26203.10727572989</v>
       </c>
       <c r="BT11" s="375" t="n">
-        <v>24936.17960454477</v>
+        <v>24936.17960454476</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>26611.64391549987</v>
+        <v>26611.64391549986</v>
       </c>
       <c r="BV11" s="375" t="n">
-        <v>26028.90500448929</v>
+        <v>26028.90500448928</v>
       </c>
       <c r="BW11" s="392" t="n">
-        <v>26365.14279158321</v>
+        <v>26365.1427915832</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>171.8792907918565</v>
+        <v>171.8792907918564</v>
       </c>
       <c r="BY11" s="372" t="n">
-        <v>179.2220110803922</v>
+        <v>179.2220110803921</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>195.907882372609</v>
+        <v>195.9078823726088</v>
       </c>
       <c r="CA11" s="372" t="n">
-        <v>199.3146296083649</v>
+        <v>199.3146296083648</v>
       </c>
       <c r="CB11" s="387" t="n">
-        <v>213.1926627868785</v>
+        <v>213.1926627868784</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>156.0446733835886</v>
+        <v>156.0446733835885</v>
       </c>
       <c r="CD11" s="389" t="n">
         <v>129.1940920210261</v>
       </c>
       <c r="CE11" s="389" t="n">
-        <v>114.3700549589269</v>
+        <v>114.3700549589268</v>
       </c>
       <c r="CF11" s="389" t="n">
-        <v>106.6766058230473</v>
+        <v>106.6766058230472</v>
       </c>
       <c r="CG11" s="390" t="n">
-        <v>105.1818718247416</v>
+        <v>105.1818718247415</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>0.6389788461903265</v>
+        <v>0.6389788461904402</v>
       </c>
       <c r="CX11" s="92" t="n">
-        <v>0.7625478833641637</v>
+        <v>0.7625478833642489</v>
       </c>
       <c r="CY11" s="92" t="n">
-        <v>0.7951566387490345</v>
+        <v>0.7951566387491198</v>
       </c>
       <c r="CZ11" s="92" t="n">
-        <v>0.8866823740377185</v>
+        <v>0.8866823740377754</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>0.9434065040171333</v>
+        <v>0.9434065040172186</v>
       </c>
       <c r="DC11" s="393" t="n">
-        <v>0.007228790260420209</v>
+        <v>0.007228790260420208</v>
       </c>
       <c r="DD11" s="394" t="n">
         <v>0.007628852866560994</v>
       </c>
       <c r="DE11" s="394" t="n">
-        <v>0.007522316429608733</v>
+        <v>0.007522316429608734</v>
       </c>
       <c r="DF11" s="394" t="n">
-        <v>0.00802817675775575</v>
+        <v>0.008028176757755748</v>
       </c>
       <c r="DG11" s="395" t="n">
-        <v>0.008141014872206942</v>
+        <v>0.008141014872206944</v>
       </c>
     </row>
     <row r="12">
@@ -3258,7 +3258,7 @@
         <v>249.4324666295045</v>
       </c>
       <c r="J12" s="372" t="n">
-        <v>272.6218550480629</v>
+        <v>272.621855048063</v>
       </c>
       <c r="K12" s="372" t="n">
         <v>296.365412761076</v>
@@ -3308,7 +3308,7 @@
         <v>249.4324666295045</v>
       </c>
       <c r="AA12" s="372" t="n">
-        <v>272.6218550480629</v>
+        <v>272.621855048063</v>
       </c>
       <c r="AB12" s="372" t="n">
         <v>296.365412761076</v>
@@ -3352,13 +3352,13 @@
         <v>28299.44189527074</v>
       </c>
       <c r="AP12" s="381" t="n">
-        <v>263.6635448393756</v>
+        <v>263.6635448393755</v>
       </c>
       <c r="AQ12" s="372" t="n">
         <v>259.1003445414195</v>
       </c>
       <c r="AR12" s="372" t="n">
-        <v>282.9757054048227</v>
+        <v>282.9757054048228</v>
       </c>
       <c r="AS12" s="372" t="n">
         <v>307.2723310876067</v>
@@ -3399,7 +3399,7 @@
         <v>29559.11465242037</v>
       </c>
       <c r="BF12" s="385" t="n">
-        <v>32791.7293542301</v>
+        <v>32791.72935423009</v>
       </c>
       <c r="BG12" s="386" t="n">
         <v>272.9940526165358</v>
@@ -3414,7 +3414,7 @@
         <v>347.1819952275418</v>
       </c>
       <c r="BK12" s="387" t="n">
-        <v>373.0006386429474</v>
+        <v>373.0006386429473</v>
       </c>
       <c r="BL12" s="386" t="n">
         <v>204.9152122953518</v>
@@ -3446,10 +3446,10 @@
         <v>25611.23615751466</v>
       </c>
       <c r="BV12" s="375" t="n">
-        <v>29739.34091087101</v>
+        <v>29739.340910871</v>
       </c>
       <c r="BW12" s="392" t="n">
-        <v>33081.47916846324</v>
+        <v>33081.47916846322</v>
       </c>
       <c r="BX12" s="386" t="n">
         <v>272.3350931926751</v>
@@ -3461,10 +3461,10 @@
         <v>310.485521541103</v>
       </c>
       <c r="CA12" s="372" t="n">
-        <v>346.3989019796252</v>
+        <v>346.3989019796251</v>
       </c>
       <c r="CB12" s="387" t="n">
-        <v>372.3484651943248</v>
+        <v>372.3484651943247</v>
       </c>
       <c r="CC12" s="386" t="n">
         <v>204.9039204600244</v>
@@ -3479,10 +3479,10 @@
         <v>186.4227432420769</v>
       </c>
       <c r="CG12" s="387" t="n">
-        <v>197.2957607538008</v>
+        <v>197.2957607538007</v>
       </c>
       <c r="CW12" s="102" t="n">
-        <v>0.6589594238606651</v>
+        <v>0.6589594238607219</v>
       </c>
       <c r="CX12" s="103" t="n">
         <v>0.7030155109170551</v>
@@ -3491,13 +3491,13 @@
         <v>0.7452609770264189</v>
       </c>
       <c r="CZ12" s="103" t="n">
-        <v>0.7830932479166108</v>
+        <v>0.7830932479166677</v>
       </c>
       <c r="DA12" s="104" t="n">
-        <v>0.652173448622591</v>
+        <v>0.6521734486226478</v>
       </c>
       <c r="DC12" s="396" t="n">
-        <v>0.002321834056615352</v>
+        <v>0.002321834056615353</v>
       </c>
       <c r="DD12" s="397" t="n">
         <v>0.002251743842844422</v>
@@ -3525,7 +3525,7 @@
         <v>47358.56763505708</v>
       </c>
       <c r="E13" s="368" t="n">
-        <v>56366.24695023874</v>
+        <v>56366.24695023875</v>
       </c>
       <c r="F13" s="368" t="n">
         <v>68048.72228447578</v>
@@ -3540,7 +3540,7 @@
         <v>585.4161049931173</v>
       </c>
       <c r="J13" s="372" t="n">
-        <v>675.1286623780475</v>
+        <v>675.1286623780476</v>
       </c>
       <c r="K13" s="372" t="n">
         <v>831.9673747798748</v>
@@ -3555,7 +3555,7 @@
         <v>432.4847715283256</v>
       </c>
       <c r="O13" s="372" t="n">
-        <v>441.0227177832656</v>
+        <v>441.0227177832658</v>
       </c>
       <c r="P13" s="372" t="n">
         <v>490.0594368241809</v>
@@ -3575,7 +3575,7 @@
         <v>47358.56763505708</v>
       </c>
       <c r="V13" s="375" t="n">
-        <v>56366.24695023874</v>
+        <v>56366.24695023875</v>
       </c>
       <c r="W13" s="375" t="n">
         <v>68048.72228447578</v>
@@ -3590,7 +3590,7 @@
         <v>585.4161049931173</v>
       </c>
       <c r="AA13" s="372" t="n">
-        <v>675.1286623780475</v>
+        <v>675.1286623780476</v>
       </c>
       <c r="AB13" s="372" t="n">
         <v>831.9673747798748</v>
@@ -3605,7 +3605,7 @@
         <v>432.4847715283256</v>
       </c>
       <c r="AF13" s="372" t="n">
-        <v>441.0227177832656</v>
+        <v>441.0227177832658</v>
       </c>
       <c r="AG13" s="372" t="n">
         <v>490.0594368241809</v>
@@ -3678,7 +3678,7 @@
         <v>62177.5150336288</v>
       </c>
       <c r="BE13" s="384" t="n">
-        <v>77060.78327347638</v>
+        <v>77060.78327347637</v>
       </c>
       <c r="BF13" s="385" t="n">
         <v>88527.1920241601</v>
@@ -3693,7 +3693,7 @@
         <v>760.3987186589601</v>
       </c>
       <c r="BJ13" s="372" t="n">
-        <v>962.6600777565144</v>
+        <v>962.6600777565143</v>
       </c>
       <c r="BK13" s="387" t="n">
         <v>1055.539724299018</v>
@@ -3708,7 +3708,7 @@
         <v>493.1278604947498</v>
       </c>
       <c r="BO13" s="372" t="n">
-        <v>562.0140619373699</v>
+        <v>562.0140619373698</v>
       </c>
       <c r="BP13" s="387" t="n">
         <v>581.7162805798679</v>
@@ -3734,13 +3734,13 @@
         <v>89449.625100333</v>
       </c>
       <c r="BX13" s="386" t="n">
-        <v>579.1549261281195</v>
+        <v>579.1549261281197</v>
       </c>
       <c r="BY13" s="372" t="n">
         <v>640.6766384545072</v>
       </c>
       <c r="BZ13" s="372" t="n">
-        <v>760.6964866649363</v>
+        <v>760.6964866649364</v>
       </c>
       <c r="CA13" s="372" t="n">
         <v>963.0963467162363</v>
@@ -3755,7 +3755,7 @@
         <v>472.4728953745258</v>
       </c>
       <c r="CE13" s="372" t="n">
-        <v>496.2057158731739</v>
+        <v>496.205715873174</v>
       </c>
       <c r="CF13" s="372" t="n">
         <v>566.8663642518962</v>
@@ -3764,16 +3764,16 @@
         <v>588.0672647234339</v>
       </c>
       <c r="CW13" s="102" t="n">
-        <v>-0.2265588582235978</v>
+        <v>-0.2265588582237115</v>
       </c>
       <c r="CX13" s="103" t="n">
         <v>-0.2407356127160938</v>
       </c>
       <c r="CY13" s="103" t="n">
-        <v>-0.2977680059761951</v>
+        <v>-0.2977680059763088</v>
       </c>
       <c r="CZ13" s="103" t="n">
-        <v>-0.4362689597219287</v>
+        <v>-0.4362689597220424</v>
       </c>
       <c r="DA13" s="104" t="n">
         <v>-0.4455219254839449</v>
@@ -3957,13 +3957,13 @@
         <v>775.8290446272288</v>
       </c>
       <c r="BD14" s="414" t="n">
-        <v>874.6233093179618</v>
+        <v>874.6233093179616</v>
       </c>
       <c r="BE14" s="414" t="n">
         <v>963.3638429855617</v>
       </c>
       <c r="BF14" s="415" t="n">
-        <v>1058.528398713628</v>
+        <v>1058.528398713627</v>
       </c>
       <c r="BG14" s="416" t="n">
         <v>230.2309670268395</v>
@@ -3972,13 +3972,13 @@
         <v>348.3518539128752</v>
       </c>
       <c r="BI14" s="417" t="n">
-        <v>381.128709355472</v>
+        <v>381.1287093554719</v>
       </c>
       <c r="BJ14" s="417" t="n">
         <v>411.4542866636065</v>
       </c>
       <c r="BK14" s="418" t="n">
-        <v>443.112866511122</v>
+        <v>443.1128665111219</v>
       </c>
       <c r="BL14" s="417" t="n">
         <v>230.2309670268395</v>
@@ -3987,13 +3987,13 @@
         <v>348.3518539128752</v>
       </c>
       <c r="BN14" s="417" t="n">
-        <v>381.128709355472</v>
+        <v>381.1287093554719</v>
       </c>
       <c r="BO14" s="417" t="n">
         <v>411.4542866636065</v>
       </c>
       <c r="BP14" s="418" t="n">
-        <v>443.112866511122</v>
+        <v>443.1128665111219</v>
       </c>
       <c r="BR14" s="111" t="inlineStr">
         <is>
@@ -4001,64 +4001,64 @@
         </is>
       </c>
       <c r="BS14" s="419" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702484</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687163</v>
       </c>
       <c r="BU14" s="420" t="n">
-        <v>869.2810738962293</v>
+        <v>869.2810738962287</v>
       </c>
       <c r="BV14" s="420" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063706</v>
       </c>
       <c r="BW14" s="421" t="n">
         <v>1052.062863383992</v>
       </c>
       <c r="BX14" s="416" t="n">
-        <v>229.300384964129</v>
+        <v>229.3003849641289</v>
       </c>
       <c r="BY14" s="417" t="n">
-        <v>347.2212936759051</v>
+        <v>347.221293675905</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>379.8917737149281</v>
+        <v>379.8917737149279</v>
       </c>
       <c r="CA14" s="417" t="n">
-        <v>410.1189307766605</v>
+        <v>410.1189307766604</v>
       </c>
       <c r="CB14" s="418" t="n">
-        <v>441.6747640809032</v>
+        <v>441.674764080903</v>
       </c>
       <c r="CC14" s="417" t="n">
-        <v>229.300384964129</v>
+        <v>229.3003849641289</v>
       </c>
       <c r="CD14" s="417" t="n">
-        <v>347.2212936759051</v>
+        <v>347.221293675905</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>379.8917737149281</v>
+        <v>379.8917737149279</v>
       </c>
       <c r="CF14" s="417" t="n">
-        <v>410.1189307766605</v>
+        <v>410.1189307766604</v>
       </c>
       <c r="CG14" s="418" t="n">
-        <v>441.6747640809032</v>
+        <v>441.674764080903</v>
       </c>
       <c r="CW14" s="132" t="n">
-        <v>0.9305820627104993</v>
+        <v>0.9305820627105845</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>1.130560236970041</v>
+        <v>1.130560236970155</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>1.236935640543891</v>
+        <v>1.236935640544061</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>1.33535588694599</v>
+        <v>1.335355886946161</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>1.438102430218805</v>
+        <v>1.438102430218862</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0</v>
@@ -4104,7 +4104,7 @@
         <v>301.8521807615508</v>
       </c>
       <c r="J15" s="427" t="n">
-        <v>340.8945737987178</v>
+        <v>340.8945737987179</v>
       </c>
       <c r="K15" s="427" t="n">
         <v>390.143021375743</v>
@@ -4154,7 +4154,7 @@
         <v>301.8521807615508</v>
       </c>
       <c r="AA15" s="433" t="n">
-        <v>340.8945737987178</v>
+        <v>340.8945737987179</v>
       </c>
       <c r="AB15" s="433" t="n">
         <v>390.143021375743</v>
@@ -4204,13 +4204,13 @@
         <v>307.9414533823692</v>
       </c>
       <c r="AR15" s="437" t="n">
-        <v>347.3855163222884</v>
+        <v>347.3855163222883</v>
       </c>
       <c r="AS15" s="437" t="n">
         <v>397.3595148844121</v>
       </c>
       <c r="AT15" s="438" t="n">
-        <v>431.9621397489194</v>
+        <v>431.9621397489193</v>
       </c>
       <c r="AU15" s="437" t="n">
         <v>242.479117894165</v>
@@ -4222,7 +4222,7 @@
         <v>204.7924191771266</v>
       </c>
       <c r="AX15" s="437" t="n">
-        <v>217.42376895703</v>
+        <v>217.4237689570301</v>
       </c>
       <c r="AY15" s="438" t="n">
         <v>223.5961438609551</v>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="BB15" s="439" t="n">
-        <v>93541.84997326985</v>
+        <v>93541.84997326987</v>
       </c>
       <c r="BC15" s="440" t="n">
         <v>98563.57285404706</v>
@@ -4257,7 +4257,7 @@
         <v>382.1251908413706</v>
       </c>
       <c r="BJ15" s="443" t="n">
-        <v>449.1259370805317</v>
+        <v>449.1259370805316</v>
       </c>
       <c r="BK15" s="444" t="n">
         <v>500.7279160191844</v>
@@ -4266,13 +4266,13 @@
         <v>250.6513127969453</v>
       </c>
       <c r="BM15" s="443" t="n">
-        <v>227.7228502878217</v>
+        <v>227.7228502878216</v>
       </c>
       <c r="BN15" s="443" t="n">
         <v>225.2723230646231</v>
       </c>
       <c r="BO15" s="443" t="n">
-        <v>245.7488755612477</v>
+        <v>245.7488755612476</v>
       </c>
       <c r="BP15" s="444" t="n">
         <v>259.1913060031134</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="BS15" s="439" t="n">
-        <v>93448.66435652964</v>
+        <v>93448.66435652961</v>
       </c>
       <c r="BT15" s="440" t="n">
-        <v>98663.05884628771</v>
+        <v>98663.05884628769</v>
       </c>
       <c r="BU15" s="440" t="n">
         <v>115620.373091089</v>
@@ -4301,22 +4301,22 @@
         <v>297.9288864996687</v>
       </c>
       <c r="BY15" s="443" t="n">
-        <v>328.0617592449053</v>
+        <v>328.0617592449051</v>
       </c>
       <c r="BZ15" s="443" t="n">
-        <v>381.8221680697479</v>
+        <v>381.8221680697478</v>
       </c>
       <c r="CA15" s="443" t="n">
-        <v>448.8688390305693</v>
+        <v>448.8688390305692</v>
       </c>
       <c r="CB15" s="444" t="n">
-        <v>500.4902004560173</v>
+        <v>500.4902004560172</v>
       </c>
       <c r="CC15" s="443" t="n">
-        <v>250.9487587914139</v>
+        <v>250.9487587914138</v>
       </c>
       <c r="CD15" s="443" t="n">
-        <v>228.3335186840541</v>
+        <v>228.333518684054</v>
       </c>
       <c r="CE15" s="443" t="n">
         <v>226.3945671991866</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="BB29" s="391" t="n">
-        <v>9.458718246319526</v>
+        <v>9.458718246319528</v>
       </c>
       <c r="BC29" s="375" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="BG29" s="386" t="n">
-        <v>0.06192447522808759</v>
+        <v>0.0619244752280876</v>
       </c>
       <c r="BH29" s="372" t="n">
         <v>0</v>
@@ -7316,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="BL29" s="388" t="n">
-        <v>0.05611715631405426</v>
+        <v>0.05611715631405428</v>
       </c>
       <c r="BM29" s="389" t="n">
         <v>0</v>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>9.473945063523477</v>
+        <v>9.473945063523473</v>
       </c>
       <c r="BT29" s="375" t="n">
         <v>0</v>
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="BX29" s="386" t="n">
-        <v>0.06214434575962195</v>
+        <v>0.06214434575962192</v>
       </c>
       <c r="BY29" s="372" t="n">
         <v>0</v>
@@ -7366,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="CC29" s="388" t="n">
-        <v>0.05641921194822883</v>
+        <v>0.05641921194822881</v>
       </c>
       <c r="CD29" s="389" t="n">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>-0.000219870531534362</v>
+        <v>-0.000219870531534321</v>
       </c>
       <c r="CX29" s="92" t="n">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="BG30" s="386" t="n">
-        <v>0.6709062403268327</v>
+        <v>0.6709062403268325</v>
       </c>
       <c r="BH30" s="372" t="n">
         <v>0</v>
@@ -7598,7 +7598,7 @@
         <v>0</v>
       </c>
       <c r="BL30" s="386" t="n">
-        <v>0.503596665748468</v>
+        <v>0.5035966657484678</v>
       </c>
       <c r="BM30" s="372" t="n">
         <v>0</v>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="BS30" s="391" t="n">
-        <v>54.81635367607643</v>
+        <v>54.81635367607642</v>
       </c>
       <c r="BT30" s="375" t="n">
         <v>0</v>
@@ -7633,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="BX30" s="386" t="n">
-        <v>0.6708443804947056</v>
+        <v>0.6708443804947054</v>
       </c>
       <c r="BY30" s="372" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="CC30" s="386" t="n">
-        <v>0.5047408395681511</v>
+        <v>0.504740839568151</v>
       </c>
       <c r="CD30" s="372" t="n">
         <v>0</v>
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="CW30" s="102" t="n">
-        <v>6.1859832127031e-05</v>
+        <v>6.1859832127142e-05</v>
       </c>
       <c r="CX30" s="103" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="BS33" s="439" t="n">
-        <v>64.2902987395999</v>
+        <v>64.29029873959989</v>
       </c>
       <c r="BT33" s="440" t="n">
         <v>0</v>
@@ -8494,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="CC33" s="443" t="n">
-        <v>0.1726463484751185</v>
+        <v>0.1726463484751184</v>
       </c>
       <c r="CD33" s="443" t="n">
         <v>0</v>
@@ -9229,7 +9229,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="D38" s="368" t="n">
-        <v>76.38905038910423</v>
+        <v>76.38905038910424</v>
       </c>
       <c r="E38" s="368" t="n">
         <v>36.27632243820575</v>
@@ -9244,7 +9244,7 @@
         <v>0.8738456594154241</v>
       </c>
       <c r="I38" s="372" t="n">
-        <v>0.5491119173446269</v>
+        <v>0.5491119173446271</v>
       </c>
       <c r="J38" s="372" t="n">
         <v>0.2677967677285775</v>
@@ -9259,7 +9259,7 @@
         <v>0.7918958260080886</v>
       </c>
       <c r="N38" s="372" t="n">
-        <v>0.3946283302395904</v>
+        <v>0.3946283302395905</v>
       </c>
       <c r="O38" s="372" t="n">
         <v>0.1555336845669933</v>
@@ -9279,7 +9279,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="U38" s="375" t="n">
-        <v>76.38905038910423</v>
+        <v>76.38905038910424</v>
       </c>
       <c r="V38" s="375" t="n">
         <v>36.27632243820575</v>
@@ -9294,7 +9294,7 @@
         <v>0.8738456594154241</v>
       </c>
       <c r="Z38" s="372" t="n">
-        <v>0.5491119173446269</v>
+        <v>0.5491119173446271</v>
       </c>
       <c r="AA38" s="372" t="n">
         <v>0.2677967677285775</v>
@@ -9309,7 +9309,7 @@
         <v>0.7918958260080886</v>
       </c>
       <c r="AE38" s="372" t="n">
-        <v>0.3946283302395904</v>
+        <v>0.3946283302395905</v>
       </c>
       <c r="AF38" s="372" t="n">
         <v>0.1555336845669933</v>
@@ -9329,7 +9329,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="AL38" s="368" t="n">
-        <v>76.38905038910423</v>
+        <v>76.38905038910424</v>
       </c>
       <c r="AM38" s="368" t="n">
         <v>36.27632243820575</v>
@@ -9344,7 +9344,7 @@
         <v>0.8738456594154241</v>
       </c>
       <c r="AQ38" s="372" t="n">
-        <v>0.5491119173446269</v>
+        <v>0.5491119173446271</v>
       </c>
       <c r="AR38" s="372" t="n">
         <v>0.2677967677285775</v>
@@ -9359,7 +9359,7 @@
         <v>0.7918958260550706</v>
       </c>
       <c r="AV38" s="372" t="n">
-        <v>0.3946283311773753</v>
+        <v>0.3946283311773754</v>
       </c>
       <c r="AW38" s="372" t="n">
         <v>0.1555336844402925</v>
@@ -9379,10 +9379,10 @@
         <v>128.8288566696583</v>
       </c>
       <c r="BC38" s="375" t="n">
-        <v>70.62874672220298</v>
+        <v>70.62874672220296</v>
       </c>
       <c r="BD38" s="375" t="n">
-        <v>32.45283468400487</v>
+        <v>32.45283468400488</v>
       </c>
       <c r="BE38" s="375" t="n">
         <v>14.61425526447143</v>
@@ -9391,22 +9391,22 @@
         <v>16.02712779187732</v>
       </c>
       <c r="BG38" s="386" t="n">
-        <v>0.8434186467714356</v>
+        <v>0.8434186467714357</v>
       </c>
       <c r="BH38" s="372" t="n">
-        <v>0.5077047866772376</v>
+        <v>0.5077047866772375</v>
       </c>
       <c r="BI38" s="372" t="n">
-        <v>0.2395712588234516</v>
+        <v>0.2395712588234517</v>
       </c>
       <c r="BJ38" s="372" t="n">
-        <v>0.1124854728516922</v>
+        <v>0.1124854728516923</v>
       </c>
       <c r="BK38" s="387" t="n">
         <v>0.1306197081235334</v>
       </c>
       <c r="BL38" s="388" t="n">
-        <v>0.7643222791106157</v>
+        <v>0.7643222791106158</v>
       </c>
       <c r="BM38" s="389" t="n">
         <v>0.3648704141517646</v>
@@ -9415,7 +9415,7 @@
         <v>0.1391405911537224</v>
       </c>
       <c r="BO38" s="389" t="n">
-        <v>0.05975972980213352</v>
+        <v>0.05975972980213354</v>
       </c>
       <c r="BP38" s="390" t="n">
         <v>0.06380170949232454</v>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>128.5810065561253</v>
+        <v>128.5810065561252</v>
       </c>
       <c r="BT38" s="375" t="n">
-        <v>70.62983584535287</v>
+        <v>70.62983584535283</v>
       </c>
       <c r="BU38" s="375" t="n">
         <v>32.4179268437376</v>
@@ -9438,13 +9438,13 @@
         <v>14.49709395855619</v>
       </c>
       <c r="BW38" s="392" t="n">
-        <v>15.94387757167488</v>
+        <v>15.94387757167487</v>
       </c>
       <c r="BX38" s="386" t="n">
-        <v>0.8434271547878566</v>
+        <v>0.8434271547878563</v>
       </c>
       <c r="BY38" s="372" t="n">
-        <v>0.5076327417923732</v>
+        <v>0.5076327417923728</v>
       </c>
       <c r="BZ38" s="372" t="n">
         <v>0.2386522012331493</v>
@@ -9453,43 +9453,43 @@
         <v>0.1110105443255847</v>
       </c>
       <c r="CB38" s="387" t="n">
-        <v>0.1289246844412498</v>
+        <v>0.1289246844412497</v>
       </c>
       <c r="CC38" s="388" t="n">
-        <v>0.7657252615214782</v>
+        <v>0.7657252615214781</v>
       </c>
       <c r="CD38" s="389" t="n">
-        <v>0.3659324586341772</v>
+        <v>0.3659324586341769</v>
       </c>
       <c r="CE38" s="389" t="n">
         <v>0.1393239773741763</v>
       </c>
       <c r="CF38" s="389" t="n">
-        <v>0.05941474593456195</v>
+        <v>0.05941474593456193</v>
       </c>
       <c r="CG38" s="390" t="n">
-        <v>0.06360697153776257</v>
+        <v>0.06360697153776254</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>-8.508016420938e-06</v>
+        <v>-8.508016420605e-06</v>
       </c>
       <c r="CX38" s="92" t="n">
-        <v>7.204488486445299e-05</v>
+        <v>7.2044884864675e-05</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>0.000919057590302336</v>
+        <v>0.000919057590302447</v>
       </c>
       <c r="CZ38" s="92" t="n">
-        <v>0.001474928526107533</v>
+        <v>0.001474928526107588</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>0.001695023682283581</v>
+        <v>0.001695023682283636</v>
       </c>
       <c r="DC38" s="393" t="n">
-        <v>0.003528009884850774</v>
+        <v>0.003528009884850775</v>
       </c>
       <c r="DD38" s="394" t="n">
-        <v>0.003547964645490739</v>
+        <v>0.003547964645490738</v>
       </c>
       <c r="DE38" s="394" t="n">
         <v>0.00731687483938503</v>
@@ -9667,13 +9667,13 @@
         <v>76.79979343970206</v>
       </c>
       <c r="BE39" s="375" t="n">
-        <v>84.04164482688765</v>
+        <v>84.04164482688762</v>
       </c>
       <c r="BF39" s="392" t="n">
-        <v>91.85091082748836</v>
+        <v>91.85091082748843</v>
       </c>
       <c r="BG39" s="386" t="n">
-        <v>1.546065453660562</v>
+        <v>1.546065453660561</v>
       </c>
       <c r="BH39" s="372" t="n">
         <v>0.858092921155409</v>
@@ -9682,7 +9682,7 @@
         <v>0.9369093940266261</v>
       </c>
       <c r="BJ39" s="372" t="n">
-        <v>0.9870981007482283</v>
+        <v>0.987098100748228</v>
       </c>
       <c r="BK39" s="387" t="n">
         <v>1.044789313442233</v>
@@ -9697,10 +9697,10 @@
         <v>0.5126657531328352</v>
       </c>
       <c r="BO39" s="372" t="n">
-        <v>0.5265382695363802</v>
+        <v>0.5265382695363799</v>
       </c>
       <c r="BP39" s="387" t="n">
-        <v>0.5475500037704472</v>
+        <v>0.5475500037704476</v>
       </c>
       <c r="BR39" s="101" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="BS39" s="391" t="n">
-        <v>124.7760115321655</v>
+        <v>124.7760115321654</v>
       </c>
       <c r="BT39" s="375" t="n">
         <v>66.95943787995972</v>
@@ -9717,13 +9717,13 @@
         <v>75.4349224130135</v>
       </c>
       <c r="BV39" s="375" t="n">
-        <v>82.71716419582474</v>
+        <v>82.71716419582471</v>
       </c>
       <c r="BW39" s="392" t="n">
-        <v>90.58922323081399</v>
+        <v>90.58922323081407</v>
       </c>
       <c r="BX39" s="386" t="n">
-        <v>1.527013027016195</v>
+        <v>1.527013027016194</v>
       </c>
       <c r="BY39" s="372" t="n">
         <v>0.8375728786571767</v>
@@ -9732,10 +9732,10 @@
         <v>0.9144990536095222</v>
       </c>
       <c r="CA39" s="372" t="n">
-        <v>0.9634757857672663</v>
+        <v>0.963475785767266</v>
       </c>
       <c r="CB39" s="387" t="n">
-        <v>1.019626663649774</v>
+        <v>1.019626663649775</v>
       </c>
       <c r="CC39" s="386" t="n">
         <v>1.14891897390462</v>
@@ -9747,13 +9747,13 @@
         <v>0.5038337079856268</v>
       </c>
       <c r="CF39" s="372" t="n">
-        <v>0.5185172297128532</v>
+        <v>0.518517229712853</v>
       </c>
       <c r="CG39" s="387" t="n">
-        <v>0.5402681549517182</v>
+        <v>0.5402681549517186</v>
       </c>
       <c r="CW39" s="102" t="n">
-        <v>0.01905242664436702</v>
+        <v>0.01905242664436724</v>
       </c>
       <c r="CX39" s="103" t="n">
         <v>0.02052004249823236</v>
@@ -9967,7 +9967,7 @@
         <v>2.400774093376043</v>
       </c>
       <c r="BK40" s="387" t="n">
-        <v>4.113416937050488</v>
+        <v>4.113416937050489</v>
       </c>
       <c r="BL40" s="386" t="n">
         <v>0.5603194807761372</v>
@@ -9976,7 +9976,7 @@
         <v>0.7101505215997634</v>
       </c>
       <c r="BN40" s="372" t="n">
-        <v>0.8864721134473437</v>
+        <v>0.8864721134473434</v>
       </c>
       <c r="BO40" s="372" t="n">
         <v>1.401604607055853</v>
@@ -10002,10 +10002,10 @@
         <v>192.7906562953858</v>
       </c>
       <c r="BW40" s="392" t="n">
-        <v>347.5611327190495</v>
+        <v>347.5611327190496</v>
       </c>
       <c r="BX40" s="386" t="n">
-        <v>0.6733796218804904</v>
+        <v>0.6733796218804905</v>
       </c>
       <c r="BY40" s="372" t="n">
         <v>0.9571440170984303</v>
@@ -10014,34 +10014,34 @@
         <v>1.356887111150443</v>
       </c>
       <c r="CA40" s="372" t="n">
-        <v>2.390163817245792</v>
+        <v>2.390163817245793</v>
       </c>
       <c r="CB40" s="387" t="n">
-        <v>4.103085148771918</v>
+        <v>4.103085148771919</v>
       </c>
       <c r="CC40" s="386" t="n">
-        <v>0.5547423026400455</v>
+        <v>0.5547423026400454</v>
       </c>
       <c r="CD40" s="372" t="n">
         <v>0.7058546822306387</v>
       </c>
       <c r="CE40" s="372" t="n">
-        <v>0.8851035230875922</v>
+        <v>0.885103523087592</v>
       </c>
       <c r="CF40" s="372" t="n">
         <v>1.406820280928509</v>
       </c>
       <c r="CG40" s="387" t="n">
-        <v>2.284965693405784</v>
+        <v>2.284965693405785</v>
       </c>
       <c r="CW40" s="102" t="n">
-        <v>0.008305537072977653</v>
+        <v>0.008305537072977542</v>
       </c>
       <c r="CX40" s="103" t="n">
         <v>0.009515698498608227</v>
       </c>
       <c r="CY40" s="103" t="n">
-        <v>0.01004490221414556</v>
+        <v>0.01004490221414533</v>
       </c>
       <c r="CZ40" s="103" t="n">
         <v>0.01061027613025045</v>
@@ -10272,64 +10272,64 @@
         </is>
       </c>
       <c r="BS41" s="419" t="n">
-        <v>67.54914673800951</v>
+        <v>67.54914673800948</v>
       </c>
       <c r="BT41" s="420" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121332</v>
       </c>
       <c r="BU41" s="420" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="BV41" s="420" t="n">
-        <v>82.54761814889748</v>
+        <v>82.54761814889746</v>
       </c>
       <c r="BW41" s="421" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
       <c r="BX41" s="416" t="n">
-        <v>22.52427460963667</v>
+        <v>22.52427460963666</v>
       </c>
       <c r="BY41" s="417" t="n">
-        <v>32.52028395838352</v>
+        <v>32.52028395838351</v>
       </c>
       <c r="BZ41" s="417" t="n">
         <v>33.86831783406382</v>
       </c>
       <c r="CA41" s="417" t="n">
-        <v>35.35776816236777</v>
+        <v>35.35776816236775</v>
       </c>
       <c r="CB41" s="418" t="n">
-        <v>36.92500467223028</v>
+        <v>36.92500467223027</v>
       </c>
       <c r="CC41" s="417" t="n">
-        <v>22.52427460963667</v>
+        <v>22.52427460963666</v>
       </c>
       <c r="CD41" s="417" t="n">
-        <v>32.52028395838352</v>
+        <v>32.52028395838351</v>
       </c>
       <c r="CE41" s="417" t="n">
         <v>33.86831783406382</v>
       </c>
       <c r="CF41" s="417" t="n">
-        <v>35.35776816236777</v>
+        <v>35.35776816236775</v>
       </c>
       <c r="CG41" s="418" t="n">
-        <v>36.92500467223028</v>
+        <v>36.92500467223027</v>
       </c>
       <c r="CW41" s="132" t="n">
-        <v>0.09141147290516471</v>
+        <v>0.09141147290517537</v>
       </c>
       <c r="CX41" s="133" t="n">
-        <v>0.1058867661861811</v>
+        <v>0.1058867661861953</v>
       </c>
       <c r="CY41" s="133" t="n">
-        <v>0.1102759583461221</v>
+        <v>0.1102759583461292</v>
       </c>
       <c r="CZ41" s="133" t="n">
-        <v>0.1151256387396629</v>
+        <v>0.1151256387396771</v>
       </c>
       <c r="DA41" s="134" t="n">
-        <v>0.1202286009377929</v>
+        <v>0.1202286009378</v>
       </c>
       <c r="DC41" s="422" t="n">
         <v>0</v>
@@ -10487,13 +10487,13 @@
         <v>1.036663558378054</v>
       </c>
       <c r="AV42" s="437" t="n">
-        <v>0.7076572009521694</v>
+        <v>0.7076572009521693</v>
       </c>
       <c r="AW42" s="437" t="n">
         <v>0.6388471416970486</v>
       </c>
       <c r="AX42" s="437" t="n">
-        <v>0.7725793681123854</v>
+        <v>0.7725793681123855</v>
       </c>
       <c r="AY42" s="438" t="n">
         <v>1.08371431320713</v>
@@ -10510,13 +10510,13 @@
         <v>288.1847568729067</v>
       </c>
       <c r="BD42" s="440" t="n">
-        <v>299.0010333103697</v>
+        <v>299.0010333103696</v>
       </c>
       <c r="BE42" s="440" t="n">
         <v>373.8923983895505</v>
       </c>
       <c r="BF42" s="441" t="n">
-        <v>541.3620711002277</v>
+        <v>541.3620711002279</v>
       </c>
       <c r="BG42" s="442" t="n">
         <v>1.195330134541267</v>
@@ -10525,7 +10525,7 @@
         <v>0.9600543652473262</v>
       </c>
       <c r="BI42" s="443" t="n">
-        <v>0.9917181252510247</v>
+        <v>0.9917181252510245</v>
       </c>
       <c r="BJ42" s="443" t="n">
         <v>1.256981514897621</v>
@@ -10534,19 +10534,19 @@
         <v>1.823553892449677</v>
       </c>
       <c r="BL42" s="443" t="n">
-        <v>1.004879198531257</v>
+        <v>1.004879198531256</v>
       </c>
       <c r="BM42" s="443" t="n">
-        <v>0.6658266572964089</v>
+        <v>0.6658266572964088</v>
       </c>
       <c r="BN42" s="443" t="n">
-        <v>0.5846425497588635</v>
+        <v>0.5846425497588634</v>
       </c>
       <c r="BO42" s="443" t="n">
         <v>0.6877843570899708</v>
       </c>
       <c r="BP42" s="444" t="n">
-        <v>0.943924434468687</v>
+        <v>0.9439244344686875</v>
       </c>
       <c r="BR42" s="155" t="inlineStr">
         <is>
@@ -10554,40 +10554,40 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>372.4189745924095</v>
+        <v>372.4189745924094</v>
       </c>
       <c r="BT42" s="440" t="n">
-        <v>285.8482213177363</v>
+        <v>285.8482213177362</v>
       </c>
       <c r="BU42" s="440" t="n">
-        <v>296.8857346669486</v>
+        <v>296.8857346669485</v>
       </c>
       <c r="BV42" s="440" t="n">
         <v>372.5525325986642</v>
       </c>
       <c r="BW42" s="441" t="n">
-        <v>542.0490575350246</v>
+        <v>542.0490575350248</v>
       </c>
       <c r="BX42" s="442" t="n">
         <v>1.187329655010871</v>
       </c>
       <c r="BY42" s="443" t="n">
-        <v>0.9504658730338159</v>
+        <v>0.9504658730338155</v>
       </c>
       <c r="BZ42" s="443" t="n">
-        <v>0.9804288971651034</v>
+        <v>0.9804288971651033</v>
       </c>
       <c r="CA42" s="443" t="n">
         <v>1.244165984092921</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>1.809225069629853</v>
+        <v>1.809225069629854</v>
       </c>
       <c r="CC42" s="443" t="n">
         <v>1.00010075122926</v>
       </c>
       <c r="CD42" s="443" t="n">
-        <v>0.6615315899007601</v>
+        <v>0.66153158990076</v>
       </c>
       <c r="CE42" s="443" t="n">
         <v>0.5813276294704895</v>
@@ -10596,7 +10596,7 @@
         <v>0.6862277568899725</v>
       </c>
       <c r="CG42" s="444" t="n">
-        <v>0.946270460230802</v>
+        <v>0.9462704602308021</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickBot="1">
@@ -11240,10 +11240,10 @@
         <v>23420.69497879438</v>
       </c>
       <c r="E47" s="375" t="n">
-        <v>24125.43688001037</v>
+        <v>24125.43688001036</v>
       </c>
       <c r="F47" s="375" t="n">
-        <v>22927.5711985104</v>
+        <v>22927.57119851041</v>
       </c>
       <c r="G47" s="455" t="n">
         <v>22594.86520251621</v>
@@ -11258,7 +11258,7 @@
         <v>178.0972706787459</v>
       </c>
       <c r="K47" s="372" t="n">
-        <v>176.4728096596964</v>
+        <v>176.4728096596965</v>
       </c>
       <c r="L47" s="373" t="n">
         <v>184.1462011265056</v>
@@ -11273,7 +11273,7 @@
         <v>103.4371137297133</v>
       </c>
       <c r="P47" s="372" t="n">
-        <v>93.75403922044431</v>
+        <v>93.75403922044434</v>
       </c>
       <c r="Q47" s="373" t="n">
         <v>89.94693514177501</v>
@@ -11290,10 +11290,10 @@
         <v>23420.69497879438</v>
       </c>
       <c r="V47" s="375" t="n">
-        <v>24125.43688001037</v>
+        <v>24125.43688001036</v>
       </c>
       <c r="W47" s="375" t="n">
-        <v>22927.5711985104</v>
+        <v>22927.57119851041</v>
       </c>
       <c r="X47" s="376" t="n">
         <v>22594.86520251621</v>
@@ -11308,7 +11308,7 @@
         <v>178.0972706787459</v>
       </c>
       <c r="AB47" s="372" t="n">
-        <v>176.4728096596964</v>
+        <v>176.4728096596965</v>
       </c>
       <c r="AC47" s="378" t="n">
         <v>184.1462011265056</v>
@@ -11323,7 +11323,7 @@
         <v>103.4371137297133</v>
       </c>
       <c r="AG47" s="372" t="n">
-        <v>93.75403922044431</v>
+        <v>93.75403922044434</v>
       </c>
       <c r="AH47" s="378" t="n">
         <v>89.94693514177501</v>
@@ -11340,10 +11340,10 @@
         <v>23420.69497879438</v>
       </c>
       <c r="AM47" s="375" t="n">
-        <v>24125.43688001037</v>
+        <v>24125.43688001036</v>
       </c>
       <c r="AN47" s="375" t="n">
-        <v>22927.5711985104</v>
+        <v>22927.57119851041</v>
       </c>
       <c r="AO47" s="456" t="n">
         <v>22594.86520251621</v>
@@ -11358,7 +11358,7 @@
         <v>178.0972706787459</v>
       </c>
       <c r="AS47" s="372" t="n">
-        <v>176.4728096596964</v>
+        <v>176.4728096596965</v>
       </c>
       <c r="AT47" s="382" t="n">
         <v>184.1462011265056</v>
@@ -11373,7 +11373,7 @@
         <v>103.4371136454514</v>
       </c>
       <c r="AX47" s="372" t="n">
-        <v>93.75403912460099</v>
+        <v>93.75403912460102</v>
       </c>
       <c r="AY47" s="382" t="n">
         <v>89.94693524561414</v>
@@ -11390,16 +11390,16 @@
         <v>25108.96630535545</v>
       </c>
       <c r="BD47" s="375" t="n">
-        <v>26678.26685355693</v>
+        <v>26678.26685355692</v>
       </c>
       <c r="BE47" s="375" t="n">
-        <v>26025.02256328181</v>
+        <v>26025.0225632818</v>
       </c>
       <c r="BF47" s="392" t="n">
         <v>26290.6697271283</v>
       </c>
       <c r="BG47" s="386" t="n">
-        <v>173.4236127600464</v>
+        <v>173.4236127600463</v>
       </c>
       <c r="BH47" s="372" t="n">
         <v>180.4922637504336</v>
@@ -11408,7 +11408,7 @@
         <v>196.9426102701814</v>
       </c>
       <c r="BJ47" s="372" t="n">
-        <v>200.3137974552543</v>
+        <v>200.3137974552542</v>
       </c>
       <c r="BK47" s="387" t="n">
         <v>214.2666889990191</v>
@@ -11434,43 +11434,43 @@
         </is>
       </c>
       <c r="BS47" s="391" t="n">
-        <v>26341.16222734956</v>
+        <v>26341.16222734954</v>
       </c>
       <c r="BT47" s="375" t="n">
-        <v>25006.80944039012</v>
+        <v>25006.80944039011</v>
       </c>
       <c r="BU47" s="375" t="n">
-        <v>26644.06184234361</v>
+        <v>26644.06184234359</v>
       </c>
       <c r="BV47" s="375" t="n">
-        <v>26043.40209844784</v>
+        <v>26043.40209844783</v>
       </c>
       <c r="BW47" s="392" t="n">
-        <v>26381.08666915488</v>
+        <v>26381.08666915487</v>
       </c>
       <c r="BX47" s="386" t="n">
-        <v>172.784862292404</v>
+        <v>172.7848622924039</v>
       </c>
       <c r="BY47" s="372" t="n">
-        <v>179.7296438221846</v>
+        <v>179.7296438221845</v>
       </c>
       <c r="BZ47" s="372" t="n">
-        <v>196.1465345738421</v>
+        <v>196.146534573842</v>
       </c>
       <c r="CA47" s="372" t="n">
         <v>199.4256401526904</v>
       </c>
       <c r="CB47" s="387" t="n">
-        <v>213.3215874713197</v>
+        <v>213.3215874713196</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>156.8668178570583</v>
+        <v>156.8668178570582</v>
       </c>
       <c r="CD47" s="389" t="n">
         <v>129.5600244796603</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>114.5093789363011</v>
+        <v>114.509378936301</v>
       </c>
       <c r="CF47" s="389" t="n">
         <v>106.7360205689818</v>
@@ -11501,7 +11501,7 @@
         <v>28412.3764402447</v>
       </c>
       <c r="H48" s="371" t="n">
-        <v>256.3637298566919</v>
+        <v>256.3637298566918</v>
       </c>
       <c r="I48" s="372" t="n">
         <v>250.3363769332586</v>
@@ -11516,7 +11516,7 @@
         <v>311.9942548690993</v>
       </c>
       <c r="M48" s="371" t="n">
-        <v>199.6427483249515</v>
+        <v>199.6427483249514</v>
       </c>
       <c r="N48" s="372" t="n">
         <v>160.2608134242311</v>
@@ -11551,7 +11551,7 @@
         <v>28412.3764402447</v>
       </c>
       <c r="Y48" s="377" t="n">
-        <v>256.3637298566919</v>
+        <v>256.3637298566918</v>
       </c>
       <c r="Z48" s="372" t="n">
         <v>250.3363769332586</v>
@@ -11566,7 +11566,7 @@
         <v>311.9942548690993</v>
       </c>
       <c r="AD48" s="377" t="n">
-        <v>199.6427483249515</v>
+        <v>199.6427483249514</v>
       </c>
       <c r="AE48" s="372" t="n">
         <v>160.2608134242311</v>
@@ -11601,13 +11601,13 @@
         <v>28412.3764402447</v>
       </c>
       <c r="AP48" s="381" t="n">
-        <v>265.9699239827366</v>
+        <v>265.9699239827365</v>
       </c>
       <c r="AQ48" s="372" t="n">
         <v>260.0392899573951</v>
       </c>
       <c r="AR48" s="372" t="n">
-        <v>284.0466471539795</v>
+        <v>284.0466471539796</v>
       </c>
       <c r="AS48" s="372" t="n">
         <v>308.4476909555582</v>
@@ -11648,7 +11648,7 @@
         <v>29643.15629724725</v>
       </c>
       <c r="BF48" s="392" t="n">
-        <v>32883.58026505759</v>
+        <v>32883.58026505758</v>
       </c>
       <c r="BG48" s="386" t="n">
         <v>275.2110243105232</v>
@@ -11663,7 +11663,7 @@
         <v>348.16909332829</v>
       </c>
       <c r="BK48" s="387" t="n">
-        <v>374.0454279563896</v>
+        <v>374.0454279563895</v>
       </c>
       <c r="BL48" s="386" t="n">
         <v>206.5793189708344</v>
@@ -11678,7 +11678,7 @@
         <v>185.7204990751851</v>
       </c>
       <c r="BP48" s="387" t="n">
-        <v>196.0285895469812</v>
+        <v>196.0285895469811</v>
       </c>
       <c r="BR48" s="101" t="inlineStr">
         <is>
@@ -11695,10 +11695,10 @@
         <v>25686.67107992767</v>
       </c>
       <c r="BV48" s="375" t="n">
-        <v>29822.05807506683</v>
+        <v>29822.05807506682</v>
       </c>
       <c r="BW48" s="392" t="n">
-        <v>33172.06839169405</v>
+        <v>33172.06839169403</v>
       </c>
       <c r="BX48" s="386" t="n">
         <v>274.532950600186</v>
@@ -11710,10 +11710,10 @@
         <v>311.4000205947125</v>
       </c>
       <c r="CA48" s="372" t="n">
-        <v>347.3623777653925</v>
+        <v>347.3623777653924</v>
       </c>
       <c r="CB48" s="387" t="n">
-        <v>373.3680918579745</v>
+        <v>373.3680918579744</v>
       </c>
       <c r="CC48" s="386" t="n">
         <v>206.5575802734972</v>
@@ -11725,10 +11725,10 @@
         <v>171.5625909330092</v>
       </c>
       <c r="CF48" s="372" t="n">
-        <v>186.9412604717898</v>
+        <v>186.9412604717897</v>
       </c>
       <c r="CG48" s="387" t="n">
-        <v>197.8360289087525</v>
+        <v>197.8360289087524</v>
       </c>
     </row>
     <row r="49">
@@ -11744,7 +11744,7 @@
         <v>47439.95465122464</v>
       </c>
       <c r="E49" s="375" t="n">
-        <v>56489.12845072967</v>
+        <v>56489.12845072969</v>
       </c>
       <c r="F49" s="375" t="n">
         <v>68266.49627472812</v>
@@ -11759,7 +11759,7 @@
         <v>586.4221588579422</v>
       </c>
       <c r="J49" s="372" t="n">
-        <v>676.6004797784625</v>
+        <v>676.6004797784626</v>
       </c>
       <c r="K49" s="372" t="n">
         <v>834.6298914132976</v>
@@ -11774,7 +11774,7 @@
         <v>433.2280086414883</v>
       </c>
       <c r="O49" s="372" t="n">
-        <v>441.9841714234138</v>
+        <v>441.9841714234139</v>
       </c>
       <c r="P49" s="372" t="n">
         <v>491.6277572192629</v>
@@ -11794,7 +11794,7 @@
         <v>47439.95465122464</v>
       </c>
       <c r="V49" s="375" t="n">
-        <v>56489.12845072967</v>
+        <v>56489.12845072969</v>
       </c>
       <c r="W49" s="375" t="n">
         <v>68266.49627472812</v>
@@ -11809,7 +11809,7 @@
         <v>586.4221588579422</v>
       </c>
       <c r="AA49" s="372" t="n">
-        <v>676.6004797784625</v>
+        <v>676.6004797784626</v>
       </c>
       <c r="AB49" s="372" t="n">
         <v>834.6298914132976</v>
@@ -11824,7 +11824,7 @@
         <v>433.2280086414883</v>
       </c>
       <c r="AF49" s="372" t="n">
-        <v>441.9841714234138</v>
+        <v>441.9841714234139</v>
       </c>
       <c r="AG49" s="372" t="n">
         <v>491.6277572192629</v>
@@ -11897,7 +11897,7 @@
         <v>62289.28854629439</v>
       </c>
       <c r="BE49" s="375" t="n">
-        <v>77252.96485072572</v>
+        <v>77252.96485072571</v>
       </c>
       <c r="BF49" s="392" t="n">
         <v>88872.18069931729</v>
@@ -11912,7 +11912,7 @@
         <v>761.7656506723247</v>
       </c>
       <c r="BJ49" s="372" t="n">
-        <v>965.0608518498905</v>
+        <v>965.0608518498904</v>
       </c>
       <c r="BK49" s="387" t="n">
         <v>1059.653141236068</v>
@@ -11927,7 +11927,7 @@
         <v>494.0143326081971</v>
       </c>
       <c r="BO49" s="372" t="n">
-        <v>563.4156665444258</v>
+        <v>563.4156665444257</v>
       </c>
       <c r="BP49" s="387" t="n">
         <v>583.9832171489149</v>
@@ -11953,13 +11953,13 @@
         <v>89797.18623305205</v>
       </c>
       <c r="BX49" s="386" t="n">
-        <v>579.82830575</v>
+        <v>579.8283057500001</v>
       </c>
       <c r="BY49" s="372" t="n">
         <v>641.6337824716056</v>
       </c>
       <c r="BZ49" s="372" t="n">
-        <v>762.0533737760867</v>
+        <v>762.0533737760868</v>
       </c>
       <c r="CA49" s="372" t="n">
         <v>965.4865105334821</v>
@@ -11974,7 +11974,7 @@
         <v>473.1787500567564</v>
       </c>
       <c r="CE49" s="372" t="n">
-        <v>497.0908193962615</v>
+        <v>497.0908193962616</v>
       </c>
       <c r="CF49" s="372" t="n">
         <v>568.2731845328248</v>
@@ -12146,7 +12146,7 @@
         <v>848.4921597470884</v>
       </c>
       <c r="BD50" s="420" t="n">
-        <v>952.5982018390351</v>
+        <v>952.5982018390349</v>
       </c>
       <c r="BE50" s="420" t="n">
         <v>1046.418764034404</v>
@@ -12161,13 +12161,13 @@
         <v>380.9780246374449</v>
       </c>
       <c r="BI50" s="417" t="n">
-        <v>415.107303147882</v>
+        <v>415.1073031478819</v>
       </c>
       <c r="BJ50" s="417" t="n">
         <v>446.927180464714</v>
       </c>
       <c r="BK50" s="418" t="n">
-        <v>480.1580997842901</v>
+        <v>480.15809978429</v>
       </c>
       <c r="BL50" s="417" t="n">
         <v>252.8466531093813</v>
@@ -12176,13 +12176,13 @@
         <v>380.9780246374449</v>
       </c>
       <c r="BN50" s="417" t="n">
-        <v>415.107303147882</v>
+        <v>415.1073031478819</v>
       </c>
       <c r="BO50" s="417" t="n">
         <v>446.927180464714</v>
       </c>
       <c r="BP50" s="418" t="n">
-        <v>480.1580997842901</v>
+        <v>480.15809978429</v>
       </c>
       <c r="BR50" s="111" t="inlineStr">
         <is>
@@ -12190,49 +12190,49 @@
         </is>
       </c>
       <c r="BS50" s="419" t="n">
-        <v>755.2092654082581</v>
+        <v>755.2092654082578</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699296</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>946.7796925421452</v>
+        <v>946.7796925421446</v>
       </c>
       <c r="BV50" s="420" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="BW50" s="421" t="n">
-        <v>1140.017687397479</v>
+        <v>1140.017687397478</v>
       </c>
       <c r="BX50" s="416" t="n">
-        <v>251.8246595737656</v>
+        <v>251.8246595737655</v>
       </c>
       <c r="BY50" s="417" t="n">
-        <v>379.7415776342887</v>
+        <v>379.7415776342885</v>
       </c>
       <c r="BZ50" s="417" t="n">
-        <v>413.760091548992</v>
+        <v>413.7600915489917</v>
       </c>
       <c r="CA50" s="417" t="n">
-        <v>445.4766989390283</v>
+        <v>445.4766989390281</v>
       </c>
       <c r="CB50" s="418" t="n">
-        <v>478.5997687531334</v>
+        <v>478.5997687531333</v>
       </c>
       <c r="CC50" s="417" t="n">
-        <v>251.8246595737656</v>
+        <v>251.8246595737655</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>379.7415776342887</v>
+        <v>379.7415776342885</v>
       </c>
       <c r="CE50" s="417" t="n">
-        <v>413.760091548992</v>
+        <v>413.7600915489917</v>
       </c>
       <c r="CF50" s="417" t="n">
-        <v>445.4766989390283</v>
+        <v>445.4766989390282</v>
       </c>
       <c r="CG50" s="418" t="n">
-        <v>478.5997687531334</v>
+        <v>478.5997687531332</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickBot="1">
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="C51" s="425" t="n">
-        <v>90032.48838082486</v>
+        <v>90032.48838082484</v>
       </c>
       <c r="D51" s="425" t="n">
         <v>92359.96532172995</v>
@@ -12263,7 +12263,7 @@
         <v>302.8565327461747</v>
       </c>
       <c r="J51" s="427" t="n">
-        <v>341.9611404536603</v>
+        <v>341.9611404536604</v>
       </c>
       <c r="K51" s="427" t="n">
         <v>391.5322002496239</v>
@@ -12292,7 +12292,7 @@
         </is>
       </c>
       <c r="T51" s="429" t="n">
-        <v>90032.48838082486</v>
+        <v>90032.48838082484</v>
       </c>
       <c r="U51" s="430" t="n">
         <v>92359.96532172995</v>
@@ -12313,7 +12313,7 @@
         <v>302.8565327461747</v>
       </c>
       <c r="AA51" s="433" t="n">
-        <v>341.9611404536603</v>
+        <v>341.9611404536604</v>
       </c>
       <c r="AB51" s="433" t="n">
         <v>391.5322002496239</v>
@@ -12328,7 +12328,7 @@
         <v>212.5547961320387</v>
       </c>
       <c r="AF51" s="433" t="n">
-        <v>204.1397368201065</v>
+        <v>204.1397368201066</v>
       </c>
       <c r="AG51" s="433" t="n">
         <v>217.0513111120699</v>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="AK51" s="435" t="n">
-        <v>90945.65390440408</v>
+        <v>90945.65390440407</v>
       </c>
       <c r="AL51" s="408" t="n">
         <v>92742.75614761523</v>
@@ -12351,7 +12351,7 @@
         <v>105062.7617317974</v>
       </c>
       <c r="AN51" s="408" t="n">
-        <v>118615.6026291498</v>
+        <v>118615.6026291499</v>
       </c>
       <c r="AO51" s="409" t="n">
         <v>128858.9943369083</v>
@@ -12363,7 +12363,7 @@
         <v>308.9618231399147</v>
       </c>
       <c r="AR51" s="437" t="n">
-        <v>348.4691806740312</v>
+        <v>348.4691806740313</v>
       </c>
       <c r="AS51" s="437" t="n">
         <v>398.7714661370073</v>
@@ -12381,7 +12381,7 @@
         <v>205.4312663188236</v>
       </c>
       <c r="AX51" s="437" t="n">
-        <v>218.1963483251424</v>
+        <v>218.1963483251425</v>
       </c>
       <c r="AY51" s="438" t="n">
         <v>224.6798581741623</v>
@@ -12395,7 +12395,7 @@
         <v>93981.06660167991</v>
       </c>
       <c r="BC51" s="440" t="n">
-        <v>98851.75761091994</v>
+        <v>98851.75761091996</v>
       </c>
       <c r="BD51" s="440" t="n">
         <v>115508.9825858523</v>
@@ -12410,7 +12410,7 @@
         <v>299.5562674783223</v>
       </c>
       <c r="BH51" s="443" t="n">
-        <v>329.313258745978</v>
+        <v>329.3132587459781</v>
       </c>
       <c r="BI51" s="443" t="n">
         <v>383.1169089666216</v>
@@ -12419,10 +12419,10 @@
         <v>450.3829185954293</v>
       </c>
       <c r="BK51" s="444" t="n">
-        <v>502.5514699116341</v>
+        <v>502.551469911634</v>
       </c>
       <c r="BL51" s="443" t="n">
-        <v>251.8282215767555</v>
+        <v>251.8282215767554</v>
       </c>
       <c r="BM51" s="443" t="n">
         <v>228.388676945118</v>
@@ -12431,7 +12431,7 @@
         <v>225.856965614382</v>
       </c>
       <c r="BO51" s="443" t="n">
-        <v>246.4366599183377</v>
+        <v>246.4366599183376</v>
       </c>
       <c r="BP51" s="444" t="n">
         <v>260.1352304375821</v>
@@ -12442,10 +12442,10 @@
         </is>
       </c>
       <c r="BS51" s="439" t="n">
-        <v>93885.37362986163</v>
+        <v>93885.37362986161</v>
       </c>
       <c r="BT51" s="440" t="n">
-        <v>98948.90706760544</v>
+        <v>98948.90706760543</v>
       </c>
       <c r="BU51" s="440" t="n">
         <v>115917.258825756</v>
@@ -12460,10 +12460,10 @@
         <v>299.321183633328</v>
       </c>
       <c r="BY51" s="417" t="n">
-        <v>329.0122251179391</v>
+        <v>329.012225117939</v>
       </c>
       <c r="BZ51" s="417" t="n">
-        <v>382.802596966913</v>
+        <v>382.8025969669129</v>
       </c>
       <c r="CA51" s="417" t="n">
         <v>450.1130050146622</v>
@@ -12481,10 +12481,10 @@
         <v>226.9758948286571</v>
       </c>
       <c r="CF51" s="417" t="n">
-        <v>248.2627251728077</v>
+        <v>248.2627251728076</v>
       </c>
       <c r="CG51" s="418" t="n">
-        <v>262.7153009012112</v>
+        <v>262.7153009012111</v>
       </c>
     </row>
     <row r="52">
@@ -13653,25 +13653,25 @@
         <v>4473</v>
       </c>
       <c r="CW58" s="91" t="n">
-        <v>0.6325076527118622</v>
+        <v>0.6325076527118648</v>
       </c>
       <c r="CX58" s="92" t="n">
-        <v>0.5588274414371717</v>
+        <v>0.5588274414371737</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>0.5575524490069852</v>
+        <v>0.5575524490069873</v>
       </c>
       <c r="CZ58" s="92" t="n">
-        <v>0.5519744899537801</v>
+        <v>0.5519744899537821</v>
       </c>
       <c r="DA58" s="93" t="n">
-        <v>0.539746239387339</v>
+        <v>0.5397462393873407</v>
       </c>
       <c r="DC58" s="393" t="n">
         <v>0.003727999122884204</v>
       </c>
       <c r="DD58" s="394" t="n">
-        <v>0.003650943496526009</v>
+        <v>0.003650943496526008</v>
       </c>
       <c r="DE58" s="394" t="n">
         <v>0.003733252162249805</v>
@@ -13962,19 +13962,19 @@
         <v>7774</v>
       </c>
       <c r="CW59" s="102" t="n">
-        <v>0.09887116171637625</v>
+        <v>0.09887116171637669</v>
       </c>
       <c r="CX59" s="103" t="n">
-        <v>0.08086620964899183</v>
+        <v>0.08086620964899219</v>
       </c>
       <c r="CY59" s="103" t="n">
-        <v>0.0829405029737426</v>
+        <v>0.08294050297374299</v>
       </c>
       <c r="CZ59" s="103" t="n">
-        <v>0.08529935814310885</v>
+        <v>0.08529935814310928</v>
       </c>
       <c r="DA59" s="104" t="n">
-        <v>0.07434357734795088</v>
+        <v>0.07434357734795133</v>
       </c>
       <c r="DC59" s="396" t="n">
         <v>0.000897498568074756</v>
@@ -14214,13 +14214,13 @@
         <v>67.40054441000001</v>
       </c>
       <c r="BX60" s="197" t="n">
-        <v>76.49891397404303</v>
+        <v>76.49891397404302</v>
       </c>
       <c r="BY60" s="190" t="n">
         <v>79.4443264888429</v>
       </c>
       <c r="BZ60" s="190" t="n">
-        <v>82.19863380507508</v>
+        <v>82.19863380507506</v>
       </c>
       <c r="CA60" s="190" t="n">
         <v>80.66001790519121</v>
@@ -14271,19 +14271,19 @@
         <v>4927</v>
       </c>
       <c r="CW60" s="102" t="n">
-        <v>0.07606313161696746</v>
+        <v>0.07606313161696947</v>
       </c>
       <c r="CX60" s="103" t="n">
-        <v>0.07577105569710546</v>
+        <v>0.07577105569710751</v>
       </c>
       <c r="CY60" s="103" t="n">
-        <v>0.07533927084492804</v>
+        <v>0.07533927084493029</v>
       </c>
       <c r="CZ60" s="103" t="n">
-        <v>0.07539709805878583</v>
+        <v>0.0753970980587883</v>
       </c>
       <c r="DA60" s="104" t="n">
-        <v>0.0749527373996228</v>
+        <v>0.07495273739962528</v>
       </c>
       <c r="DC60" s="396" t="n">
         <v>0.0008781181361755121</v>
@@ -14580,19 +14580,19 @@
         <v>360</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>0.00623418106180267</v>
+        <v>0.006234181061802625</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.006396145085788257</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>0.006590523934945409</v>
+        <v>0.006590523934945361</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760346054</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885872</v>
       </c>
       <c r="DC61" s="422" t="n">
         <v>0</v>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="AK62" s="220" t="n">
-        <v>59.46086383</v>
+        <v>59.46086382999999</v>
       </c>
       <c r="AL62" s="209" t="n">
         <v>132.64704174</v>
@@ -14747,10 +14747,10 @@
         <v>296.871989</v>
       </c>
       <c r="AU62" s="207" t="n">
-        <v>373.1951328299999</v>
+        <v>373.19513283</v>
       </c>
       <c r="AV62" s="207" t="n">
-        <v>432.82249774</v>
+        <v>432.8224977400001</v>
       </c>
       <c r="AW62" s="207" t="n">
         <v>511.42537168</v>
@@ -14767,7 +14767,7 @@
         </is>
       </c>
       <c r="BB62" s="221" t="n">
-        <v>59.46086383</v>
+        <v>59.46086382999999</v>
       </c>
       <c r="BC62" s="222" t="n">
         <v>132.64704174</v>
@@ -14797,10 +14797,10 @@
         <v>296.871989</v>
       </c>
       <c r="BL62" s="222" t="n">
-        <v>373.1951328299999</v>
+        <v>373.19513283</v>
       </c>
       <c r="BM62" s="222" t="n">
-        <v>432.82249774</v>
+        <v>432.8224977400001</v>
       </c>
       <c r="BN62" s="222" t="n">
         <v>511.42537168</v>
@@ -14835,7 +14835,7 @@
         <v>313.660972772553</v>
       </c>
       <c r="BY62" s="222" t="n">
-        <v>300.7453812153509</v>
+        <v>300.745381215351</v>
       </c>
       <c r="BZ62" s="222" t="n">
         <v>302.8121014439594</v>
@@ -14859,7 +14859,7 @@
         <v>542.899247164084</v>
       </c>
       <c r="CG62" s="214" t="n">
-        <v>572.8267766097391</v>
+        <v>572.8267766097392</v>
       </c>
       <c r="CI62" s="349" t="n">
         <v>0</v>
@@ -14889,19 +14889,19 @@
         <v>17534</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>0.8136761271070085</v>
+        <v>0.8136761271070136</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>0.7218608518690572</v>
+        <v>0.7218608518690617</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>0.7224227467606013</v>
+        <v>0.7224227467606059</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>0.7193951259160208</v>
+        <v>0.7193951259160257</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>0.6959031002607986</v>
+        <v>0.6959031002608032</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="BS67" s="236" t="n">
-        <v>71.47924935026255</v>
+        <v>71.47924935026256</v>
       </c>
       <c r="BT67" s="237" t="n">
         <v>56.33223463137914</v>
@@ -15769,7 +15769,7 @@
         <v>45.51792185462426</v>
       </c>
       <c r="BX67" s="462" t="n">
-        <v>0.4657540040095084</v>
+        <v>0.4657540040095087</v>
       </c>
       <c r="BY67" s="463" t="n">
         <v>0.4025462995973391</v>
@@ -15781,10 +15781,10 @@
         <v>0.3918221549312477</v>
       </c>
       <c r="CB67" s="464" t="n">
-        <v>0.3682217376588177</v>
+        <v>0.3682217376588176</v>
       </c>
       <c r="CC67" s="199" t="n">
-        <v>71.0044943456336</v>
+        <v>71.00449434563363</v>
       </c>
       <c r="CD67" s="200" t="n">
         <v>56.00856036260793</v>
@@ -15793,10 +15793,10 @@
         <v>55.48203028735139</v>
       </c>
       <c r="CF67" s="200" t="n">
-        <v>51.16885634235306</v>
+        <v>51.16885634235305</v>
       </c>
       <c r="CG67" s="201" t="n">
-        <v>45.5373021070833</v>
+        <v>45.53730210708329</v>
       </c>
       <c r="CW67" s="465" t="n"/>
       <c r="CX67" s="465" t="n"/>
@@ -16041,7 +16041,7 @@
         <v>0.2116220377663219</v>
       </c>
       <c r="CA68" s="463" t="n">
-        <v>0.2217157632371279</v>
+        <v>0.2217157632371278</v>
       </c>
       <c r="CB68" s="464" t="n">
         <v>0.2241174067434663</v>
@@ -16280,16 +16280,16 @@
         </is>
       </c>
       <c r="BS69" s="236" t="n">
-        <v>45.33733851771335</v>
+        <v>45.33733851771334</v>
       </c>
       <c r="BT69" s="237" t="n">
-        <v>46.47854001102073</v>
+        <v>46.47854001102072</v>
       </c>
       <c r="BU69" s="237" t="n">
         <v>50.45142226201709</v>
       </c>
       <c r="BV69" s="237" t="n">
-        <v>55.51399834326029</v>
+        <v>55.5139983432603</v>
       </c>
       <c r="BW69" s="238" t="n">
         <v>55.46093120356361</v>
@@ -16298,28 +16298,28 @@
         <v>0.5931011032526519</v>
       </c>
       <c r="BY69" s="463" t="n">
-        <v>0.5864807637667119</v>
+        <v>0.5864807637667117</v>
       </c>
       <c r="BZ69" s="463" t="n">
-        <v>0.6166436496495233</v>
+        <v>0.6166436496495235</v>
       </c>
       <c r="CA69" s="463" t="n">
-        <v>0.6932064424993806</v>
+        <v>0.6932064424993808</v>
       </c>
       <c r="CB69" s="464" t="n">
-        <v>0.6609797710301051</v>
+        <v>0.660979771030105</v>
       </c>
       <c r="CC69" s="197" t="n">
-        <v>45.37159027563463</v>
+        <v>45.37159027563462</v>
       </c>
       <c r="CD69" s="190" t="n">
-        <v>46.59256927610861</v>
+        <v>46.59256927610859</v>
       </c>
       <c r="CE69" s="190" t="n">
         <v>50.68726554576618</v>
       </c>
       <c r="CF69" s="190" t="n">
-        <v>55.91404406399394</v>
+        <v>55.91404406399396</v>
       </c>
       <c r="CG69" s="198" t="n">
         <v>55.98979050979757</v>
@@ -16721,7 +16721,7 @@
         <v>0.018</v>
       </c>
       <c r="AP71" s="206" t="n">
-        <v>0.7403798996599998</v>
+        <v>0.74037989966</v>
       </c>
       <c r="AQ71" s="207" t="n">
         <v>1.29178606722</v>
@@ -16739,7 +16739,7 @@
         <v>314.47464889966</v>
       </c>
       <c r="AV71" s="207" t="n">
-        <v>301.46724206722</v>
+        <v>301.4672420672201</v>
       </c>
       <c r="AW71" s="207" t="n">
         <v>303.53452419072</v>
@@ -16771,7 +16771,7 @@
         <v>0.018</v>
       </c>
       <c r="BG71" s="221" t="n">
-        <v>0.7403798996599998</v>
+        <v>0.74037989966</v>
       </c>
       <c r="BH71" s="222" t="n">
         <v>1.29178606722</v>
@@ -16789,7 +16789,7 @@
         <v>314.47464889966</v>
       </c>
       <c r="BM71" s="222" t="n">
-        <v>301.46724206722</v>
+        <v>301.4672420672201</v>
       </c>
       <c r="BN71" s="222" t="n">
         <v>303.53452419072</v>
@@ -16821,10 +16821,10 @@
         <v>123.1276364700726</v>
       </c>
       <c r="BX71" s="466" t="n">
-        <v>0.4422912017091774</v>
+        <v>0.4422912017091776</v>
       </c>
       <c r="BY71" s="467" t="n">
-        <v>0.4020516272219036</v>
+        <v>0.4020516272219035</v>
       </c>
       <c r="BZ71" s="467" t="n">
         <v>0.4158147707356966</v>
@@ -16833,13 +16833,13 @@
         <v>0.4289762806318075</v>
       </c>
       <c r="CB71" s="468" t="n">
-        <v>0.413283389747968</v>
+        <v>0.4132833897479679</v>
       </c>
       <c r="CC71" s="212" t="n">
-        <v>138.729488576842</v>
+        <v>138.7294885768421</v>
       </c>
       <c r="CD71" s="212" t="n">
-        <v>120.9151698971036</v>
+        <v>120.9151698971035</v>
       </c>
       <c r="CE71" s="212" t="n">
         <v>125.9137445379145</v>
@@ -16848,7 +16848,7 @@
         <v>128.4524748445455</v>
       </c>
       <c r="CG71" s="213" t="n">
-        <v>123.8208975037021</v>
+        <v>123.820897503702</v>
       </c>
       <c r="CW71" s="465" t="n"/>
       <c r="CX71" s="465" t="n"/>
@@ -18253,7 +18253,7 @@
         <v>0.2625407779589659</v>
       </c>
       <c r="BZ78" s="463" t="n">
-        <v>0.3476955335384144</v>
+        <v>0.3476955335384145</v>
       </c>
       <c r="CA78" s="463" t="n">
         <v>0.4114126108102495</v>
@@ -18572,7 +18572,7 @@
         <v>0.4755947700452125</v>
       </c>
       <c r="M80" s="495" t="n">
-        <v>0.148642826448622</v>
+        <v>0.1486428264486221</v>
       </c>
       <c r="N80" s="495" t="n">
         <v>0.2951820885819316</v>
@@ -18622,7 +18622,7 @@
         <v>0.4755947700452125</v>
       </c>
       <c r="AD80" s="498" t="n">
-        <v>0.148642826448622</v>
+        <v>0.1486428264486221</v>
       </c>
       <c r="AE80" s="498" t="n">
         <v>0.2951820885819316</v>
@@ -18660,16 +18660,16 @@
         <v>0.1593291514256858</v>
       </c>
       <c r="AQ80" s="501" t="n">
-        <v>0.3064698402523479</v>
+        <v>0.3064698402523478</v>
       </c>
       <c r="AR80" s="501" t="n">
-        <v>0.410475078681376</v>
+        <v>0.4104750786813761</v>
       </c>
       <c r="AS80" s="501" t="n">
         <v>0.4528285826494517</v>
       </c>
       <c r="AT80" s="502" t="n">
-        <v>0.4823709689212073</v>
+        <v>0.4823709689212075</v>
       </c>
       <c r="AU80" s="501" t="n">
         <v>0.1573452565821342</v>
@@ -18678,7 +18678,7 @@
         <v>0.3034852771255115</v>
       </c>
       <c r="AW80" s="501" t="n">
-        <v>0.4064930271378044</v>
+        <v>0.4064930271378045</v>
       </c>
       <c r="AX80" s="501" t="n">
         <v>0.447850117626528</v>
@@ -18710,16 +18710,16 @@
         <v>0.1593291514256858</v>
       </c>
       <c r="BH80" s="504" t="n">
-        <v>0.3064698402523479</v>
+        <v>0.3064698402523478</v>
       </c>
       <c r="BI80" s="504" t="n">
-        <v>0.410475078681376</v>
+        <v>0.4104750786813761</v>
       </c>
       <c r="BJ80" s="504" t="n">
         <v>0.4528285826494517</v>
       </c>
       <c r="BK80" s="505" t="n">
-        <v>0.4823709689212073</v>
+        <v>0.4823709689212075</v>
       </c>
       <c r="BL80" s="504" t="n">
         <v>0.1573452565821342</v>
@@ -18728,7 +18728,7 @@
         <v>0.3034852771255115</v>
       </c>
       <c r="BN80" s="504" t="n">
-        <v>0.4064930271378044</v>
+        <v>0.4064930271378045</v>
       </c>
       <c r="BO80" s="504" t="n">
         <v>0.447850117626528</v>
@@ -18769,7 +18769,7 @@
         <v>0.4484435632675828</v>
       </c>
       <c r="CB80" s="505" t="n">
-        <v>0.476974713585857</v>
+        <v>0.4769747135858569</v>
       </c>
       <c r="CC80" s="492" t="n">
         <v>0</v>
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="AK91" s="435" t="n">
-        <v>80794.97273624</v>
+        <v>80794.97273623999</v>
       </c>
       <c r="AL91" s="408" t="n">
         <v>174399.72519538</v>
@@ -20246,7 +20246,7 @@
         </is>
       </c>
       <c r="BB91" s="439" t="n">
-        <v>80794.97273624</v>
+        <v>80794.97273623999</v>
       </c>
       <c r="BC91" s="440" t="n">
         <v>174399.72519538</v>
@@ -20987,13 +20987,13 @@
         <v>980.9518563653344</v>
       </c>
       <c r="AU96" s="379" t="n">
-        <v>62744.73673092617</v>
+        <v>62744.73673092618</v>
       </c>
       <c r="AV96" s="375" t="n">
         <v>57819.84417732574</v>
       </c>
       <c r="AW96" s="375" t="n">
-        <v>60662.44851795744</v>
+        <v>60662.44851795745</v>
       </c>
       <c r="AX96" s="375" t="n">
         <v>60011.32023524767</v>
@@ -21087,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>51470.90723857201</v>
+        <v>51470.90723857198</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>45635.36296202838</v>
+        <v>45635.36296202835</v>
       </c>
       <c r="DE96" s="375" t="n">
-        <v>48298.66965794647</v>
+        <v>48298.66965794645</v>
       </c>
       <c r="DF96" s="375" t="n">
         <v>48006.25177536014</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>47632.48598332283</v>
+        <v>47632.48598332281</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21214,19 +21214,19 @@
         <v>2679.065581588176</v>
       </c>
       <c r="AU97" s="379" t="n">
-        <v>45456.50369077884</v>
+        <v>45456.50369077885</v>
       </c>
       <c r="AV97" s="375" t="n">
         <v>43702.50065591514</v>
       </c>
       <c r="AW97" s="375" t="n">
-        <v>49502.12565485341</v>
+        <v>49502.12565485342</v>
       </c>
       <c r="AX97" s="375" t="n">
-        <v>56261.10047610578</v>
+        <v>56261.10047610577</v>
       </c>
       <c r="AY97" s="456" t="n">
-        <v>62226.25224586705</v>
+        <v>62226.25224586704</v>
       </c>
       <c r="BA97" s="101" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>41067.18882515781</v>
       </c>
       <c r="DD97" s="375" t="n">
-        <v>36821.37305298006</v>
+        <v>36821.37305298005</v>
       </c>
       <c r="DE97" s="375" t="n">
         <v>41785.52761429289</v>
@@ -21326,7 +21326,7 @@
         <v>47557.42876343117</v>
       </c>
       <c r="DG97" s="392" t="n">
-        <v>52673.28590197935</v>
+        <v>52673.28590197933</v>
       </c>
       <c r="DI97" s="368" t="n"/>
       <c r="DJ97" s="368" t="n"/>
@@ -21441,19 +21441,19 @@
         <v>2961.659668425772</v>
       </c>
       <c r="AU98" s="379" t="n">
-        <v>91957.61105517835</v>
+        <v>91957.61105517833</v>
       </c>
       <c r="AV98" s="375" t="n">
-        <v>109522.0380868603</v>
+        <v>109522.0380868604</v>
       </c>
       <c r="AW98" s="375" t="n">
-        <v>126384.8968960265</v>
+        <v>126384.8968960264</v>
       </c>
       <c r="AX98" s="375" t="n">
-        <v>147026.8981883552</v>
+        <v>147026.8981883551</v>
       </c>
       <c r="AY98" s="456" t="n">
-        <v>161259.4019061702</v>
+        <v>161259.4019061703</v>
       </c>
       <c r="BA98" s="111" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>174806.782848637</v>
       </c>
       <c r="BU98" s="375" t="n">
-        <v>198099.8272827797</v>
+        <v>198099.8272827796</v>
       </c>
       <c r="BV98" s="375" t="n">
         <v>222315.7395983371</v>
@@ -21771,16 +21771,16 @@
         <v>4417.155833572388</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>4764.761531358742</v>
+        <v>4764.761531358741</v>
       </c>
       <c r="DE99" s="420" t="n">
         <v>5167.082612807762</v>
       </c>
       <c r="DF99" s="420" t="n">
-        <v>5549.162947051829</v>
+        <v>5549.162947051827</v>
       </c>
       <c r="DG99" s="421" t="n">
-        <v>5955.299443910369</v>
+        <v>5955.299443910367</v>
       </c>
       <c r="DI99" s="368" t="n"/>
       <c r="DJ99" s="368" t="n"/>
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="AK100" s="435" t="n">
-        <v>500699.1934410001</v>
+        <v>500699.193441</v>
       </c>
       <c r="AL100" s="408" t="n">
         <v>470981.9918169999</v>
@@ -21892,7 +21892,7 @@
         <v>1883.42709415302</v>
       </c>
       <c r="AT100" s="438" t="n">
-        <v>2059.761193481949</v>
+        <v>2059.761193481948</v>
       </c>
       <c r="AU100" s="435" t="n">
         <v>205544.9016100361</v>
@@ -21904,7 +21904,7 @@
         <v>242827.0115175217</v>
       </c>
       <c r="AX100" s="408" t="n">
-        <v>270024.4103171415</v>
+        <v>270024.4103171414</v>
       </c>
       <c r="AY100" s="409" t="n">
         <v>290024.5766233449</v>
@@ -21915,7 +21915,7 @@
         </is>
       </c>
       <c r="BB100" s="439" t="n">
-        <v>500699.1934410001</v>
+        <v>500699.193441</v>
       </c>
       <c r="BC100" s="440" t="n">
         <v>470981.9918169999</v>
@@ -21942,7 +21942,7 @@
         <v>1883.42709415302</v>
       </c>
       <c r="BK100" s="444" t="n">
-        <v>2059.761193481949</v>
+        <v>2059.761193481948</v>
       </c>
       <c r="BR100" s="155" t="inlineStr">
         <is>
@@ -21965,10 +21965,10 @@
         <v>617393.3372465657</v>
       </c>
       <c r="BX100" s="442" t="n">
-        <v>1596.75384841597</v>
+        <v>1596.753848415971</v>
       </c>
       <c r="BY100" s="443" t="n">
-        <v>1570.164225545281</v>
+        <v>1570.16422554528</v>
       </c>
       <c r="BZ100" s="443" t="n">
         <v>1707.66459445468</v>
@@ -21997,10 +21997,10 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>183894.2944741638</v>
+        <v>183894.2944741637</v>
       </c>
       <c r="DD100" s="440" t="n">
-        <v>185270.002757828</v>
+        <v>185270.0027578279</v>
       </c>
       <c r="DE100" s="440" t="n">
         <v>213060.002378536</v>
@@ -22009,7 +22009,7 @@
         <v>244491.9258505616</v>
       </c>
       <c r="DG100" s="441" t="n">
-        <v>273672.1247265293</v>
+        <v>273672.1247265292</v>
       </c>
       <c r="DI100" s="368" t="n"/>
       <c r="DJ100" s="368" t="n"/>
@@ -23090,7 +23090,7 @@
         <v>39.62531155453372</v>
       </c>
       <c r="CA108" s="190" t="n">
-        <v>33.12007282619747</v>
+        <v>33.12007282619748</v>
       </c>
       <c r="CB108" s="198" t="n">
         <v>32.63877585077052</v>
@@ -23105,7 +23105,7 @@
         <v>39.62531155453372</v>
       </c>
       <c r="CF108" s="200" t="n">
-        <v>33.12007282619747</v>
+        <v>33.12007282619748</v>
       </c>
       <c r="CG108" s="201" t="n">
         <v>32.63877585077052</v>
@@ -23138,19 +23138,19 @@
         <v>2844</v>
       </c>
       <c r="CW108" s="199" t="n">
-        <v>0.6325076527118622</v>
+        <v>0.6325076527118648</v>
       </c>
       <c r="CX108" s="200" t="n">
-        <v>0.5588274414371717</v>
+        <v>0.5588274414371737</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>0.5575524490069852</v>
+        <v>0.5575524490069873</v>
       </c>
       <c r="CZ108" s="200" t="n">
-        <v>0.5519744899537801</v>
+        <v>0.5519744899537821</v>
       </c>
       <c r="DA108" s="201" t="n">
-        <v>0.539746239387339</v>
+        <v>0.5397462393873407</v>
       </c>
     </row>
     <row r="109">
@@ -23385,7 +23385,7 @@
         <v>33.13520019411237</v>
       </c>
       <c r="CA109" s="190" t="n">
-        <v>30.41392781311714</v>
+        <v>30.41392781311715</v>
       </c>
       <c r="CB109" s="198" t="n">
         <v>30.60683374054618</v>
@@ -23400,7 +23400,7 @@
         <v>33.13520019411237</v>
       </c>
       <c r="CF109" s="190" t="n">
-        <v>30.41392781311714</v>
+        <v>30.41392781311715</v>
       </c>
       <c r="CG109" s="198" t="n">
         <v>30.60683374054618</v>
@@ -23433,19 +23433,19 @@
         <v>6366</v>
       </c>
       <c r="CW109" s="197" t="n">
-        <v>0.09887116171637625</v>
+        <v>0.09887116171637669</v>
       </c>
       <c r="CX109" s="190" t="n">
-        <v>0.08086620964899183</v>
+        <v>0.08086620964899219</v>
       </c>
       <c r="CY109" s="190" t="n">
-        <v>0.0829405029737426</v>
+        <v>0.08294050297374299</v>
       </c>
       <c r="CZ109" s="190" t="n">
-        <v>0.08529935814310885</v>
+        <v>0.08529935814310928</v>
       </c>
       <c r="DA109" s="198" t="n">
-        <v>0.07434357734795088</v>
+        <v>0.07434357734795133</v>
       </c>
     </row>
     <row r="110">
@@ -23728,19 +23728,19 @@
         <v>10888</v>
       </c>
       <c r="CW110" s="197" t="n">
-        <v>0.07606313161696746</v>
+        <v>0.07606313161696947</v>
       </c>
       <c r="CX110" s="190" t="n">
-        <v>0.07577105569710546</v>
+        <v>0.07577105569710751</v>
       </c>
       <c r="CY110" s="190" t="n">
-        <v>0.07533927084492804</v>
+        <v>0.07533927084493029</v>
       </c>
       <c r="CZ110" s="190" t="n">
-        <v>0.07539709805878583</v>
+        <v>0.0753970980587883</v>
       </c>
       <c r="DA110" s="198" t="n">
-        <v>0.0749527373996228</v>
+        <v>0.07495273739962528</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" thickBot="1">
@@ -24023,19 +24023,19 @@
         <v>2178</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>0.00623418106180267</v>
+        <v>0.006234181061802625</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.006396145085788257</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>0.006590523934945409</v>
+        <v>0.006590523934945361</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760346054</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885872</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24061,7 +24061,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="H112" s="215" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="I112" s="215" t="n">
         <v>258.2717129066097</v>
@@ -24111,7 +24111,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="Y112" s="217" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="Z112" s="218" t="n">
         <v>258.2717129066097</v>
@@ -24173,7 +24173,7 @@
         <v>184.5460315779278</v>
       </c>
       <c r="AT112" s="208" t="n">
-        <v>184.1393065227</v>
+        <v>184.1393065227001</v>
       </c>
       <c r="AU112" s="207" t="n">
         <v>306.4692253853382</v>
@@ -24223,7 +24223,7 @@
         <v>184.5460315779278</v>
       </c>
       <c r="BK112" s="214" t="n">
-        <v>184.1393065227</v>
+        <v>184.1393065227001</v>
       </c>
       <c r="BL112" s="222" t="n">
         <v>306.4692253853382</v>
@@ -24318,19 +24318,19 @@
         <v>22276</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>0.8136761271070085</v>
+        <v>0.8136761271070136</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>0.7218608518690572</v>
+        <v>0.7218608518690617</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>0.7224227467606013</v>
+        <v>0.7224227467606059</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>0.7193951259160208</v>
+        <v>0.7193951259160257</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>0.6959031002607986</v>
+        <v>0.6959031002608032</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -25197,7 +25197,7 @@
         <v>0</v>
       </c>
       <c r="BX117" s="515" t="n">
-        <v>0.0637615035800784</v>
+        <v>0.06376150358007837</v>
       </c>
       <c r="BY117" s="461" t="n">
         <v>0</v>
@@ -25212,7 +25212,7 @@
         <v>0</v>
       </c>
       <c r="CC117" s="199" t="n">
-        <v>6.119676900831885</v>
+        <v>6.119676900831882</v>
       </c>
       <c r="CD117" s="200" t="n">
         <v>0</v>
@@ -25704,10 +25704,10 @@
         <v>0.1226153021746937</v>
       </c>
       <c r="BY119" s="461" t="n">
-        <v>0.0491208390524707</v>
+        <v>0.04912083905247068</v>
       </c>
       <c r="BZ119" s="461" t="n">
-        <v>0.07514744396219582</v>
+        <v>0.0751474439621958</v>
       </c>
       <c r="CA119" s="461" t="n">
         <v>0.1051194925474057</v>
@@ -25716,10 +25716,10 @@
         <v>0.1481374028113281</v>
       </c>
       <c r="CC119" s="197" t="n">
-        <v>14.27934975127427</v>
+        <v>14.27934975127428</v>
       </c>
       <c r="CD119" s="190" t="n">
-        <v>5.41840906430786</v>
+        <v>5.418409064307857</v>
       </c>
       <c r="CE119" s="190" t="n">
         <v>7.617414578501112</v>
@@ -26020,7 +26020,7 @@
         <v>0.2290284821556444</v>
       </c>
       <c r="M121" s="215" t="n">
-        <v>299.8251834757914</v>
+        <v>299.8251834757915</v>
       </c>
       <c r="N121" s="215" t="n">
         <v>258.3767770590746</v>
@@ -26070,7 +26070,7 @@
         <v>0.2290284821556444</v>
       </c>
       <c r="AD121" s="218" t="n">
-        <v>299.8251834757914</v>
+        <v>299.8251834757915</v>
       </c>
       <c r="AE121" s="218" t="n">
         <v>258.3767770590746</v>
@@ -26205,25 +26205,25 @@
         <v>15.05560425447307</v>
       </c>
       <c r="BX121" s="466" t="n">
-        <v>0.08073335857661967</v>
+        <v>0.08073335857661966</v>
       </c>
       <c r="BY121" s="467" t="n">
-        <v>0.0207761701658156</v>
+        <v>0.02077617016581559</v>
       </c>
       <c r="BZ121" s="467" t="n">
-        <v>0.03870161400865597</v>
+        <v>0.03870161400865596</v>
       </c>
       <c r="CA121" s="467" t="n">
         <v>0.05766731015337993</v>
       </c>
       <c r="CB121" s="468" t="n">
-        <v>0.08106838078708534</v>
+        <v>0.08106838078708532</v>
       </c>
       <c r="CC121" s="212" t="n">
-        <v>24.3735728873113</v>
+        <v>24.37357288731129</v>
       </c>
       <c r="CD121" s="212" t="n">
-        <v>5.41840906430786</v>
+        <v>5.418409064307857</v>
       </c>
       <c r="CE121" s="212" t="n">
         <v>7.617414578501112</v>
@@ -27923,7 +27923,7 @@
         <v>0.08911974768298138</v>
       </c>
       <c r="M130" s="495" t="n">
-        <v>0.01762997011581366</v>
+        <v>0.01762997011581365</v>
       </c>
       <c r="N130" s="495" t="n">
         <v>0.02604799752893461</v>
@@ -27973,7 +27973,7 @@
         <v>0.08911974768298138</v>
       </c>
       <c r="AD130" s="498" t="n">
-        <v>0.01762997011581366</v>
+        <v>0.01762997011581365</v>
       </c>
       <c r="AE130" s="498" t="n">
         <v>0.02604799752893461</v>
@@ -28017,10 +28017,10 @@
         <v>0.06486477924766289</v>
       </c>
       <c r="AS130" s="501" t="n">
-        <v>0.08487377617971927</v>
+        <v>0.08487377617971928</v>
       </c>
       <c r="AT130" s="502" t="n">
-        <v>0.08844011763846212</v>
+        <v>0.0884401176384621</v>
       </c>
       <c r="AU130" s="501" t="n">
         <v>0.01755729915518768</v>
@@ -28032,7 +28032,7 @@
         <v>0.06417494373955945</v>
       </c>
       <c r="AX130" s="501" t="n">
-        <v>0.0839538126416958</v>
+        <v>0.08395381264169581</v>
       </c>
       <c r="AY130" s="502" t="n">
         <v>0.08730633919542499</v>
@@ -28067,10 +28067,10 @@
         <v>0.06486477924766289</v>
       </c>
       <c r="BJ130" s="504" t="n">
-        <v>0.08487377617971927</v>
+        <v>0.08487377617971928</v>
       </c>
       <c r="BK130" s="505" t="n">
-        <v>0.08844011763846212</v>
+        <v>0.0884401176384621</v>
       </c>
       <c r="BL130" s="504" t="n">
         <v>0.01755729915518768</v>
@@ -28082,7 +28082,7 @@
         <v>0.06417494373955945</v>
       </c>
       <c r="BO130" s="504" t="n">
-        <v>0.0839538126416958</v>
+        <v>0.08395381264169581</v>
       </c>
       <c r="BP130" s="505" t="n">
         <v>0.08730633919542499</v>
@@ -28114,7 +28114,7 @@
         <v>0.02581229457357406</v>
       </c>
       <c r="BZ130" s="504" t="n">
-        <v>0.06395446060673496</v>
+        <v>0.06395446060673494</v>
       </c>
       <c r="CA130" s="504" t="n">
         <v>0.08365538593373106</v>
@@ -30305,7 +30305,7 @@
         <v>23699.58807988908</v>
       </c>
       <c r="BV146" s="375" t="n">
-        <v>17508.43584393735</v>
+        <v>17508.43584393736</v>
       </c>
       <c r="BW146" s="392" t="n">
         <v>15991.02151418759</v>
@@ -30326,19 +30326,19 @@
         <v>489.9393772395445</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>471.5664447721919</v>
+        <v>471.5664447721938</v>
       </c>
       <c r="CX146" s="512" t="n">
-        <v>447.1539032149585</v>
+        <v>447.1539032149601</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>475.8887582186936</v>
+        <v>475.8887582186954</v>
       </c>
       <c r="CZ146" s="512" t="n">
-        <v>501.0331779117008</v>
+        <v>501.0331779117026</v>
       </c>
       <c r="DA146" s="513" t="n">
-        <v>529.4650754932184</v>
+        <v>529.46507549322</v>
       </c>
     </row>
     <row r="147">
@@ -30491,7 +30491,7 @@
         <v>108589.2921092424</v>
       </c>
       <c r="BT147" s="375" t="n">
-        <v>78890.61125020419</v>
+        <v>78890.61125020418</v>
       </c>
       <c r="BU147" s="375" t="n">
         <v>49657.28648951092</v>
@@ -30518,19 +30518,19 @@
         <v>1543.329831969467</v>
       </c>
       <c r="CW147" s="391" t="n">
-        <v>209.089063316188</v>
+        <v>209.089063316189</v>
       </c>
       <c r="CX147" s="375" t="n">
-        <v>182.3742324386158</v>
+        <v>182.3742324386166</v>
       </c>
       <c r="CY147" s="375" t="n">
-        <v>197.8808137627532</v>
+        <v>197.8808137627541</v>
       </c>
       <c r="CZ147" s="375" t="n">
-        <v>215.3422933026861</v>
+        <v>215.3422933026872</v>
       </c>
       <c r="DA147" s="392" t="n">
-        <v>199.1713192850336</v>
+        <v>199.1713192850348</v>
       </c>
     </row>
     <row r="148">
@@ -30701,7 +30701,7 @@
         <v>945.2241020431043</v>
       </c>
       <c r="BZ148" s="372" t="n">
-        <v>933.7315448160737</v>
+        <v>933.7315448160736</v>
       </c>
       <c r="CA148" s="372" t="n">
         <v>1028.228235052464</v>
@@ -30710,19 +30710,19 @@
         <v>1106.234747135651</v>
       </c>
       <c r="CW148" s="391" t="n">
-        <v>157.1403271775087</v>
+        <v>157.1403271775129</v>
       </c>
       <c r="CX148" s="375" t="n">
-        <v>166.7242339994669</v>
+        <v>166.7242339994714</v>
       </c>
       <c r="CY148" s="375" t="n">
-        <v>181.568669102008</v>
+        <v>181.5686691020134</v>
       </c>
       <c r="CZ148" s="375" t="n">
-        <v>207.8100408830747</v>
+        <v>207.8100408830815</v>
       </c>
       <c r="DA148" s="392" t="n">
-        <v>221.9844993945709</v>
+        <v>221.9844993945782</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" thickBot="1">
@@ -30902,19 +30902,19 @@
         <v>26563.90922549893</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>117.1118499841886</v>
+        <v>117.1118499841878</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>16.66360582296741</v>
+        <v>16.66360582296729</v>
       </c>
       <c r="CY149" s="420" t="n">
-        <v>18.02852008769406</v>
+        <v>18.02852008769393</v>
       </c>
       <c r="CZ149" s="420" t="n">
-        <v>19.31384565002039</v>
+        <v>19.31384565002025</v>
       </c>
       <c r="DA149" s="421" t="n">
-        <v>20.69080559165297</v>
+        <v>20.69080559165283</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" thickBot="1">
@@ -30939,7 +30939,7 @@
         <v>711031.5138816028</v>
       </c>
       <c r="H150" s="427" t="n">
-        <v>3049.699233174205</v>
+        <v>3049.699233174204</v>
       </c>
       <c r="I150" s="427" t="n">
         <v>3395.734214293858</v>
@@ -30974,7 +30974,7 @@
         <v>711031.5138816028</v>
       </c>
       <c r="Y150" s="432" t="n">
-        <v>3049.699233174205</v>
+        <v>3049.699233174204</v>
       </c>
       <c r="Z150" s="433" t="n">
         <v>3395.734214293858</v>
@@ -31021,7 +31021,7 @@
         <v>3688.333869463637</v>
       </c>
       <c r="AT150" s="438" t="n">
-        <v>3876.857014318611</v>
+        <v>3876.85701431861</v>
       </c>
       <c r="BA150" s="155" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>3688.333869463637</v>
       </c>
       <c r="BK150" s="444" t="n">
-        <v>3876.857014318611</v>
+        <v>3876.85701431861</v>
       </c>
       <c r="BR150" s="155" t="inlineStr">
         <is>
@@ -31094,19 +31094,19 @@
         <v>3895.613624696012</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>954.9076852500772</v>
+        <v>954.9076852500834</v>
       </c>
       <c r="CX150" s="420" t="n">
-        <v>812.9159754760085</v>
+        <v>812.9159754760153</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>873.3667611711488</v>
+        <v>873.3667611711569</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>943.4993577474819</v>
+        <v>943.4993577474916</v>
       </c>
       <c r="DA150" s="421" t="n">
-        <v>971.3116997644759</v>
+        <v>971.3116997644859</v>
       </c>
     </row>
     <row r="151">
@@ -34859,7 +34859,7 @@
         <v>80.66001811726784</v>
       </c>
       <c r="CB174" s="198" t="n">
-        <v>84.70726796324807</v>
+        <v>84.70726796324806</v>
       </c>
       <c r="CC174" s="197" t="n">
         <v>92.85966563013208</v>
@@ -34874,7 +34874,7 @@
         <v>137.0400037672678</v>
       </c>
       <c r="CG174" s="198" t="n">
-        <v>152.1078123702481</v>
+        <v>152.107812370248</v>
       </c>
       <c r="CI174" s="197" t="n">
         <v>0</v>
@@ -38461,13 +38461,13 @@
         <v>128.501482714</v>
       </c>
       <c r="AP190" s="194" t="n">
-        <v>152.7460378582457</v>
+        <v>152.7460378582458</v>
       </c>
       <c r="AQ190" s="179" t="n">
         <v>139.1138089017757</v>
       </c>
       <c r="AR190" s="179" t="n">
-        <v>135.4621367577627</v>
+        <v>135.4621367577628</v>
       </c>
       <c r="AS190" s="179" t="n">
         <v>129.9212678290772</v>
@@ -38476,19 +38476,19 @@
         <v>122.7006859698305</v>
       </c>
       <c r="AU190" s="190" t="n">
-        <v>168.5530568454999</v>
+        <v>168.5530568455</v>
       </c>
       <c r="AV190" s="190" t="n">
         <v>193.5721394432552</v>
       </c>
       <c r="AW190" s="190" t="n">
-        <v>233.2377229516892</v>
+        <v>233.2377229516894</v>
       </c>
       <c r="AX190" s="190" t="n">
         <v>244.5502230780748</v>
       </c>
       <c r="AY190" s="196" t="n">
-        <v>251.2021686833874</v>
+        <v>251.2021686833873</v>
       </c>
       <c r="BA190" s="83" t="inlineStr">
         <is>
@@ -38511,13 +38511,13 @@
         <v>128.501482714</v>
       </c>
       <c r="BG190" s="197" t="n">
-        <v>152.7460378582457</v>
+        <v>152.7460378582458</v>
       </c>
       <c r="BH190" s="190" t="n">
         <v>139.1138089017757</v>
       </c>
       <c r="BI190" s="190" t="n">
-        <v>135.4621367577627</v>
+        <v>135.4621367577628</v>
       </c>
       <c r="BJ190" s="190" t="n">
         <v>129.9212678290772</v>
@@ -38526,13 +38526,13 @@
         <v>122.7006859698305</v>
       </c>
       <c r="BL190" s="199" t="n">
-        <v>168.5530568452457</v>
+        <v>168.5530568452458</v>
       </c>
       <c r="BM190" s="200" t="n">
-        <v>193.5721394427758</v>
+        <v>193.5721394427757</v>
       </c>
       <c r="BN190" s="200" t="n">
-        <v>233.2377229517627</v>
+        <v>233.2377229517628</v>
       </c>
       <c r="BO190" s="200" t="n">
         <v>244.5502230780772</v>
@@ -38561,34 +38561,34 @@
         <v>126.994269702</v>
       </c>
       <c r="BX190" s="197" t="n">
-        <v>152.4525594531149</v>
+        <v>152.452559453115</v>
       </c>
       <c r="BY190" s="190" t="n">
         <v>139.1356978786664</v>
       </c>
       <c r="BZ190" s="190" t="n">
-        <v>135.8375352005598</v>
+        <v>135.83753520056</v>
       </c>
       <c r="CA190" s="190" t="n">
         <v>130.5920444545107</v>
       </c>
       <c r="CB190" s="198" t="n">
-        <v>123.6681527425453</v>
+        <v>123.6681527425452</v>
       </c>
       <c r="CC190" s="199" t="n">
-        <v>167.9224723261149</v>
+        <v>167.922472326115</v>
       </c>
       <c r="CD190" s="200" t="n">
         <v>193.0133120016664</v>
       </c>
       <c r="CE190" s="200" t="n">
-        <v>232.6801705025599</v>
+        <v>232.68017050256</v>
       </c>
       <c r="CF190" s="200" t="n">
         <v>243.9982485885107</v>
       </c>
       <c r="CG190" s="201" t="n">
-        <v>250.6624224445453</v>
+        <v>250.6624224445452</v>
       </c>
       <c r="CI190" s="199" t="n">
         <v>0</v>
@@ -38618,34 +38618,34 @@
         <v>4473</v>
       </c>
       <c r="CW190" s="91" t="n">
-        <v>0.6305845188212781</v>
+        <v>0.6305845188212807</v>
       </c>
       <c r="CX190" s="92" t="n">
-        <v>0.5588274414376452</v>
+        <v>0.5588274414376472</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>0.5575524490099095</v>
+        <v>0.5575524490099116</v>
       </c>
       <c r="CZ190" s="92" t="n">
-        <v>0.5519744899569327</v>
+        <v>0.5519744899569347</v>
       </c>
       <c r="DA190" s="93" t="n">
-        <v>0.539746239388267</v>
+        <v>0.5397462393882688</v>
       </c>
       <c r="DC190" s="393" t="n">
-        <v>0.003727999126343933</v>
+        <v>0.00372799912634393</v>
       </c>
       <c r="DD190" s="394" t="n">
         <v>0.003650943499103835</v>
       </c>
       <c r="DE190" s="394" t="n">
-        <v>0.003733252168925715</v>
+        <v>0.003733252168925711</v>
       </c>
       <c r="DF190" s="394" t="n">
         <v>0.003868615951756972</v>
       </c>
       <c r="DG190" s="395" t="n">
-        <v>0.004025408043775216</v>
+        <v>0.004025408043775219</v>
       </c>
     </row>
     <row r="191">
@@ -38770,16 +38770,16 @@
         <v>79.835566996</v>
       </c>
       <c r="AP191" s="194" t="n">
-        <v>81.59394147686064</v>
+        <v>81.59394147686066</v>
       </c>
       <c r="AQ191" s="179" t="n">
-        <v>79.63781580564707</v>
+        <v>79.63781580564705</v>
       </c>
       <c r="AR191" s="179" t="n">
-        <v>81.97142012176491</v>
+        <v>81.97142012176488</v>
       </c>
       <c r="AS191" s="179" t="n">
-        <v>85.14011399953931</v>
+        <v>85.14011399953935</v>
       </c>
       <c r="AT191" s="195" t="n">
         <v>87.91333277020929</v>
@@ -38791,10 +38791,10 @@
         <v>129.2203678213853</v>
       </c>
       <c r="AW191" s="190" t="n">
-        <v>149.8048056361101</v>
+        <v>149.80480563611</v>
       </c>
       <c r="AX191" s="190" t="n">
-        <v>159.6116553915465</v>
+        <v>159.6116553915466</v>
       </c>
       <c r="AY191" s="196" t="n">
         <v>167.7488997663571</v>
@@ -38820,31 +38820,31 @@
         <v>79.835566996</v>
       </c>
       <c r="BG191" s="197" t="n">
-        <v>81.59394147686064</v>
+        <v>81.59394147686066</v>
       </c>
       <c r="BH191" s="190" t="n">
-        <v>79.63781580564707</v>
+        <v>79.63781580564705</v>
       </c>
       <c r="BI191" s="190" t="n">
-        <v>81.97142012176491</v>
+        <v>81.97142012176488</v>
       </c>
       <c r="BJ191" s="190" t="n">
-        <v>85.14011399953931</v>
+        <v>85.14011399953935</v>
       </c>
       <c r="BK191" s="198" t="n">
         <v>87.91333277020929</v>
       </c>
       <c r="BL191" s="197" t="n">
-        <v>108.7018404878606</v>
+        <v>108.7018404878607</v>
       </c>
       <c r="BM191" s="190" t="n">
-        <v>129.2203678216471</v>
+        <v>129.220367821647</v>
       </c>
       <c r="BN191" s="190" t="n">
         <v>149.8048056357649</v>
       </c>
       <c r="BO191" s="190" t="n">
-        <v>159.6116553915393</v>
+        <v>159.6116553915394</v>
       </c>
       <c r="BP191" s="198" t="n">
         <v>167.7488997662093</v>
@@ -38870,22 +38870,22 @@
         <v>78.82907359699999</v>
       </c>
       <c r="BX191" s="197" t="n">
-        <v>81.71417618742456</v>
+        <v>81.71417618742458</v>
       </c>
       <c r="BY191" s="190" t="n">
-        <v>79.94461069946266</v>
+        <v>79.94461069946264</v>
       </c>
       <c r="BZ191" s="190" t="n">
-        <v>82.48769884133461</v>
+        <v>82.48769884133458</v>
       </c>
       <c r="CA191" s="190" t="n">
-        <v>85.85287291835388</v>
+        <v>85.85287291835392</v>
       </c>
       <c r="CB191" s="198" t="n">
         <v>88.84548259145757</v>
       </c>
       <c r="CC191" s="197" t="n">
-        <v>108.6046715174245</v>
+        <v>108.6046715174246</v>
       </c>
       <c r="CD191" s="190" t="n">
         <v>129.1395016124627</v>
@@ -38927,22 +38927,22 @@
         <v>7774</v>
       </c>
       <c r="CW191" s="102" t="n">
-        <v>0.09716897041179687</v>
+        <v>0.09716897041179728</v>
       </c>
       <c r="CX191" s="103" t="n">
-        <v>0.08086620964934652</v>
+        <v>0.08086620964934688</v>
       </c>
       <c r="CY191" s="103" t="n">
-        <v>0.08294050297335381</v>
+        <v>0.0829405029733542</v>
       </c>
       <c r="CZ191" s="103" t="n">
-        <v>0.08529935814312077</v>
+        <v>0.0852993581431212</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>0.07434357734897762</v>
+        <v>0.07434357734897806</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.000897498562829492</v>
+        <v>0.000897498562829491</v>
       </c>
       <c r="DD191" s="397" t="n">
         <v>0.000757009318203595</v>
@@ -38951,7 +38951,7 @@
         <v>0.00073806262958656</v>
       </c>
       <c r="DF191" s="397" t="n">
-        <v>0.000713514308280145</v>
+        <v>0.000713514308280144</v>
       </c>
       <c r="DG191" s="398" t="n">
         <v>0.000554165033420904</v>
@@ -39079,25 +39079,25 @@
         <v>68.313640998</v>
       </c>
       <c r="AP192" s="194" t="n">
-        <v>76.38910727404406</v>
+        <v>76.38910727404416</v>
       </c>
       <c r="AQ192" s="179" t="n">
-        <v>79.19668896951387</v>
+        <v>79.19668896951396</v>
       </c>
       <c r="AR192" s="179" t="n">
-        <v>81.76962101062624</v>
+        <v>81.76962101062622</v>
       </c>
       <c r="AS192" s="179" t="n">
         <v>80.04983821064684</v>
       </c>
       <c r="AT192" s="195" t="n">
-        <v>83.86912411019696</v>
+        <v>83.86912411019695</v>
       </c>
       <c r="AU192" s="190" t="n">
-        <v>92.93505310856983</v>
+        <v>92.93505310856993</v>
       </c>
       <c r="AV192" s="190" t="n">
-        <v>107.802848145305</v>
+        <v>107.8028481453051</v>
       </c>
       <c r="AW192" s="190" t="n">
         <v>126.08801898962</v>
@@ -39129,25 +39129,25 @@
         <v>68.313640998</v>
       </c>
       <c r="BG192" s="197" t="n">
-        <v>76.38910727404406</v>
+        <v>76.38910727404416</v>
       </c>
       <c r="BH192" s="190" t="n">
-        <v>79.19668896951387</v>
+        <v>79.19668896951396</v>
       </c>
       <c r="BI192" s="190" t="n">
-        <v>81.76962101062624</v>
+        <v>81.76962101062622</v>
       </c>
       <c r="BJ192" s="190" t="n">
         <v>80.04983821064684</v>
       </c>
       <c r="BK192" s="198" t="n">
-        <v>83.86912411019696</v>
+        <v>83.86912411019695</v>
       </c>
       <c r="BL192" s="197" t="n">
-        <v>92.93505310904406</v>
+        <v>92.93505310904416</v>
       </c>
       <c r="BM192" s="190" t="n">
-        <v>107.8028481455139</v>
+        <v>107.802848145514</v>
       </c>
       <c r="BN192" s="190" t="n">
         <v>126.0880189896262</v>
@@ -39156,7 +39156,7 @@
         <v>137.1154008646468</v>
       </c>
       <c r="BP192" s="198" t="n">
-        <v>152.182765108197</v>
+        <v>152.1827651081969</v>
       </c>
       <c r="BR192" s="111" t="inlineStr">
         <is>
@@ -39179,25 +39179,25 @@
         <v>67.400544407</v>
       </c>
       <c r="BX192" s="197" t="n">
-        <v>76.49958990117621</v>
+        <v>76.49958990117631</v>
       </c>
       <c r="BY192" s="190" t="n">
-        <v>79.44432645825329</v>
+        <v>79.44432645825337</v>
       </c>
       <c r="BZ192" s="190" t="n">
-        <v>82.19863381573984</v>
+        <v>82.19863381573983</v>
       </c>
       <c r="CA192" s="190" t="n">
         <v>80.66001811691197</v>
       </c>
       <c r="CB192" s="198" t="n">
-        <v>84.70726796344701</v>
+        <v>84.70726796344698</v>
       </c>
       <c r="CC192" s="197" t="n">
-        <v>92.85966563017621</v>
+        <v>92.85966563017631</v>
       </c>
       <c r="CD192" s="190" t="n">
-        <v>107.7270770902533</v>
+        <v>107.7270770902534</v>
       </c>
       <c r="CE192" s="190" t="n">
         <v>126.0126797187398</v>
@@ -39236,25 +39236,25 @@
         <v>4927</v>
       </c>
       <c r="CW192" s="102" t="n">
-        <v>0.07538747908594198</v>
+        <v>0.07538747908594384</v>
       </c>
       <c r="CX192" s="103" t="n">
-        <v>0.07577105569712549</v>
+        <v>0.07577105569712757</v>
       </c>
       <c r="CY192" s="103" t="n">
-        <v>0.0753392708449033</v>
+        <v>0.07533927084490553</v>
       </c>
       <c r="CZ192" s="103" t="n">
-        <v>0.07539709805810332</v>
+        <v>0.07539709805810581</v>
       </c>
       <c r="DA192" s="104" t="n">
-        <v>0.0749527373991361</v>
+        <v>0.07495273739913856</v>
       </c>
       <c r="DC192" s="396" t="n">
-        <v>0.000878118133025285</v>
+        <v>0.000878118133025283</v>
       </c>
       <c r="DD192" s="397" t="n">
-        <v>0.000838943494900306</v>
+        <v>0.000838943494900305</v>
       </c>
       <c r="DE192" s="397" t="n">
         <v>0.000795955228085786</v>
@@ -39388,34 +39388,34 @@
         <v>0</v>
       </c>
       <c r="AP193" s="206" t="n">
-        <v>3.005182788725762</v>
+        <v>3.005182788725758</v>
       </c>
       <c r="AQ193" s="207" t="n">
-        <v>2.227141504817265</v>
+        <v>2.227141504817268</v>
       </c>
       <c r="AR193" s="207" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="AS193" s="207" t="n">
-        <v>2.341363372665477</v>
+        <v>2.341363372665473</v>
       </c>
       <c r="AT193" s="208" t="n">
-        <v>2.38884622186313</v>
+        <v>2.388846221863133</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>3.005182788725762</v>
+        <v>3.005182788725758</v>
       </c>
       <c r="AV193" s="209" t="n">
-        <v>2.227141504817265</v>
+        <v>2.227141504817268</v>
       </c>
       <c r="AW193" s="209" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="AX193" s="209" t="n">
-        <v>2.341363372665477</v>
+        <v>2.341363372665473</v>
       </c>
       <c r="AY193" s="210" t="n">
-        <v>2.38884622186313</v>
+        <v>2.388846221863133</v>
       </c>
       <c r="BA193" s="111" t="inlineStr">
         <is>
@@ -39438,34 +39438,34 @@
         <v>0</v>
       </c>
       <c r="BG193" s="211" t="n">
-        <v>3.005182788725762</v>
+        <v>3.005182788725758</v>
       </c>
       <c r="BH193" s="212" t="n">
-        <v>2.227141504817265</v>
+        <v>2.227141504817268</v>
       </c>
       <c r="BI193" s="212" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="BJ193" s="212" t="n">
-        <v>2.341363372665477</v>
+        <v>2.341363372665473</v>
       </c>
       <c r="BK193" s="213" t="n">
-        <v>2.38884622186313</v>
+        <v>2.388846221863133</v>
       </c>
       <c r="BL193" s="212" t="n">
-        <v>3.005182788725762</v>
+        <v>3.005182788725758</v>
       </c>
       <c r="BM193" s="212" t="n">
-        <v>2.227141504817265</v>
+        <v>2.227141504817268</v>
       </c>
       <c r="BN193" s="212" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="BO193" s="212" t="n">
-        <v>2.341363372665477</v>
+        <v>2.341363372665473</v>
       </c>
       <c r="BP193" s="213" t="n">
-        <v>2.38884622186313</v>
+        <v>2.388846221863133</v>
       </c>
       <c r="BR193" s="111" t="inlineStr">
         <is>
@@ -39488,34 +39488,34 @@
         <v>0</v>
       </c>
       <c r="BX193" s="211" t="n">
-        <v>2.998948607663959</v>
+        <v>2.998948607663956</v>
       </c>
       <c r="BY193" s="212" t="n">
-        <v>2.220745359731477</v>
+        <v>2.22074535973148</v>
       </c>
       <c r="BZ193" s="212" t="n">
         <v>2.288233811213716</v>
       </c>
       <c r="CA193" s="212" t="n">
-        <v>2.334639192905131</v>
+        <v>2.334639192905127</v>
       </c>
       <c r="CB193" s="213" t="n">
-        <v>2.381985675737244</v>
+        <v>2.381985675737247</v>
       </c>
       <c r="CC193" s="212" t="n">
-        <v>2.998948607663959</v>
+        <v>2.998948607663956</v>
       </c>
       <c r="CD193" s="212" t="n">
-        <v>2.220745359731477</v>
+        <v>2.22074535973148</v>
       </c>
       <c r="CE193" s="212" t="n">
         <v>2.288233811213716</v>
       </c>
       <c r="CF193" s="212" t="n">
-        <v>2.334639192905131</v>
+        <v>2.334639192905127</v>
       </c>
       <c r="CG193" s="213" t="n">
-        <v>2.381985675737244</v>
+        <v>2.381985675737247</v>
       </c>
       <c r="CI193" s="211" t="n">
         <v>0</v>
@@ -39545,19 +39545,19 @@
         <v>360</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>0.006234181061802671</v>
+        <v>0.006234181061802626</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.006396145085788257</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.00659052393494536</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760346054</v>
       </c>
       <c r="DA193" s="134" t="n">
-        <v>0.006860546125885923</v>
+        <v>0.006860546125885872</v>
       </c>
       <c r="DC193" s="422" t="n">
         <v>0</v>
@@ -39697,25 +39697,25 @@
         <v>276.650690708</v>
       </c>
       <c r="AP194" s="206" t="n">
-        <v>313.7342693978762</v>
+        <v>313.7342693978764</v>
       </c>
       <c r="AQ194" s="207" t="n">
-        <v>300.1754551817539</v>
+        <v>300.175455181754</v>
       </c>
       <c r="AR194" s="207" t="n">
-        <v>301.4980022253025</v>
+        <v>301.4980022253026</v>
       </c>
       <c r="AS194" s="207" t="n">
         <v>297.4525834119289</v>
       </c>
       <c r="AT194" s="208" t="n">
-        <v>296.8719890721</v>
+        <v>296.8719890720998</v>
       </c>
       <c r="AU194" s="207" t="n">
-        <v>373.1951332305628</v>
+        <v>373.195133230563</v>
       </c>
       <c r="AV194" s="207" t="n">
-        <v>432.8224969147627</v>
+        <v>432.8224969147628</v>
       </c>
       <c r="AW194" s="207" t="n">
         <v>511.425371912568</v>
@@ -39724,7 +39724,7 @@
         <v>543.6186427065202</v>
       </c>
       <c r="AY194" s="208" t="n">
-        <v>573.5226797797417</v>
+        <v>573.5226797797416</v>
       </c>
       <c r="BA194" s="155" t="inlineStr">
         <is>
@@ -39747,22 +39747,22 @@
         <v>276.650690708</v>
       </c>
       <c r="BG194" s="221" t="n">
-        <v>313.7342693978762</v>
+        <v>313.7342693978764</v>
       </c>
       <c r="BH194" s="222" t="n">
-        <v>300.1754551817539</v>
+        <v>300.175455181754</v>
       </c>
       <c r="BI194" s="222" t="n">
-        <v>301.4980022253025</v>
+        <v>301.4980022253026</v>
       </c>
       <c r="BJ194" s="222" t="n">
         <v>297.4525834119289</v>
       </c>
       <c r="BK194" s="214" t="n">
-        <v>296.8719890721</v>
+        <v>296.8719890720998</v>
       </c>
       <c r="BL194" s="222" t="n">
-        <v>373.1951332308761</v>
+        <v>373.1951332308764</v>
       </c>
       <c r="BM194" s="222" t="n">
         <v>432.822496914754</v>
@@ -39774,7 +39774,7 @@
         <v>543.6186427069289</v>
       </c>
       <c r="BP194" s="214" t="n">
-        <v>573.5226797800999</v>
+        <v>573.5226797800998</v>
       </c>
       <c r="BR194" s="155" t="inlineStr">
         <is>
@@ -39797,34 +39797,34 @@
         <v>273.223887706</v>
       </c>
       <c r="BX194" s="221" t="n">
-        <v>313.6652741493796</v>
+        <v>313.6652741493799</v>
       </c>
       <c r="BY194" s="222" t="n">
         <v>300.7453803961139</v>
       </c>
       <c r="BZ194" s="222" t="n">
-        <v>302.812101668848</v>
+        <v>302.8121016688481</v>
       </c>
       <c r="CA194" s="222" t="n">
         <v>299.4395746826817</v>
       </c>
       <c r="CB194" s="214" t="n">
-        <v>299.6028889731871</v>
+        <v>299.602888973187</v>
       </c>
       <c r="CC194" s="222" t="n">
-        <v>372.3857580813796</v>
+        <v>372.3857580813798</v>
       </c>
       <c r="CD194" s="222" t="n">
-        <v>432.1006360641138</v>
+        <v>432.1006360641139</v>
       </c>
       <c r="CE194" s="222" t="n">
-        <v>510.702949164848</v>
+        <v>510.7029491648481</v>
       </c>
       <c r="CF194" s="222" t="n">
         <v>542.8992475816817</v>
       </c>
       <c r="CG194" s="214" t="n">
-        <v>572.8267766791871</v>
+        <v>572.826776679187</v>
       </c>
       <c r="CI194" s="349" t="n">
         <v>0</v>
@@ -39854,19 +39854,19 @@
         <v>17534</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>0.8093751493808197</v>
+        <v>0.8093751493808246</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>0.7218608518699055</v>
+        <v>0.7218608518699099</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>0.722422746763112</v>
+        <v>0.7224227467631168</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>0.7193951259185029</v>
+        <v>0.7193951259185077</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>0.6959031002622666</v>
+        <v>0.6959031002622713</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40822,13 +40822,13 @@
         <v>0.006</v>
       </c>
       <c r="AP199" s="233" t="n">
-        <v>0.3371061136909998</v>
+        <v>0.337106113691</v>
       </c>
       <c r="AQ199" s="190" t="n">
-        <v>0.5807164183297657</v>
+        <v>0.5807164183297656</v>
       </c>
       <c r="AR199" s="190" t="n">
-        <v>0.9329508918067571</v>
+        <v>0.9329508918067575</v>
       </c>
       <c r="AS199" s="190" t="n">
         <v>1.222751115390374</v>
@@ -40837,19 +40837,19 @@
         <v>1.507213012100324</v>
       </c>
       <c r="AU199" s="190" t="n">
-        <v>153.0831439719367</v>
+        <v>153.0831439719368</v>
       </c>
       <c r="AV199" s="190" t="n">
         <v>139.6945253201055</v>
       </c>
       <c r="AW199" s="190" t="n">
-        <v>136.3950876495695</v>
+        <v>136.3950876495696</v>
       </c>
       <c r="AX199" s="190" t="n">
         <v>131.1440189444676</v>
       </c>
       <c r="AY199" s="196" t="n">
-        <v>124.2078989819309</v>
+        <v>124.2078989819308</v>
       </c>
       <c r="BA199" s="83" t="inlineStr">
         <is>
@@ -40872,13 +40872,13 @@
         <v>0.006</v>
       </c>
       <c r="BG199" s="197" t="n">
-        <v>0.3371061136904914</v>
+        <v>0.3371061136904916</v>
       </c>
       <c r="BH199" s="190" t="n">
         <v>0.5807164183283272</v>
       </c>
       <c r="BI199" s="190" t="n">
-        <v>0.9329508918070508</v>
+        <v>0.9329508918070513</v>
       </c>
       <c r="BJ199" s="190" t="n">
         <v>1.222751115390386</v>
@@ -40887,19 +40887,19 @@
         <v>1.507213012102983</v>
       </c>
       <c r="BL199" s="199" t="n">
-        <v>153.0831439719362</v>
+        <v>153.0831439719363</v>
       </c>
       <c r="BM199" s="200" t="n">
-        <v>139.6945253201041</v>
+        <v>139.694525320104</v>
       </c>
       <c r="BN199" s="200" t="n">
-        <v>136.3950876495697</v>
+        <v>136.3950876495699</v>
       </c>
       <c r="BO199" s="200" t="n">
         <v>131.1440189444676</v>
       </c>
       <c r="BP199" s="201" t="n">
-        <v>124.2078989819335</v>
+        <v>124.2078989819334</v>
       </c>
       <c r="BR199" s="83" t="inlineStr">
         <is>
@@ -40922,34 +40922,34 @@
         <v>45.51792185462426</v>
       </c>
       <c r="BX199" s="462" t="n">
-        <v>0.4511414436917206</v>
+        <v>0.4511414436917203</v>
       </c>
       <c r="BY199" s="463" t="n">
         <v>0.4025462998827071</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>0.4084440298900073</v>
+        <v>0.408444029890007</v>
       </c>
       <c r="CA199" s="463" t="n">
         <v>0.3918221554489027</v>
       </c>
       <c r="CB199" s="464" t="n">
-        <v>0.3682217377497506</v>
+        <v>0.3682217377497508</v>
       </c>
       <c r="CC199" s="199" t="n">
         <v>68.77766776617612</v>
       </c>
       <c r="CD199" s="200" t="n">
-        <v>56.00856036265539</v>
+        <v>56.00856036265538</v>
       </c>
       <c r="CE199" s="200" t="n">
-        <v>55.48203028764238</v>
+        <v>55.48203028764239</v>
       </c>
       <c r="CF199" s="200" t="n">
         <v>51.16885634264531</v>
       </c>
       <c r="CG199" s="201" t="n">
-        <v>45.5373021071616</v>
+        <v>45.53730210716159</v>
       </c>
       <c r="CI199" s="396" t="n">
         <v>0.9999999999992563</v>
@@ -41135,31 +41135,31 @@
         <v>0.006</v>
       </c>
       <c r="AP200" s="233" t="n">
-        <v>0.2174036809755345</v>
+        <v>0.2174036809755346</v>
       </c>
       <c r="AQ200" s="190" t="n">
         <v>0.3876611034641558</v>
       </c>
       <c r="AR200" s="190" t="n">
-        <v>0.5992192225444403</v>
+        <v>0.59921922254444</v>
       </c>
       <c r="AS200" s="190" t="n">
-        <v>0.7980582769577328</v>
+        <v>0.7980582769577329</v>
       </c>
       <c r="AT200" s="196" t="n">
         <v>1.006493398598143</v>
       </c>
       <c r="AU200" s="190" t="n">
-        <v>81.81134515783617</v>
+        <v>81.8113451578362</v>
       </c>
       <c r="AV200" s="190" t="n">
-        <v>80.02547690911122</v>
+        <v>80.02547690911121</v>
       </c>
       <c r="AW200" s="190" t="n">
-        <v>82.57063934430934</v>
+        <v>82.57063934430931</v>
       </c>
       <c r="AX200" s="190" t="n">
-        <v>85.93817227649704</v>
+        <v>85.93817227649708</v>
       </c>
       <c r="AY200" s="196" t="n">
         <v>88.91982616880743</v>
@@ -41188,28 +41188,28 @@
         <v>0.2174036809757213</v>
       </c>
       <c r="BH200" s="190" t="n">
-        <v>0.3876611034649412</v>
+        <v>0.3876611034649411</v>
       </c>
       <c r="BI200" s="190" t="n">
-        <v>0.5992192225430597</v>
+        <v>0.5992192225430595</v>
       </c>
       <c r="BJ200" s="190" t="n">
-        <v>0.7980582769576967</v>
+        <v>0.7980582769576968</v>
       </c>
       <c r="BK200" s="198" t="n">
         <v>1.006493398597256</v>
       </c>
       <c r="BL200" s="197" t="n">
-        <v>81.81134515783636</v>
+        <v>81.81134515783639</v>
       </c>
       <c r="BM200" s="190" t="n">
-        <v>80.025476909112</v>
+        <v>80.02547690911199</v>
       </c>
       <c r="BN200" s="190" t="n">
-        <v>82.57063934430796</v>
+        <v>82.57063934430793</v>
       </c>
       <c r="BO200" s="190" t="n">
-        <v>85.938172276497</v>
+        <v>85.93817227649704</v>
       </c>
       <c r="BP200" s="198" t="n">
         <v>88.91982616880655</v>
@@ -41235,7 +41235,7 @@
         <v>19.75993719002158</v>
       </c>
       <c r="BX200" s="462" t="n">
-        <v>0.2304794499825067</v>
+        <v>0.2304794499825066</v>
       </c>
       <c r="BY200" s="463" t="n">
         <v>0.2013055634134734</v>
@@ -41244,7 +41244,7 @@
         <v>0.2116220374516506</v>
       </c>
       <c r="CA200" s="463" t="n">
-        <v>0.2217157632383287</v>
+        <v>0.2217157632383286</v>
       </c>
       <c r="CB200" s="464" t="n">
         <v>0.2241174073297618</v>
@@ -41280,19 +41280,19 @@
         <v>1.00000000004451</v>
       </c>
       <c r="CN200" s="396" t="n">
-        <v>0.999991164304411</v>
+        <v>0.9999911643044108</v>
       </c>
       <c r="CO200" s="397" t="n">
         <v>1.000000000391533</v>
       </c>
       <c r="CP200" s="397" t="n">
-        <v>0.9999999998779148</v>
+        <v>0.9999999998779147</v>
       </c>
       <c r="CQ200" s="397" t="n">
         <v>0.9999999973707342</v>
       </c>
       <c r="CR200" s="398" t="n">
-        <v>0.9999999986937638</v>
+        <v>0.9999999986937639</v>
       </c>
       <c r="CS200" s="465" t="n"/>
       <c r="CT200" s="396" t="n">
@@ -41317,7 +41317,7 @@
         <v>1.000000000163925</v>
       </c>
       <c r="DA200" s="397" t="n">
-        <v>0.9999999999453313</v>
+        <v>0.9999999999453315</v>
       </c>
       <c r="DB200" s="397" t="n">
         <v>0.999999998837279</v>
@@ -41448,34 +41448,34 @@
         <v>0.006</v>
       </c>
       <c r="AP201" s="233" t="n">
-        <v>0.1858701062171397</v>
+        <v>0.1858701062171399</v>
       </c>
       <c r="AQ201" s="190" t="n">
-        <v>0.323408544435915</v>
+        <v>0.3234085444359152</v>
       </c>
       <c r="AR201" s="190" t="n">
-        <v>0.50435207595848</v>
+        <v>0.5043520759584799</v>
       </c>
       <c r="AS201" s="190" t="n">
         <v>0.6855770043211665</v>
       </c>
       <c r="AT201" s="196" t="n">
-        <v>0.9130965906488043</v>
+        <v>0.9130965906488041</v>
       </c>
       <c r="AU201" s="190" t="n">
-        <v>76.5749773802612</v>
+        <v>76.5749773802613</v>
       </c>
       <c r="AV201" s="190" t="n">
-        <v>79.52009751394979</v>
+        <v>79.52009751394988</v>
       </c>
       <c r="AW201" s="190" t="n">
-        <v>82.27397308658472</v>
+        <v>82.2739730865847</v>
       </c>
       <c r="AX201" s="190" t="n">
         <v>80.735415214968</v>
       </c>
       <c r="AY201" s="196" t="n">
-        <v>84.78222070084577</v>
+        <v>84.78222070084576</v>
       </c>
       <c r="BA201" s="111" t="inlineStr">
         <is>
@@ -41498,34 +41498,34 @@
         <v>0.006</v>
       </c>
       <c r="BG201" s="197" t="n">
-        <v>0.1858701062180881</v>
+        <v>0.1858701062180883</v>
       </c>
       <c r="BH201" s="190" t="n">
-        <v>0.3234085444365417</v>
+        <v>0.3234085444365419</v>
       </c>
       <c r="BI201" s="190" t="n">
-        <v>0.504352075958505</v>
+        <v>0.5043520759585048</v>
       </c>
       <c r="BJ201" s="190" t="n">
         <v>0.6855770043232342</v>
       </c>
       <c r="BK201" s="198" t="n">
-        <v>0.9130965906491819</v>
+        <v>0.9130965906491817</v>
       </c>
       <c r="BL201" s="197" t="n">
-        <v>76.57497738026215</v>
+        <v>76.57497738026225</v>
       </c>
       <c r="BM201" s="190" t="n">
-        <v>79.52009751395042</v>
+        <v>79.5200975139505</v>
       </c>
       <c r="BN201" s="190" t="n">
-        <v>82.27397308658475</v>
+        <v>82.27397308658473</v>
       </c>
       <c r="BO201" s="190" t="n">
         <v>80.73541521497008</v>
       </c>
       <c r="BP201" s="198" t="n">
-        <v>84.78222070084614</v>
+        <v>84.78222070084612</v>
       </c>
       <c r="BR201" s="111" t="inlineStr">
         <is>
@@ -41545,31 +41545,31 @@
         <v>55.5139983432603</v>
       </c>
       <c r="BW201" s="337" t="n">
-        <v>55.46093120356362</v>
+        <v>55.46093120356361</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.5476011357906765</v>
+        <v>0.5476011357906757</v>
       </c>
       <c r="BY201" s="463" t="n">
-        <v>0.5864807639926883</v>
+        <v>0.5864807639926877</v>
       </c>
       <c r="BZ201" s="463" t="n">
         <v>0.6166436495693151</v>
       </c>
       <c r="CA201" s="463" t="n">
-        <v>0.6932064406735401</v>
+        <v>0.6932064406735402</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>0.6609797701608648</v>
+        <v>0.660979770160865</v>
       </c>
       <c r="CC201" s="197" t="n">
-        <v>41.89126231740506</v>
+        <v>41.89126231740505</v>
       </c>
       <c r="CD201" s="190" t="n">
         <v>46.59256927612093</v>
       </c>
       <c r="CE201" s="190" t="n">
-        <v>50.68726554574953</v>
+        <v>50.68726554574952</v>
       </c>
       <c r="CF201" s="190" t="n">
         <v>55.91404406348781</v>
@@ -41611,7 +41611,7 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="CU201" s="423" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="CV201" s="423" t="n">
         <v>1</v>
@@ -41629,10 +41629,10 @@
         <v>1.000000016316011</v>
       </c>
       <c r="DA201" s="423" t="n">
-        <v>0.9999999865923037</v>
+        <v>0.9999999865923039</v>
       </c>
       <c r="DB201" s="423" t="n">
-        <v>0.9999999834778831</v>
+        <v>0.999999983477883</v>
       </c>
       <c r="DC201" s="424" t="n">
         <v>0.9999999903158332</v>
@@ -41775,19 +41775,19 @@
         <v>0</v>
       </c>
       <c r="AU202" s="209" t="n">
-        <v>3.005182788725762</v>
+        <v>3.005182788725758</v>
       </c>
       <c r="AV202" s="209" t="n">
-        <v>2.227141504817265</v>
+        <v>2.227141504817268</v>
       </c>
       <c r="AW202" s="209" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="AX202" s="209" t="n">
-        <v>2.341363372665477</v>
+        <v>2.341363372665473</v>
       </c>
       <c r="AY202" s="210" t="n">
-        <v>2.38884622186313</v>
+        <v>2.388846221863133</v>
       </c>
       <c r="BA202" s="111" t="inlineStr">
         <is>
@@ -41825,19 +41825,19 @@
         <v>0</v>
       </c>
       <c r="BL202" s="212" t="n">
-        <v>3.005182788725762</v>
+        <v>3.005182788725758</v>
       </c>
       <c r="BM202" s="212" t="n">
-        <v>2.227141504817265</v>
+        <v>2.227141504817268</v>
       </c>
       <c r="BN202" s="212" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="BO202" s="212" t="n">
-        <v>2.341363372665477</v>
+        <v>2.341363372665473</v>
       </c>
       <c r="BP202" s="213" t="n">
-        <v>2.38884622186313</v>
+        <v>2.388846221863133</v>
       </c>
       <c r="BR202" s="111" t="inlineStr">
         <is>
@@ -41860,19 +41860,19 @@
         <v>2.388846221863131</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>0.7217567347449483</v>
+        <v>0.7217567347449492</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>0.9999999999999992</v>
+        <v>0.9999999999999976</v>
       </c>
       <c r="BZ202" s="467" t="n">
         <v>0.9999999999999992</v>
       </c>
       <c r="CA202" s="467" t="n">
-        <v>0.999999999999999</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="CB202" s="468" t="n">
-        <v>1</v>
+        <v>0.9999999999999989</v>
       </c>
       <c r="CC202" s="212" t="n">
         <v>2.164511354735448</v>
@@ -41884,7 +41884,7 @@
         <v>2.288233811213714</v>
       </c>
       <c r="CF202" s="212" t="n">
-        <v>2.334639192905128</v>
+        <v>2.334639192905129</v>
       </c>
       <c r="CG202" s="213" t="n">
         <v>2.381985675737245</v>
@@ -42022,10 +42022,10 @@
         <v>0.018</v>
       </c>
       <c r="AP203" s="206" t="n">
-        <v>0.740379900883674</v>
+        <v>0.7403799008836744</v>
       </c>
       <c r="AQ203" s="207" t="n">
-        <v>1.291786066229836</v>
+        <v>1.291786066229837</v>
       </c>
       <c r="AR203" s="207" t="n">
         <v>2.036522190309677</v>
@@ -42034,22 +42034,22 @@
         <v>2.706386396669274</v>
       </c>
       <c r="AT203" s="208" t="n">
-        <v>3.426803001347271</v>
+        <v>3.42680300134727</v>
       </c>
       <c r="AU203" s="207" t="n">
-        <v>314.4746492987598</v>
+        <v>314.4746492987601</v>
       </c>
       <c r="AV203" s="207" t="n">
         <v>301.4672412479838</v>
       </c>
       <c r="AW203" s="207" t="n">
-        <v>303.5345244156122</v>
+        <v>303.5345244156123</v>
       </c>
       <c r="AX203" s="207" t="n">
         <v>300.1589698085982</v>
       </c>
       <c r="AY203" s="208" t="n">
-        <v>300.2987920734472</v>
+        <v>300.2987920734471</v>
       </c>
       <c r="BA203" s="155" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>0.018</v>
       </c>
       <c r="BG203" s="221" t="n">
-        <v>0.7403799008843008</v>
+        <v>0.7403799008843013</v>
       </c>
       <c r="BH203" s="222" t="n">
         <v>1.29178606622981</v>
@@ -42084,22 +42084,22 @@
         <v>2.706386396671317</v>
       </c>
       <c r="BK203" s="214" t="n">
-        <v>3.426803001349421</v>
+        <v>3.42680300134942</v>
       </c>
       <c r="BL203" s="222" t="n">
-        <v>314.4746492987605</v>
+        <v>314.4746492987607</v>
       </c>
       <c r="BM203" s="222" t="n">
         <v>301.4672412479838</v>
       </c>
       <c r="BN203" s="222" t="n">
-        <v>303.5345244156111</v>
+        <v>303.5345244156112</v>
       </c>
       <c r="BO203" s="222" t="n">
         <v>300.1589698086002</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>300.2987920734494</v>
+        <v>300.2987920734492</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>123.1276364700726</v>
       </c>
       <c r="BX203" s="466" t="n">
-        <v>0.4197687492784521</v>
+        <v>0.4197687492784518</v>
       </c>
       <c r="BY203" s="467" t="n">
         <v>0.4020516283175345</v>
@@ -42131,10 +42131,10 @@
         <v>0.4158147704275204</v>
       </c>
       <c r="CA203" s="467" t="n">
-        <v>0.4289762800406605</v>
+        <v>0.4289762800406604</v>
       </c>
       <c r="CB203" s="468" t="n">
-        <v>0.4132833896497344</v>
+        <v>0.4132833896497345</v>
       </c>
       <c r="CC203" s="212" t="n">
         <v>131.6668798217679</v>
@@ -42937,34 +42937,34 @@
         <v>126.9942697018997</v>
       </c>
       <c r="AP208" s="473" t="n">
-        <v>0.09378067228850867</v>
+        <v>0.09378067228850863</v>
       </c>
       <c r="AQ208" s="463" t="n">
         <v>0.2813335157534057</v>
       </c>
       <c r="AR208" s="463" t="n">
-        <v>0.4192100015235483</v>
+        <v>0.419210001523548</v>
       </c>
       <c r="AS208" s="463" t="n">
         <v>0.4687337995696748</v>
       </c>
       <c r="AT208" s="474" t="n">
-        <v>0.5115460721818799</v>
+        <v>0.51154607218188</v>
       </c>
       <c r="AU208" s="463" t="n">
-        <v>0.09178067228700054</v>
+        <v>0.09178067228700049</v>
       </c>
       <c r="AV208" s="463" t="n">
         <v>0.2783335157509287</v>
       </c>
       <c r="AW208" s="463" t="n">
-        <v>0.4152100015238631</v>
+        <v>0.4152100015238628</v>
       </c>
       <c r="AX208" s="463" t="n">
         <v>0.4637337995696847</v>
       </c>
       <c r="AY208" s="474" t="n">
-        <v>0.505546072183644</v>
+        <v>0.5055460721836441</v>
       </c>
       <c r="BA208" s="83" t="inlineStr">
         <is>
@@ -42987,34 +42987,34 @@
         <v>126.994269702</v>
       </c>
       <c r="BG208" s="462" t="n">
-        <v>0.09378067228714197</v>
+        <v>0.09378067228714192</v>
       </c>
       <c r="BH208" s="463" t="n">
-        <v>0.2813335157516255</v>
+        <v>0.2813335157516256</v>
       </c>
       <c r="BI208" s="463" t="n">
-        <v>0.4192100015237311</v>
+        <v>0.4192100015237308</v>
       </c>
       <c r="BJ208" s="463" t="n">
         <v>0.46873379956968</v>
       </c>
       <c r="BK208" s="464" t="n">
-        <v>0.5115460721827415</v>
+        <v>0.5115460721827417</v>
       </c>
       <c r="BL208" s="475" t="n">
-        <v>0.0917806722853057</v>
+        <v>0.09178067228530565</v>
       </c>
       <c r="BM208" s="476" t="n">
         <v>0.2783335157533217</v>
       </c>
       <c r="BN208" s="476" t="n">
-        <v>0.4152100015229038</v>
+        <v>0.4152100015229036</v>
       </c>
       <c r="BO208" s="476" t="n">
         <v>0.4637337995712764</v>
       </c>
       <c r="BP208" s="477" t="n">
-        <v>0.5055460721831515</v>
+        <v>0.5055460721831517</v>
       </c>
       <c r="BR208" s="83" t="inlineStr">
         <is>
@@ -43037,19 +43037,19 @@
         <v>0</v>
       </c>
       <c r="BX208" s="462" t="n">
-        <v>0.09212532818690614</v>
+        <v>0.09212532818690607</v>
       </c>
       <c r="BY208" s="463" t="n">
         <v>0.2791393690116816</v>
       </c>
       <c r="BZ208" s="463" t="n">
-        <v>0.4162049352672904</v>
+        <v>0.4162049352672901</v>
       </c>
       <c r="CA208" s="463" t="n">
         <v>0.464782861311653</v>
       </c>
       <c r="CB208" s="464" t="n">
-        <v>0.5066346541436433</v>
+        <v>0.5066346541436435</v>
       </c>
       <c r="CC208" s="478" t="n">
         <v>0</v>
@@ -43192,31 +43192,31 @@
         <v>78.82907359740186</v>
       </c>
       <c r="AP209" s="473" t="n">
-        <v>0.2493784731635451</v>
+        <v>0.249378473163545</v>
       </c>
       <c r="AQ209" s="463" t="n">
-        <v>0.3837053929785561</v>
+        <v>0.3837053929785562</v>
       </c>
       <c r="AR209" s="463" t="n">
-        <v>0.4528118121865784</v>
+        <v>0.4528118121865786</v>
       </c>
       <c r="AS209" s="463" t="n">
-        <v>0.4665795941362778</v>
+        <v>0.4665795941362777</v>
       </c>
       <c r="AT209" s="474" t="n">
         <v>0.475923043950475</v>
       </c>
       <c r="AU209" s="463" t="n">
-        <v>0.2473784731644041</v>
+        <v>0.247378473164404</v>
       </c>
       <c r="AV209" s="463" t="n">
         <v>0.3807053929805821</v>
       </c>
       <c r="AW209" s="463" t="n">
-        <v>0.4488118121842744</v>
+        <v>0.4488118121842746</v>
       </c>
       <c r="AX209" s="463" t="n">
-        <v>0.4615795941362326</v>
+        <v>0.4615795941362325</v>
       </c>
       <c r="AY209" s="474" t="n">
         <v>0.469923043949594</v>
@@ -43242,28 +43242,28 @@
         <v>78.82907359699999</v>
       </c>
       <c r="BG209" s="462" t="n">
-        <v>0.2493784731641899</v>
+        <v>0.2493784731641898</v>
       </c>
       <c r="BH209" s="463" t="n">
-        <v>0.3837053929798047</v>
+        <v>0.3837053929798048</v>
       </c>
       <c r="BI209" s="463" t="n">
-        <v>0.4528118121853176</v>
+        <v>0.4528118121853178</v>
       </c>
       <c r="BJ209" s="463" t="n">
-        <v>0.4665795941362537</v>
+        <v>0.4665795941362536</v>
       </c>
       <c r="BK209" s="464" t="n">
         <v>0.4759230439500133</v>
       </c>
       <c r="BL209" s="462" t="n">
-        <v>0.2473784731639665</v>
+        <v>0.2473784731639664</v>
       </c>
       <c r="BM209" s="463" t="n">
         <v>0.3807053929834028</v>
       </c>
       <c r="BN209" s="463" t="n">
-        <v>0.4488118121822673</v>
+        <v>0.4488118121822675</v>
       </c>
       <c r="BO209" s="463" t="n">
         <v>0.4615795941359886</v>
@@ -43292,7 +43292,7 @@
         <v>0</v>
       </c>
       <c r="BX209" s="462" t="n">
-        <v>0.2475998035285774</v>
+        <v>0.2475998035285773</v>
       </c>
       <c r="BY209" s="463" t="n">
         <v>0.3809437879095271</v>
@@ -43301,7 +43301,7 @@
         <v>0.4490604377094405</v>
       </c>
       <c r="CA209" s="463" t="n">
-        <v>0.4618264025262152</v>
+        <v>0.4618264025262151</v>
       </c>
       <c r="CB209" s="464" t="n">
         <v>0.4701313985194043</v>
@@ -43447,13 +43447,13 @@
         <v>67.40054440735119</v>
       </c>
       <c r="AP210" s="473" t="n">
-        <v>0.1780377293721051</v>
+        <v>0.1780377293721049</v>
       </c>
       <c r="AQ210" s="463" t="n">
-        <v>0.2653562467777617</v>
+        <v>0.2653562467777615</v>
       </c>
       <c r="AR210" s="463" t="n">
-        <v>0.3514877807909901</v>
+        <v>0.3514877807909902</v>
       </c>
       <c r="AS210" s="463" t="n">
         <v>0.4161863823750238</v>
@@ -43462,13 +43462,13 @@
         <v>0.4488920998997262</v>
       </c>
       <c r="AU210" s="463" t="n">
-        <v>0.1760377293772079</v>
+        <v>0.1760377293772077</v>
       </c>
       <c r="AV210" s="463" t="n">
-        <v>0.2623562467796993</v>
+        <v>0.2623562467796991</v>
       </c>
       <c r="AW210" s="463" t="n">
-        <v>0.3474877807910396</v>
+        <v>0.3474877807910397</v>
       </c>
       <c r="AX210" s="463" t="n">
         <v>0.4111863823780397</v>
@@ -43497,10 +43497,10 @@
         <v>67.400544407</v>
       </c>
       <c r="BG210" s="462" t="n">
-        <v>0.1780377293762994</v>
+        <v>0.1780377293762992</v>
       </c>
       <c r="BH210" s="463" t="n">
-        <v>0.2653562467791851</v>
+        <v>0.2653562467791849</v>
       </c>
       <c r="BI210" s="463" t="n">
         <v>0.3514877807910223</v>
@@ -43509,13 +43509,13 @@
         <v>0.4161863823767845</v>
       </c>
       <c r="BK210" s="464" t="n">
-        <v>0.448892099899954</v>
+        <v>0.4488920998999541</v>
       </c>
       <c r="BL210" s="462" t="n">
-        <v>0.1760377293786461</v>
+        <v>0.1760377293786459</v>
       </c>
       <c r="BM210" s="463" t="n">
-        <v>0.2623562467832345</v>
+        <v>0.2623562467832343</v>
       </c>
       <c r="BN210" s="463" t="n">
         <v>0.3474877807906931</v>
@@ -43524,7 +43524,7 @@
         <v>0.4111863823791419</v>
       </c>
       <c r="BP210" s="464" t="n">
-        <v>0.4428920998976488</v>
+        <v>0.4428920998976489</v>
       </c>
       <c r="BR210" s="111" t="inlineStr">
         <is>
@@ -43547,10 +43547,10 @@
         <v>0</v>
       </c>
       <c r="BX210" s="462" t="n">
-        <v>0.1761806443946912</v>
+        <v>0.176180644394691</v>
       </c>
       <c r="BY210" s="463" t="n">
-        <v>0.2625407780098297</v>
+        <v>0.2625407780098295</v>
       </c>
       <c r="BZ210" s="463" t="n">
         <v>0.3476955335033974</v>
@@ -43957,7 +43957,7 @@
         <v>273.2238877066527</v>
       </c>
       <c r="AP212" s="500" t="n">
-        <v>0.1593291512627112</v>
+        <v>0.1593291512627111</v>
       </c>
       <c r="AQ212" s="501" t="n">
         <v>0.306469840820503</v>
@@ -43969,13 +43969,13 @@
         <v>0.4528285823116924</v>
       </c>
       <c r="AT212" s="502" t="n">
-        <v>0.4823709688590627</v>
+        <v>0.4823709688590628</v>
       </c>
       <c r="AU212" s="501" t="n">
-        <v>0.1573452564180101</v>
+        <v>0.1573452564180099</v>
       </c>
       <c r="AV212" s="501" t="n">
-        <v>0.303485277690264</v>
+        <v>0.3034852776902639</v>
       </c>
       <c r="AW212" s="501" t="n">
         <v>0.4064930269674435</v>
@@ -43984,7 +43984,7 @@
         <v>0.4478501172921799</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0.4763959601590348</v>
+        <v>0.4763959601590349</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>273.223887706</v>
       </c>
       <c r="BG212" s="503" t="n">
-        <v>0.1593291512625774</v>
+        <v>0.1593291512625773</v>
       </c>
       <c r="BH212" s="504" t="n">
         <v>0.3064698408205093</v>
@@ -44019,10 +44019,10 @@
         <v>0.452828582311352</v>
       </c>
       <c r="BK212" s="505" t="n">
-        <v>0.4823709688587614</v>
+        <v>0.4823709688587615</v>
       </c>
       <c r="BL212" s="504" t="n">
-        <v>0.1573452564175662</v>
+        <v>0.1573452564175661</v>
       </c>
       <c r="BM212" s="504" t="n">
         <v>0.3034852776931115</v>
@@ -44057,19 +44057,19 @@
         <v>0</v>
       </c>
       <c r="BX212" s="503" t="n">
-        <v>0.1576872440947848</v>
+        <v>0.1576872440947847</v>
       </c>
       <c r="BY212" s="504" t="n">
         <v>0.3039922756524475</v>
       </c>
       <c r="BZ212" s="504" t="n">
-        <v>0.407068037958198</v>
+        <v>0.4070680379581978</v>
       </c>
       <c r="CA212" s="504" t="n">
         <v>0.4484435629326791</v>
       </c>
       <c r="CB212" s="505" t="n">
-        <v>0.4769747135249922</v>
+        <v>0.4769747135249923</v>
       </c>
       <c r="CC212" s="492" t="n">
         <v>0</v>
@@ -44731,10 +44731,10 @@
         </is>
       </c>
       <c r="AK219" s="506" t="n">
-        <v>9300.44889838463</v>
+        <v>9300.448898384631</v>
       </c>
       <c r="AL219" s="368" t="n">
-        <v>34513.2223587984</v>
+        <v>34513.22235879839</v>
       </c>
       <c r="AM219" s="368" t="n">
         <v>62356.24033128741</v>
@@ -44746,10 +44746,10 @@
         <v>89580.48173789638</v>
       </c>
       <c r="AP219" s="381" t="n">
-        <v>588.3746268688296</v>
+        <v>588.3746268688298</v>
       </c>
       <c r="AQ219" s="372" t="n">
-        <v>633.7546894283594</v>
+        <v>633.7546894283593</v>
       </c>
       <c r="AR219" s="372" t="n">
         <v>637.7485705640689</v>
@@ -44766,10 +44766,10 @@
         </is>
       </c>
       <c r="BB219" s="391" t="n">
-        <v>9300.44889838463</v>
+        <v>9300.448898384631</v>
       </c>
       <c r="BC219" s="375" t="n">
-        <v>34513.2223587984</v>
+        <v>34513.22235879839</v>
       </c>
       <c r="BD219" s="375" t="n">
         <v>62356.24033128741</v>
@@ -44781,10 +44781,10 @@
         <v>89580.48173789638</v>
       </c>
       <c r="BG219" s="386" t="n">
-        <v>588.3746268688296</v>
+        <v>588.3746268688298</v>
       </c>
       <c r="BH219" s="372" t="n">
-        <v>633.7546894283594</v>
+        <v>633.7546894283593</v>
       </c>
       <c r="BI219" s="372" t="n">
         <v>637.7485705640689</v>
@@ -44801,10 +44801,10 @@
         </is>
       </c>
       <c r="BS219" s="391" t="n">
-        <v>9102.104214344678</v>
+        <v>9102.104214344679</v>
       </c>
       <c r="BT219" s="375" t="n">
-        <v>34145.19060566286</v>
+        <v>34145.19060566285</v>
       </c>
       <c r="BU219" s="375" t="n">
         <v>61761.25223350794</v>
@@ -44816,10 +44816,10 @@
         <v>88529.77893785875</v>
       </c>
       <c r="BX219" s="386" t="n">
-        <v>588.3746268688296</v>
+        <v>588.3746268688298</v>
       </c>
       <c r="BY219" s="372" t="n">
-        <v>633.7546894283594</v>
+        <v>633.7546894283593</v>
       </c>
       <c r="BZ219" s="372" t="n">
         <v>637.7485705640689</v>
@@ -44926,7 +44926,7 @@
         </is>
       </c>
       <c r="AK220" s="506" t="n">
-        <v>44335.44858341061</v>
+        <v>44335.44858341062</v>
       </c>
       <c r="AL220" s="368" t="n">
         <v>90066.83119143533</v>
@@ -44941,7 +44941,7 @@
         <v>159406.5384542814</v>
       </c>
       <c r="AP220" s="381" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="AQ220" s="372" t="n">
         <v>1816.502530212065</v>
@@ -44953,7 +44953,7 @@
         <v>1944.270389399368</v>
       </c>
       <c r="AT220" s="382" t="n">
-        <v>1996.685743614349</v>
+        <v>1996.685743614348</v>
       </c>
       <c r="BA220" s="101" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         </is>
       </c>
       <c r="BB220" s="391" t="n">
-        <v>44335.44858341061</v>
+        <v>44335.44858341062</v>
       </c>
       <c r="BC220" s="375" t="n">
         <v>90066.83119143533</v>
@@ -44976,7 +44976,7 @@
         <v>159406.5384542814</v>
       </c>
       <c r="BG220" s="386" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="BH220" s="372" t="n">
         <v>1816.502530212065</v>
@@ -44988,7 +44988,7 @@
         <v>1944.270389399368</v>
       </c>
       <c r="BK220" s="387" t="n">
-        <v>1996.685743614349</v>
+        <v>1996.685743614348</v>
       </c>
       <c r="BR220" s="101" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         </is>
       </c>
       <c r="BS220" s="391" t="n">
-        <v>43979.88101556226</v>
+        <v>43979.88101556227</v>
       </c>
       <c r="BT220" s="375" t="n">
         <v>89362.64381697103</v>
@@ -45011,7 +45011,7 @@
         <v>157396.8874334561</v>
       </c>
       <c r="BX220" s="386" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="BY220" s="372" t="n">
         <v>1816.502530212065</v>
@@ -45023,7 +45023,7 @@
         <v>1944.270389399368</v>
       </c>
       <c r="CB220" s="387" t="n">
-        <v>1996.685743614349</v>
+        <v>1996.685743614348</v>
       </c>
       <c r="CI220" s="197" t="n">
         <v>0</v>
@@ -45124,13 +45124,13 @@
         <v>27159.07525444582</v>
       </c>
       <c r="AL221" s="368" t="n">
-        <v>49819.67164514307</v>
+        <v>49819.67164514306</v>
       </c>
       <c r="AM221" s="368" t="n">
         <v>74511.52994761143</v>
       </c>
       <c r="AN221" s="368" t="n">
-        <v>88747.26377651542</v>
+        <v>88747.26377651544</v>
       </c>
       <c r="AO221" s="380" t="n">
         <v>112279.5677980626</v>
@@ -45139,7 +45139,7 @@
         <v>1641.4338306968</v>
       </c>
       <c r="AQ221" s="372" t="n">
-        <v>1741.571503487291</v>
+        <v>1741.57150348729</v>
       </c>
       <c r="AR221" s="372" t="n">
         <v>1681.27760355684</v>
@@ -45159,13 +45159,13 @@
         <v>27159.07525444582</v>
       </c>
       <c r="BC221" s="375" t="n">
-        <v>49819.67164514307</v>
+        <v>49819.67164514306</v>
       </c>
       <c r="BD221" s="375" t="n">
         <v>74511.52994761143</v>
       </c>
       <c r="BE221" s="375" t="n">
-        <v>88747.26377651542</v>
+        <v>88747.26377651544</v>
       </c>
       <c r="BF221" s="392" t="n">
         <v>112279.5677980626</v>
@@ -45174,7 +45174,7 @@
         <v>1641.4338306968</v>
       </c>
       <c r="BH221" s="372" t="n">
-        <v>1741.571503487291</v>
+        <v>1741.57150348729</v>
       </c>
       <c r="BI221" s="372" t="n">
         <v>1681.27760355684</v>
@@ -45194,13 +45194,13 @@
         <v>26853.98177434222</v>
       </c>
       <c r="BT221" s="375" t="n">
-        <v>49256.43254092836</v>
+        <v>49256.43254092835</v>
       </c>
       <c r="BU221" s="375" t="n">
         <v>73663.57409792523</v>
       </c>
       <c r="BV221" s="375" t="n">
-        <v>87681.06762627319</v>
+        <v>87681.06762627322</v>
       </c>
       <c r="BW221" s="392" t="n">
         <v>110778.8120324848</v>
@@ -45209,7 +45209,7 @@
         <v>1641.4338306968</v>
       </c>
       <c r="BY221" s="372" t="n">
-        <v>1741.571503487291</v>
+        <v>1741.57150348729</v>
       </c>
       <c r="BZ221" s="372" t="n">
         <v>1681.27760355684</v>
@@ -45511,7 +45511,7 @@
         </is>
       </c>
       <c r="AK223" s="435" t="n">
-        <v>80794.97273624105</v>
+        <v>80794.97273624106</v>
       </c>
       <c r="AL223" s="408" t="n">
         <v>174399.7251953768</v>
@@ -45529,7 +45529,7 @@
         <v>1358.792448141342</v>
       </c>
       <c r="AQ223" s="437" t="n">
-        <v>1314.76528173481</v>
+        <v>1314.765281734809</v>
       </c>
       <c r="AR223" s="437" t="n">
         <v>1264.71030450529</v>
@@ -45546,7 +45546,7 @@
         </is>
       </c>
       <c r="BB223" s="439" t="n">
-        <v>80794.97273624105</v>
+        <v>80794.97273624106</v>
       </c>
       <c r="BC223" s="440" t="n">
         <v>174399.7251953768</v>
@@ -45564,7 +45564,7 @@
         <v>1358.792448141342</v>
       </c>
       <c r="BH223" s="443" t="n">
-        <v>1314.76528173481</v>
+        <v>1314.765281734809</v>
       </c>
       <c r="BI223" s="443" t="n">
         <v>1264.71030450529</v>
@@ -45584,13 +45584,13 @@
         <v>79935.96700424916</v>
       </c>
       <c r="BT223" s="440" t="n">
-        <v>172764.2669635623</v>
+        <v>172764.2669635622</v>
       </c>
       <c r="BU223" s="440" t="n">
         <v>262918.0900008731</v>
       </c>
       <c r="BV223" s="440" t="n">
-        <v>307244.6077463383</v>
+        <v>307244.6077463384</v>
       </c>
       <c r="BW223" s="441" t="n">
         <v>356705.4784037996</v>
@@ -45599,7 +45599,7 @@
         <v>1361.296121074501</v>
       </c>
       <c r="BY223" s="443" t="n">
-        <v>1315.244419303811</v>
+        <v>1315.24441930381</v>
       </c>
       <c r="BZ223" s="443" t="n">
         <v>1264.692953863358</v>
@@ -47629,10 +47629,10 @@
         </is>
       </c>
       <c r="AK237" s="506" t="n">
-        <v>9300.44889838463</v>
+        <v>9300.448898384631</v>
       </c>
       <c r="AL237" s="368" t="n">
-        <v>34513.2223587984</v>
+        <v>34513.22235879839</v>
       </c>
       <c r="AM237" s="368" t="n">
         <v>62356.24033128741</v>
@@ -47644,10 +47644,10 @@
         <v>89580.48173789638</v>
       </c>
       <c r="AP237" s="381" t="n">
-        <v>588.3746268688296</v>
+        <v>588.3746268688298</v>
       </c>
       <c r="AQ237" s="372" t="n">
-        <v>633.7546894283594</v>
+        <v>633.7546894283593</v>
       </c>
       <c r="AR237" s="372" t="n">
         <v>637.7485705640689</v>
@@ -47664,10 +47664,10 @@
         </is>
       </c>
       <c r="BB237" s="391" t="n">
-        <v>9300.44889838463</v>
+        <v>9300.448898384631</v>
       </c>
       <c r="BC237" s="375" t="n">
-        <v>34513.2223587984</v>
+        <v>34513.22235879839</v>
       </c>
       <c r="BD237" s="375" t="n">
         <v>62356.24033128741</v>
@@ -47679,10 +47679,10 @@
         <v>89580.48173789638</v>
       </c>
       <c r="BG237" s="386" t="n">
-        <v>588.3746268688296</v>
+        <v>588.3746268688298</v>
       </c>
       <c r="BH237" s="372" t="n">
-        <v>633.7546894283594</v>
+        <v>633.7546894283593</v>
       </c>
       <c r="BI237" s="372" t="n">
         <v>637.7485705640689</v>
@@ -47699,10 +47699,10 @@
         </is>
       </c>
       <c r="BS237" s="391" t="n">
-        <v>9102.104214344678</v>
+        <v>9102.104214344679</v>
       </c>
       <c r="BT237" s="375" t="n">
-        <v>34145.19060566286</v>
+        <v>34145.19060566285</v>
       </c>
       <c r="BU237" s="375" t="n">
         <v>61761.25223350794</v>
@@ -47714,10 +47714,10 @@
         <v>88529.77893785875</v>
       </c>
       <c r="BX237" s="386" t="n">
-        <v>588.3746268688296</v>
+        <v>588.3746268688298</v>
       </c>
       <c r="BY237" s="372" t="n">
-        <v>633.7546894283594</v>
+        <v>633.7546894283593</v>
       </c>
       <c r="BZ237" s="372" t="n">
         <v>637.7485705640689</v>
@@ -47824,7 +47824,7 @@
         </is>
       </c>
       <c r="AK238" s="506" t="n">
-        <v>44335.44858341061</v>
+        <v>44335.44858341062</v>
       </c>
       <c r="AL238" s="368" t="n">
         <v>90066.83119143533</v>
@@ -47839,7 +47839,7 @@
         <v>159406.5384542814</v>
       </c>
       <c r="AP238" s="381" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="AQ238" s="372" t="n">
         <v>1816.502530212065</v>
@@ -47851,7 +47851,7 @@
         <v>1944.270389399368</v>
       </c>
       <c r="AT238" s="382" t="n">
-        <v>1996.685743614349</v>
+        <v>1996.685743614348</v>
       </c>
       <c r="BA238" s="101" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         </is>
       </c>
       <c r="BB238" s="391" t="n">
-        <v>44335.44858341061</v>
+        <v>44335.44858341062</v>
       </c>
       <c r="BC238" s="375" t="n">
         <v>90066.83119143533</v>
@@ -47874,7 +47874,7 @@
         <v>159406.5384542814</v>
       </c>
       <c r="BG238" s="386" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="BH238" s="372" t="n">
         <v>1816.502530212065</v>
@@ -47886,7 +47886,7 @@
         <v>1944.270389399368</v>
       </c>
       <c r="BK238" s="387" t="n">
-        <v>1996.685743614349</v>
+        <v>1996.685743614348</v>
       </c>
       <c r="BR238" s="101" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         </is>
       </c>
       <c r="BS238" s="391" t="n">
-        <v>43979.88101556226</v>
+        <v>43979.88101556227</v>
       </c>
       <c r="BT238" s="375" t="n">
         <v>89362.64381697103</v>
@@ -47909,7 +47909,7 @@
         <v>157396.8874334561</v>
       </c>
       <c r="BX238" s="386" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="BY238" s="372" t="n">
         <v>1816.502530212065</v>
@@ -47921,7 +47921,7 @@
         <v>1944.270389399368</v>
       </c>
       <c r="CB238" s="387" t="n">
-        <v>1996.685743614349</v>
+        <v>1996.685743614348</v>
       </c>
       <c r="CI238" s="197" t="n">
         <v>0</v>
@@ -48022,13 +48022,13 @@
         <v>27159.07525444582</v>
       </c>
       <c r="AL239" s="368" t="n">
-        <v>49819.67164514307</v>
+        <v>49819.67164514306</v>
       </c>
       <c r="AM239" s="368" t="n">
         <v>74511.52994761143</v>
       </c>
       <c r="AN239" s="368" t="n">
-        <v>88747.26377651542</v>
+        <v>88747.26377651544</v>
       </c>
       <c r="AO239" s="380" t="n">
         <v>112279.5677980626</v>
@@ -48037,7 +48037,7 @@
         <v>1641.4338306968</v>
       </c>
       <c r="AQ239" s="372" t="n">
-        <v>1741.571503487291</v>
+        <v>1741.57150348729</v>
       </c>
       <c r="AR239" s="372" t="n">
         <v>1681.27760355684</v>
@@ -48057,13 +48057,13 @@
         <v>27159.07525444582</v>
       </c>
       <c r="BC239" s="375" t="n">
-        <v>49819.67164514307</v>
+        <v>49819.67164514306</v>
       </c>
       <c r="BD239" s="375" t="n">
         <v>74511.52994761143</v>
       </c>
       <c r="BE239" s="375" t="n">
-        <v>88747.26377651542</v>
+        <v>88747.26377651544</v>
       </c>
       <c r="BF239" s="392" t="n">
         <v>112279.5677980626</v>
@@ -48072,7 +48072,7 @@
         <v>1641.4338306968</v>
       </c>
       <c r="BH239" s="372" t="n">
-        <v>1741.571503487291</v>
+        <v>1741.57150348729</v>
       </c>
       <c r="BI239" s="372" t="n">
         <v>1681.27760355684</v>
@@ -48092,13 +48092,13 @@
         <v>26853.98177434222</v>
       </c>
       <c r="BT239" s="375" t="n">
-        <v>49256.43254092836</v>
+        <v>49256.43254092835</v>
       </c>
       <c r="BU239" s="375" t="n">
         <v>73663.57409792523</v>
       </c>
       <c r="BV239" s="375" t="n">
-        <v>87681.06762627319</v>
+        <v>87681.06762627322</v>
       </c>
       <c r="BW239" s="392" t="n">
         <v>110778.8120324848</v>
@@ -48107,7 +48107,7 @@
         <v>1641.4338306968</v>
       </c>
       <c r="BY239" s="372" t="n">
-        <v>1741.571503487291</v>
+        <v>1741.57150348729</v>
       </c>
       <c r="BZ239" s="372" t="n">
         <v>1681.27760355684</v>
@@ -48409,7 +48409,7 @@
         </is>
       </c>
       <c r="AK241" s="435" t="n">
-        <v>80794.97273624105</v>
+        <v>80794.97273624106</v>
       </c>
       <c r="AL241" s="408" t="n">
         <v>174399.7251953768</v>
@@ -48427,7 +48427,7 @@
         <v>1358.792448141342</v>
       </c>
       <c r="AQ241" s="437" t="n">
-        <v>1314.76528173481</v>
+        <v>1314.765281734809</v>
       </c>
       <c r="AR241" s="437" t="n">
         <v>1264.71030450529</v>
@@ -48444,7 +48444,7 @@
         </is>
       </c>
       <c r="BB241" s="439" t="n">
-        <v>80794.97273624105</v>
+        <v>80794.97273624106</v>
       </c>
       <c r="BC241" s="440" t="n">
         <v>174399.7251953768</v>
@@ -48462,7 +48462,7 @@
         <v>1358.792448141342</v>
       </c>
       <c r="BH241" s="443" t="n">
-        <v>1314.76528173481</v>
+        <v>1314.765281734809</v>
       </c>
       <c r="BI241" s="443" t="n">
         <v>1264.71030450529</v>
@@ -48482,13 +48482,13 @@
         <v>79935.96700424916</v>
       </c>
       <c r="BT241" s="440" t="n">
-        <v>172764.2669635623</v>
+        <v>172764.2669635622</v>
       </c>
       <c r="BU241" s="440" t="n">
         <v>262918.0900008731</v>
       </c>
       <c r="BV241" s="440" t="n">
-        <v>307244.6077463383</v>
+        <v>307244.6077463384</v>
       </c>
       <c r="BW241" s="441" t="n">
         <v>356705.4784037996</v>
@@ -48497,7 +48497,7 @@
         <v>1361.296121074501</v>
       </c>
       <c r="BY241" s="443" t="n">
-        <v>1315.244419303811</v>
+        <v>1315.24441930381</v>
       </c>
       <c r="BZ241" s="443" t="n">
         <v>1264.692953863358</v>
@@ -49048,22 +49048,22 @@
         <v>117930.9315359258</v>
       </c>
       <c r="AO246" s="380" t="n">
-        <v>120363.4657088641</v>
+        <v>120363.4657088642</v>
       </c>
       <c r="AP246" s="381" t="n">
         <v>745.5505766414577</v>
       </c>
       <c r="AQ246" s="372" t="n">
-        <v>800.164541630362</v>
+        <v>800.1645416303616</v>
       </c>
       <c r="AR246" s="372" t="n">
-        <v>853.5318245326978</v>
+        <v>853.5318245326976</v>
       </c>
       <c r="AS246" s="372" t="n">
         <v>907.7107505689086</v>
       </c>
       <c r="AT246" s="382" t="n">
-        <v>980.9518566040674</v>
+        <v>980.9518566040676</v>
       </c>
       <c r="BA246" s="83" t="inlineStr">
         <is>
@@ -49083,22 +49083,22 @@
         <v>117930.9315359258</v>
       </c>
       <c r="BF246" s="392" t="n">
-        <v>120363.4657088641</v>
+        <v>120363.4657088642</v>
       </c>
       <c r="BG246" s="386" t="n">
         <v>745.5505766414577</v>
       </c>
       <c r="BH246" s="372" t="n">
-        <v>800.164541630362</v>
+        <v>800.1645416303616</v>
       </c>
       <c r="BI246" s="372" t="n">
-        <v>853.5318245326978</v>
+        <v>853.5318245326976</v>
       </c>
       <c r="BJ246" s="372" t="n">
         <v>907.7107505689086</v>
       </c>
       <c r="BK246" s="387" t="n">
-        <v>980.9518566040674</v>
+        <v>980.9518566040676</v>
       </c>
       <c r="BR246" s="83" t="inlineStr">
         <is>
@@ -49124,16 +49124,16 @@
         <v>745.5505766414577</v>
       </c>
       <c r="BY246" s="372" t="n">
-        <v>800.164541630362</v>
+        <v>800.1645416303616</v>
       </c>
       <c r="BZ246" s="372" t="n">
-        <v>853.5318245326978</v>
+        <v>853.5318245326976</v>
       </c>
       <c r="CA246" s="372" t="n">
         <v>907.7107505689086</v>
       </c>
       <c r="CB246" s="387" t="n">
-        <v>980.9518566040674</v>
+        <v>980.9518566040676</v>
       </c>
       <c r="CI246" s="225" t="n"/>
       <c r="CJ246" s="225" t="n"/>
@@ -49218,7 +49218,7 @@
         <v>172551.8381675001</v>
       </c>
       <c r="AL247" s="368" t="n">
-        <v>179603.8868293243</v>
+        <v>179603.8868293242</v>
       </c>
       <c r="AM247" s="368" t="n">
         <v>195568.7596927182</v>
@@ -49230,10 +49230,10 @@
         <v>235525.5846029741</v>
       </c>
       <c r="AP247" s="381" t="n">
-        <v>2114.762873860428</v>
+        <v>2114.762873860429</v>
       </c>
       <c r="AQ247" s="372" t="n">
-        <v>2255.25882410995</v>
+        <v>2255.258824109948</v>
       </c>
       <c r="AR247" s="372" t="n">
         <v>2385.816415058426</v>
@@ -49242,7 +49242,7 @@
         <v>2524.5476401112</v>
       </c>
       <c r="AT247" s="382" t="n">
-        <v>2679.065588596887</v>
+        <v>2679.065588596888</v>
       </c>
       <c r="BA247" s="101" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>172551.8381675001</v>
       </c>
       <c r="BC247" s="375" t="n">
-        <v>179603.8868293243</v>
+        <v>179603.8868293242</v>
       </c>
       <c r="BD247" s="375" t="n">
         <v>195568.7596927182</v>
@@ -49265,10 +49265,10 @@
         <v>235525.5846029741</v>
       </c>
       <c r="BG247" s="386" t="n">
-        <v>2114.762873860428</v>
+        <v>2114.762873860429</v>
       </c>
       <c r="BH247" s="372" t="n">
-        <v>2255.25882410995</v>
+        <v>2255.258824109948</v>
       </c>
       <c r="BI247" s="372" t="n">
         <v>2385.816415058426</v>
@@ -49277,7 +49277,7 @@
         <v>2524.5476401112</v>
       </c>
       <c r="BK247" s="387" t="n">
-        <v>2679.065588596887</v>
+        <v>2679.065588596888</v>
       </c>
       <c r="BR247" s="101" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>172806.1060695505</v>
       </c>
       <c r="BT247" s="375" t="n">
-        <v>180295.7887207968</v>
+        <v>180295.7887207967</v>
       </c>
       <c r="BU247" s="375" t="n">
         <v>196800.5059366165</v>
@@ -49297,13 +49297,13 @@
         <v>216739.6677239698</v>
       </c>
       <c r="BW247" s="392" t="n">
-        <v>238022.8751124911</v>
+        <v>238022.8751124912</v>
       </c>
       <c r="BX247" s="386" t="n">
-        <v>2114.762873860428</v>
+        <v>2114.762873860429</v>
       </c>
       <c r="BY247" s="372" t="n">
-        <v>2255.25882410995</v>
+        <v>2255.258824109948</v>
       </c>
       <c r="BZ247" s="372" t="n">
         <v>2385.816415058426</v>
@@ -49312,7 +49312,7 @@
         <v>2524.5476401112</v>
       </c>
       <c r="CB247" s="387" t="n">
-        <v>2679.065588596887</v>
+        <v>2679.065588596888</v>
       </c>
       <c r="CI247" s="225" t="n"/>
       <c r="CJ247" s="225" t="n"/>
@@ -49397,7 +49397,7 @@
         <v>157813.7661646547</v>
       </c>
       <c r="AL248" s="368" t="n">
-        <v>174261.8891516261</v>
+        <v>174261.8891516262</v>
       </c>
       <c r="AM248" s="368" t="n">
         <v>197065.9005779591</v>
@@ -49412,16 +49412,16 @@
         <v>2065.919759980866</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>2200.368366660347</v>
+        <v>2200.368366660348</v>
       </c>
       <c r="AR248" s="372" t="n">
-        <v>2410.013622954898</v>
+        <v>2410.013622954899</v>
       </c>
       <c r="AS248" s="372" t="n">
-        <v>2756.207409643826</v>
+        <v>2756.207409643825</v>
       </c>
       <c r="AT248" s="382" t="n">
-        <v>2961.659664545515</v>
+        <v>2961.659664545514</v>
       </c>
       <c r="BA248" s="111" t="inlineStr">
         <is>
@@ -49432,7 +49432,7 @@
         <v>157813.7661646547</v>
       </c>
       <c r="BC248" s="375" t="n">
-        <v>174261.8891516261</v>
+        <v>174261.8891516262</v>
       </c>
       <c r="BD248" s="375" t="n">
         <v>197065.9005779591</v>
@@ -49447,16 +49447,16 @@
         <v>2065.919759980866</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>2200.368366660347</v>
+        <v>2200.368366660348</v>
       </c>
       <c r="BI248" s="372" t="n">
-        <v>2410.013622954898</v>
+        <v>2410.013622954899</v>
       </c>
       <c r="BJ248" s="372" t="n">
-        <v>2756.207409643826</v>
+        <v>2756.207409643825</v>
       </c>
       <c r="BK248" s="387" t="n">
-        <v>2961.659664545515</v>
+        <v>2961.659664545514</v>
       </c>
       <c r="BR248" s="111" t="inlineStr">
         <is>
@@ -49467,31 +49467,31 @@
         <v>158042.0144071815</v>
       </c>
       <c r="BT248" s="375" t="n">
-        <v>174806.782848244</v>
+        <v>174806.7828482441</v>
       </c>
       <c r="BU248" s="375" t="n">
-        <v>198099.827282697</v>
+        <v>198099.8272826971</v>
       </c>
       <c r="BV248" s="375" t="n">
-        <v>222315.7395968189</v>
+        <v>222315.7395968188</v>
       </c>
       <c r="BW248" s="392" t="n">
-        <v>250874.0988206003</v>
+        <v>250874.0988206002</v>
       </c>
       <c r="BX248" s="386" t="n">
         <v>2065.919759980866</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>2200.368366660347</v>
+        <v>2200.368366660348</v>
       </c>
       <c r="BZ248" s="372" t="n">
-        <v>2410.013622954898</v>
+        <v>2410.013622954899</v>
       </c>
       <c r="CA248" s="372" t="n">
-        <v>2756.207409643826</v>
+        <v>2756.207409643825</v>
       </c>
       <c r="CB248" s="387" t="n">
-        <v>2961.659664545515</v>
+        <v>2961.659664545514</v>
       </c>
       <c r="CI248" s="225" t="n"/>
       <c r="CJ248" s="225" t="n"/>
@@ -49573,31 +49573,31 @@
         </is>
       </c>
       <c r="AK249" s="435" t="n">
-        <v>56453.6925031906</v>
+        <v>56453.69250319048</v>
       </c>
       <c r="AL249" s="408" t="n">
         <v>5802.278701392817</v>
       </c>
       <c r="AM249" s="408" t="n">
-        <v>6277.540448684245</v>
+        <v>6277.540448684362</v>
       </c>
       <c r="AN249" s="408" t="n">
-        <v>6725.091417432996</v>
+        <v>6725.091417432879</v>
       </c>
       <c r="AO249" s="409" t="n">
         <v>7204.550084947376</v>
       </c>
       <c r="AP249" s="410" t="n">
-        <v>18785.44383717041</v>
+        <v>18785.44383717037</v>
       </c>
       <c r="AQ249" s="411" t="n">
         <v>2605.258214786317</v>
       </c>
       <c r="AR249" s="411" t="n">
-        <v>2735.521125927158</v>
+        <v>2735.521125927209</v>
       </c>
       <c r="AS249" s="411" t="n">
-        <v>2872.297182853938</v>
+        <v>2872.297182853888</v>
       </c>
       <c r="AT249" s="412" t="n">
         <v>3015.9120409666</v>
@@ -49608,31 +49608,31 @@
         </is>
       </c>
       <c r="BB249" s="419" t="n">
-        <v>56453.6925031906</v>
+        <v>56453.69250319048</v>
       </c>
       <c r="BC249" s="420" t="n">
         <v>5802.278701392817</v>
       </c>
       <c r="BD249" s="420" t="n">
-        <v>6277.540448684245</v>
+        <v>6277.540448684362</v>
       </c>
       <c r="BE249" s="420" t="n">
-        <v>6725.091417432996</v>
+        <v>6725.091417432879</v>
       </c>
       <c r="BF249" s="421" t="n">
         <v>7204.550084947376</v>
       </c>
       <c r="BG249" s="416" t="n">
-        <v>18785.44383717041</v>
+        <v>18785.44383717037</v>
       </c>
       <c r="BH249" s="417" t="n">
         <v>2605.258214786317</v>
       </c>
       <c r="BI249" s="417" t="n">
-        <v>2735.521125927158</v>
+        <v>2735.521125927209</v>
       </c>
       <c r="BJ249" s="417" t="n">
-        <v>2872.297182853938</v>
+        <v>2872.297182853888</v>
       </c>
       <c r="BK249" s="418" t="n">
         <v>3015.9120409666</v>
@@ -49643,31 +49643,31 @@
         </is>
       </c>
       <c r="BS249" s="419" t="n">
-        <v>56336.58064497267</v>
+        <v>56336.58064497256</v>
       </c>
       <c r="BT249" s="420" t="n">
         <v>5785.615091863735</v>
       </c>
       <c r="BU249" s="420" t="n">
-        <v>6259.511931230441</v>
+        <v>6259.511931230557</v>
       </c>
       <c r="BV249" s="420" t="n">
-        <v>6705.77757485584</v>
+        <v>6705.777574855722</v>
       </c>
       <c r="BW249" s="421" t="n">
         <v>7183.859281277524</v>
       </c>
       <c r="BX249" s="416" t="n">
-        <v>18785.44383717041</v>
+        <v>18785.44383717037</v>
       </c>
       <c r="BY249" s="417" t="n">
         <v>2605.258214786317</v>
       </c>
       <c r="BZ249" s="417" t="n">
-        <v>2735.521125927158</v>
+        <v>2735.521125927209</v>
       </c>
       <c r="CA249" s="417" t="n">
-        <v>2872.297182853938</v>
+        <v>2872.297182853888</v>
       </c>
       <c r="CB249" s="418" t="n">
         <v>3015.9120409666</v>
@@ -49752,25 +49752,25 @@
         </is>
       </c>
       <c r="AK250" s="435" t="n">
-        <v>500699.1934400753</v>
+        <v>500699.1934400751</v>
       </c>
       <c r="AL250" s="408" t="n">
-        <v>470981.9918168658</v>
+        <v>470981.9918168657</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>514533.4454606615</v>
+        <v>514533.4454606617</v>
       </c>
       <c r="AN250" s="408" t="n">
-        <v>560230.254048805</v>
+        <v>560230.2540488049</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>611485.4023741343</v>
+        <v>611485.4023741344</v>
       </c>
       <c r="AP250" s="436" t="n">
-        <v>1595.934018941659</v>
+        <v>1595.934018941658</v>
       </c>
       <c r="AQ250" s="437" t="n">
-        <v>1569.022329061861</v>
+        <v>1569.02232906186</v>
       </c>
       <c r="AR250" s="437" t="n">
         <v>1706.589899983435</v>
@@ -49787,25 +49787,25 @@
         </is>
       </c>
       <c r="BB250" s="439" t="n">
-        <v>500699.1934400753</v>
+        <v>500699.1934400751</v>
       </c>
       <c r="BC250" s="440" t="n">
-        <v>470981.9918168658</v>
+        <v>470981.9918168657</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>514533.4454606615</v>
+        <v>514533.4454606617</v>
       </c>
       <c r="BE250" s="440" t="n">
-        <v>560230.254048805</v>
+        <v>560230.2540488049</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>611485.4023741343</v>
+        <v>611485.4023741344</v>
       </c>
       <c r="BG250" s="442" t="n">
-        <v>1595.934018941659</v>
+        <v>1595.934018941658</v>
       </c>
       <c r="BH250" s="443" t="n">
-        <v>1569.022329061861</v>
+        <v>1569.02232906186</v>
       </c>
       <c r="BI250" s="443" t="n">
         <v>1706.589899983435</v>
@@ -49825,13 +49825,13 @@
         <v>500845.7947322577</v>
       </c>
       <c r="BT250" s="440" t="n">
-        <v>472219.6385785877</v>
+        <v>472219.6385785876</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>517101.5044096495</v>
+        <v>517101.5044096496</v>
       </c>
       <c r="BV250" s="440" t="n">
-        <v>564300.9875857062</v>
+        <v>564300.9875857061</v>
       </c>
       <c r="BW250" s="441" t="n">
         <v>617393.3372501316</v>
@@ -51954,22 +51954,22 @@
         <v>117930.9315359258</v>
       </c>
       <c r="AO264" s="380" t="n">
-        <v>120363.4657088641</v>
+        <v>120363.4657088642</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>745.5505766402586</v>
+        <v>745.550576640258</v>
       </c>
       <c r="AQ264" s="372" t="n">
-        <v>800.164541631652</v>
+        <v>800.1645416316517</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>853.5318245278921</v>
+        <v>853.5318245278912</v>
       </c>
       <c r="AS264" s="372" t="n">
         <v>907.7107505683691</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>980.9518566054221</v>
+        <v>980.951856605423</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51989,22 +51989,22 @@
         <v>117930.9315359258</v>
       </c>
       <c r="BF264" s="392" t="n">
-        <v>120363.4657088641</v>
+        <v>120363.4657088642</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>745.5505766402586</v>
+        <v>745.550576640258</v>
       </c>
       <c r="BH264" s="372" t="n">
-        <v>800.164541631652</v>
+        <v>800.1645416316517</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>853.5318245278921</v>
+        <v>853.5318245278912</v>
       </c>
       <c r="BJ264" s="372" t="n">
         <v>907.7107505683691</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>980.9518566054221</v>
+        <v>980.951856605423</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52027,25 +52027,25 @@
         <v>121312.5040357627</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>745.5505766402586</v>
+        <v>745.550576640258</v>
       </c>
       <c r="BY264" s="372" t="n">
-        <v>800.164541631652</v>
+        <v>800.1645416316517</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>853.5318245278921</v>
+        <v>853.5318245278912</v>
       </c>
       <c r="CA264" s="372" t="n">
         <v>907.7107505683691</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>980.9518566054221</v>
+        <v>980.951856605423</v>
       </c>
       <c r="CI264" s="396" t="n">
         <v>1.000000000004931</v>
       </c>
       <c r="CJ264" s="397" t="n">
-        <v>0.9999999999883409</v>
+        <v>0.9999999999883411</v>
       </c>
       <c r="CK264" s="397" t="n">
         <v>0.9999999999917994</v>
@@ -52060,22 +52060,22 @@
         <v>0.9999873853678014</v>
       </c>
       <c r="CO264" s="103" t="n">
-        <v>1.000000000006277</v>
+        <v>1.000000000006278</v>
       </c>
       <c r="CP264" s="103" t="n">
-        <v>0.9999999999995002</v>
+        <v>0.9999999999995005</v>
       </c>
       <c r="CQ264" s="103" t="n">
         <v>1.000000000000478</v>
       </c>
       <c r="CR264" s="104" t="n">
-        <v>1.000000000000483</v>
+        <v>1.000000000000482</v>
       </c>
       <c r="CT264" s="396" t="n">
         <v>1.000000000004931</v>
       </c>
       <c r="CU264" s="397" t="n">
-        <v>0.9999999999883409</v>
+        <v>0.9999999999883411</v>
       </c>
       <c r="CV264" s="397" t="n">
         <v>0.9999999999917994</v>
@@ -52093,13 +52093,13 @@
         <v>1.00000000000242</v>
       </c>
       <c r="DA264" s="103" t="n">
-        <v>0.9999999999934642</v>
+        <v>0.9999999999934645</v>
       </c>
       <c r="DB264" s="103" t="n">
         <v>0.999999999995553</v>
       </c>
       <c r="DC264" s="104" t="n">
-        <v>0.9999999999994758</v>
+        <v>0.9999999999994756</v>
       </c>
       <c r="DE264" s="511" t="n">
         <v>0</v>
@@ -52117,19 +52117,19 @@
         <v>0</v>
       </c>
       <c r="DK264" s="391" t="n">
-        <v>51470.90723855192</v>
+        <v>51470.90723855189</v>
       </c>
       <c r="DL264" s="375" t="n">
-        <v>45635.36296202311</v>
+        <v>45635.36296202309</v>
       </c>
       <c r="DM264" s="375" t="n">
-        <v>48298.66965804058</v>
+        <v>48298.66965804056</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>48006.25177548523</v>
+        <v>48006.25177548522</v>
       </c>
       <c r="DO264" s="392" t="n">
-        <v>47632.4859833645</v>
+        <v>47632.48598336448</v>
       </c>
     </row>
     <row r="265">
@@ -52212,7 +52212,7 @@
         <v>172551.8381675001</v>
       </c>
       <c r="AL265" s="368" t="n">
-        <v>179603.8868293243</v>
+        <v>179603.8868293242</v>
       </c>
       <c r="AM265" s="368" t="n">
         <v>195568.7596927182</v>
@@ -52227,16 +52227,16 @@
         <v>2114.76287386404</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>2255.258824119944</v>
+        <v>2255.258824119943</v>
       </c>
       <c r="AR265" s="372" t="n">
         <v>2385.816415065269</v>
       </c>
       <c r="AS265" s="372" t="n">
-        <v>2524.54764012486</v>
+        <v>2524.547640124859</v>
       </c>
       <c r="AT265" s="382" t="n">
-        <v>2679.065588590509</v>
+        <v>2679.06558859051</v>
       </c>
       <c r="BA265" s="101" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>172551.8381675001</v>
       </c>
       <c r="BC265" s="375" t="n">
-        <v>179603.8868293243</v>
+        <v>179603.8868293242</v>
       </c>
       <c r="BD265" s="375" t="n">
         <v>195568.7596927182</v>
@@ -52262,16 +52262,16 @@
         <v>2114.76287386404</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>2255.258824119944</v>
+        <v>2255.258824119943</v>
       </c>
       <c r="BI265" s="372" t="n">
         <v>2385.816415065269</v>
       </c>
       <c r="BJ265" s="372" t="n">
-        <v>2524.54764012486</v>
+        <v>2524.547640124859</v>
       </c>
       <c r="BK265" s="387" t="n">
-        <v>2679.065588590509</v>
+        <v>2679.06558859051</v>
       </c>
       <c r="BR265" s="101" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>172806.1060695505</v>
       </c>
       <c r="BT265" s="375" t="n">
-        <v>180295.7887207969</v>
+        <v>180295.7887207968</v>
       </c>
       <c r="BU265" s="375" t="n">
         <v>196800.5059366164</v>
@@ -52291,22 +52291,22 @@
         <v>216739.6677239698</v>
       </c>
       <c r="BW265" s="392" t="n">
-        <v>238022.8751124911</v>
+        <v>238022.8751124912</v>
       </c>
       <c r="BX265" s="386" t="n">
         <v>2114.76287386404</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>2255.258824119944</v>
+        <v>2255.258824119943</v>
       </c>
       <c r="BZ265" s="372" t="n">
         <v>2385.816415065269</v>
       </c>
       <c r="CA265" s="372" t="n">
-        <v>2524.54764012486</v>
+        <v>2524.547640124859</v>
       </c>
       <c r="CB265" s="387" t="n">
-        <v>2679.065588590509</v>
+        <v>2679.06558859051</v>
       </c>
       <c r="CI265" s="396" t="n">
         <v>1.000000000036132</v>
@@ -52321,13 +52321,13 @@
         <v>1.000000000000422</v>
       </c>
       <c r="CM265" s="398" t="n">
-        <v>0.9999999999879453</v>
+        <v>0.9999999999879455</v>
       </c>
       <c r="CN265" s="102" t="n">
-        <v>0.9999791689592888</v>
+        <v>0.9999791689592887</v>
       </c>
       <c r="CO265" s="103" t="n">
-        <v>0.9999999999962768</v>
+        <v>0.9999999999962776</v>
       </c>
       <c r="CP265" s="103" t="n">
         <v>1.000000000004635</v>
@@ -52336,7 +52336,7 @@
         <v>0.9999999999975464</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>0.9999999999884865</v>
+        <v>0.9999999999884861</v>
       </c>
       <c r="CT265" s="396" t="n">
         <v>1.000000000036132</v>
@@ -52351,13 +52351,13 @@
         <v>1.000000000000422</v>
       </c>
       <c r="CX265" s="398" t="n">
-        <v>0.9999999999879453</v>
+        <v>0.9999999999879455</v>
       </c>
       <c r="CY265" s="102" t="n">
         <v>1.000000000004148</v>
       </c>
       <c r="CZ265" s="103" t="n">
-        <v>0.9999999999956886</v>
+        <v>0.999999999995689</v>
       </c>
       <c r="DA265" s="103" t="n">
         <v>1.000000000004899</v>
@@ -52366,7 +52366,7 @@
         <v>0.999999999997966</v>
       </c>
       <c r="DC265" s="104" t="n">
-        <v>0.9999999999885584</v>
+        <v>0.999999999988558</v>
       </c>
       <c r="DE265" s="391" t="n">
         <v>0</v>
@@ -52384,10 +52384,10 @@
         <v>0</v>
       </c>
       <c r="DK265" s="391" t="n">
-        <v>41067.18882522402</v>
+        <v>41067.18882522401</v>
       </c>
       <c r="DL265" s="375" t="n">
-        <v>36821.37305297976</v>
+        <v>36821.37305297975</v>
       </c>
       <c r="DM265" s="375" t="n">
         <v>41785.52761424545</v>
@@ -52396,7 +52396,7 @@
         <v>47557.42876343562</v>
       </c>
       <c r="DO265" s="392" t="n">
-        <v>52673.28590222183</v>
+        <v>52673.28590222182</v>
       </c>
     </row>
     <row r="266">
@@ -52479,7 +52479,7 @@
         <v>157813.7661646547</v>
       </c>
       <c r="AL266" s="368" t="n">
-        <v>174261.8891516261</v>
+        <v>174261.8891516262</v>
       </c>
       <c r="AM266" s="368" t="n">
         <v>197065.9005779591</v>
@@ -52491,19 +52491,19 @@
         <v>248391.8019773487</v>
       </c>
       <c r="AP266" s="381" t="n">
-        <v>2065.919759979674</v>
+        <v>2065.919759979671</v>
       </c>
       <c r="AQ266" s="372" t="n">
-        <v>2200.36836664607</v>
+        <v>2200.368366646069</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2410.013622936441</v>
+        <v>2410.013622936443</v>
       </c>
       <c r="AS266" s="372" t="n">
-        <v>2756.207409655986</v>
+        <v>2756.207409655985</v>
       </c>
       <c r="AT266" s="382" t="n">
-        <v>2961.659664538559</v>
+        <v>2961.65966453856</v>
       </c>
       <c r="BA266" s="111" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>157813.7661646547</v>
       </c>
       <c r="BC266" s="375" t="n">
-        <v>174261.8891516261</v>
+        <v>174261.8891516262</v>
       </c>
       <c r="BD266" s="375" t="n">
         <v>197065.9005779591</v>
@@ -52526,19 +52526,19 @@
         <v>248391.8019773487</v>
       </c>
       <c r="BG266" s="386" t="n">
-        <v>2065.919759979674</v>
+        <v>2065.919759979671</v>
       </c>
       <c r="BH266" s="372" t="n">
-        <v>2200.36836664607</v>
+        <v>2200.368366646069</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2410.013622936441</v>
+        <v>2410.013622936443</v>
       </c>
       <c r="BJ266" s="372" t="n">
-        <v>2756.207409655986</v>
+        <v>2756.207409655985</v>
       </c>
       <c r="BK266" s="387" t="n">
-        <v>2961.659664538559</v>
+        <v>2961.65966453856</v>
       </c>
       <c r="BR266" s="111" t="inlineStr">
         <is>
@@ -52549,10 +52549,10 @@
         <v>158042.0144071814</v>
       </c>
       <c r="BT266" s="375" t="n">
-        <v>174806.782848244</v>
+        <v>174806.7828482441</v>
       </c>
       <c r="BU266" s="375" t="n">
-        <v>198099.827282697</v>
+        <v>198099.8272826971</v>
       </c>
       <c r="BV266" s="375" t="n">
         <v>222315.7395968188</v>
@@ -52561,25 +52561,25 @@
         <v>250874.0988206003</v>
       </c>
       <c r="BX266" s="386" t="n">
-        <v>2065.919759979674</v>
+        <v>2065.919759979671</v>
       </c>
       <c r="BY266" s="372" t="n">
-        <v>2200.36836664607</v>
+        <v>2200.368366646069</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2410.013622936441</v>
+        <v>2410.013622936443</v>
       </c>
       <c r="CA266" s="372" t="n">
-        <v>2756.207409655986</v>
+        <v>2756.207409655985</v>
       </c>
       <c r="CB266" s="387" t="n">
-        <v>2961.659664538559</v>
+        <v>2961.65966453856</v>
       </c>
       <c r="CI266" s="396" t="n">
         <v>1.000000000017503</v>
       </c>
       <c r="CJ266" s="397" t="n">
-        <v>0.9999999999824443</v>
+        <v>0.9999999999824444</v>
       </c>
       <c r="CK266" s="397" t="n">
         <v>1.000000000002067</v>
@@ -52591,7 +52591,7 @@
         <v>1.00000000001521</v>
       </c>
       <c r="CN266" s="102" t="n">
-        <v>0.9999911678934661</v>
+        <v>0.999991167893466</v>
       </c>
       <c r="CO266" s="103" t="n">
         <v>1.000000000002248</v>
@@ -52609,7 +52609,7 @@
         <v>1.000000000017503</v>
       </c>
       <c r="CU266" s="397" t="n">
-        <v>0.9999999999824443</v>
+        <v>0.9999999999824444</v>
       </c>
       <c r="CV266" s="397" t="n">
         <v>1.000000000002067</v>
@@ -52743,34 +52743,34 @@
         </is>
       </c>
       <c r="AK267" s="435" t="n">
-        <v>56453.6925031906</v>
+        <v>56453.69250319048</v>
       </c>
       <c r="AL267" s="408" t="n">
         <v>5802.278701392817</v>
       </c>
       <c r="AM267" s="408" t="n">
-        <v>6277.540448684245</v>
+        <v>6277.540448684362</v>
       </c>
       <c r="AN267" s="408" t="n">
-        <v>6725.091417432996</v>
+        <v>6725.091417432879</v>
       </c>
       <c r="AO267" s="409" t="n">
         <v>7204.550084947376</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>18785.44383888467</v>
+        <v>18785.44383888465</v>
       </c>
       <c r="AQ267" s="411" t="n">
-        <v>2605.258215000079</v>
+        <v>2605.258215000075</v>
       </c>
       <c r="AR267" s="411" t="n">
-        <v>2735.52112574995</v>
+        <v>2735.52112575</v>
       </c>
       <c r="AS267" s="411" t="n">
-        <v>2872.297182037556</v>
+        <v>2872.29718203751</v>
       </c>
       <c r="AT267" s="412" t="n">
-        <v>3015.9120411394</v>
+        <v>3015.912041139396</v>
       </c>
       <c r="BA267" s="111" t="inlineStr">
         <is>
@@ -52778,34 +52778,34 @@
         </is>
       </c>
       <c r="BB267" s="419" t="n">
-        <v>56453.6925031906</v>
+        <v>56453.69250319048</v>
       </c>
       <c r="BC267" s="420" t="n">
         <v>5802.278701392817</v>
       </c>
       <c r="BD267" s="420" t="n">
-        <v>6277.540448684245</v>
+        <v>6277.540448684362</v>
       </c>
       <c r="BE267" s="420" t="n">
-        <v>6725.091417432996</v>
+        <v>6725.091417432879</v>
       </c>
       <c r="BF267" s="421" t="n">
         <v>7204.550084947376</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>18785.44383888467</v>
+        <v>18785.44383888465</v>
       </c>
       <c r="BH267" s="417" t="n">
-        <v>2605.258215000079</v>
+        <v>2605.258215000075</v>
       </c>
       <c r="BI267" s="417" t="n">
-        <v>2735.52112574995</v>
+        <v>2735.52112575</v>
       </c>
       <c r="BJ267" s="417" t="n">
-        <v>2872.297182037556</v>
+        <v>2872.29718203751</v>
       </c>
       <c r="BK267" s="418" t="n">
-        <v>3015.9120411394</v>
+        <v>3015.912041139396</v>
       </c>
       <c r="BR267" s="111" t="inlineStr">
         <is>
@@ -52813,34 +52813,34 @@
         </is>
       </c>
       <c r="BS267" s="419" t="n">
-        <v>56336.58064497267</v>
+        <v>56336.58064497256</v>
       </c>
       <c r="BT267" s="420" t="n">
         <v>5785.615091863735</v>
       </c>
       <c r="BU267" s="420" t="n">
-        <v>6259.511931230442</v>
+        <v>6259.511931230558</v>
       </c>
       <c r="BV267" s="420" t="n">
-        <v>6705.77757485584</v>
+        <v>6705.777574855723</v>
       </c>
       <c r="BW267" s="421" t="n">
         <v>7183.859281277524</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>18785.44383888467</v>
+        <v>18785.44383888465</v>
       </c>
       <c r="BY267" s="417" t="n">
-        <v>2605.258215000079</v>
+        <v>2605.258215000075</v>
       </c>
       <c r="BZ267" s="417" t="n">
-        <v>2735.52112574995</v>
+        <v>2735.52112575</v>
       </c>
       <c r="CA267" s="417" t="n">
-        <v>2872.297182037556</v>
+        <v>2872.29718203751</v>
       </c>
       <c r="CB267" s="418" t="n">
-        <v>3015.9120411394</v>
+        <v>3015.912041139396</v>
       </c>
       <c r="CI267" s="422" t="n">
         <v>1</v>
@@ -52858,22 +52858,22 @@
         <v>1</v>
       </c>
       <c r="CN267" s="132" t="n">
-        <v>1.000000000142769</v>
+        <v>1.000000000142771</v>
       </c>
       <c r="CO267" s="133" t="n">
         <v>1.000000000572679</v>
       </c>
       <c r="CP267" s="133" t="n">
-        <v>0.9999999996296619</v>
+        <v>0.9999999996296435</v>
       </c>
       <c r="CQ267" s="133" t="n">
-        <v>0.9999999994771882</v>
+        <v>0.9999999994772057</v>
       </c>
       <c r="CR267" s="134" t="n">
         <v>0.9999999997398088</v>
       </c>
       <c r="CT267" s="422" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="CU267" s="423" t="n">
         <v>1</v>
@@ -52888,16 +52888,16 @@
         <v>1</v>
       </c>
       <c r="CY267" s="132" t="n">
-        <v>0.9999999999997268</v>
+        <v>0.9999999999997269</v>
       </c>
       <c r="CZ267" s="133" t="n">
-        <v>0.9999999999994045</v>
+        <v>0.9999999999994043</v>
       </c>
       <c r="DA267" s="133" t="n">
         <v>1.000000000000557</v>
       </c>
       <c r="DB267" s="133" t="n">
-        <v>0.9999999999991758</v>
+        <v>0.999999999999176</v>
       </c>
       <c r="DC267" s="134" t="n">
         <v>1.000000000000095</v>
@@ -52918,19 +52918,19 @@
         <v>0</v>
       </c>
       <c r="DK267" s="419" t="n">
-        <v>4417.155833637554</v>
+        <v>4417.155833637553</v>
       </c>
       <c r="DL267" s="420" t="n">
-        <v>4764.761531629004</v>
+        <v>4764.761531629003</v>
       </c>
       <c r="DM267" s="420" t="n">
-        <v>5167.082612404439</v>
+        <v>5167.082612404438</v>
       </c>
       <c r="DN267" s="420" t="n">
-        <v>5549.162946288739</v>
+        <v>5549.162946288738</v>
       </c>
       <c r="DO267" s="421" t="n">
-        <v>5955.299443328723</v>
+        <v>5955.299443328721</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" thickBot="1">
@@ -53010,34 +53010,34 @@
         </is>
       </c>
       <c r="AK268" s="435" t="n">
-        <v>500699.1934400753</v>
+        <v>500699.1934400751</v>
       </c>
       <c r="AL268" s="408" t="n">
-        <v>470981.9918168658</v>
+        <v>470981.9918168657</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>514533.4454606615</v>
+        <v>514533.4454606617</v>
       </c>
       <c r="AN268" s="408" t="n">
-        <v>560230.254048805</v>
+        <v>560230.2540488049</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>611485.4023741343</v>
+        <v>611485.4023741344</v>
       </c>
       <c r="AP268" s="436" t="n">
-        <v>1595.934018942289</v>
+        <v>1595.934018942287</v>
       </c>
       <c r="AQ268" s="437" t="n">
-        <v>1569.022329063147</v>
+        <v>1569.022329063146</v>
       </c>
       <c r="AR268" s="437" t="n">
         <v>1706.589899976062</v>
       </c>
       <c r="AS268" s="437" t="n">
-        <v>1883.427091547452</v>
+        <v>1883.427091547451</v>
       </c>
       <c r="AT268" s="438" t="n">
-        <v>2059.761192982156</v>
+        <v>2059.761192982157</v>
       </c>
       <c r="BA268" s="155" t="inlineStr">
         <is>
@@ -53045,34 +53045,34 @@
         </is>
       </c>
       <c r="BB268" s="439" t="n">
-        <v>500699.1934400753</v>
+        <v>500699.1934400751</v>
       </c>
       <c r="BC268" s="440" t="n">
-        <v>470981.9918168658</v>
+        <v>470981.9918168657</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>514533.4454606615</v>
+        <v>514533.4454606617</v>
       </c>
       <c r="BE268" s="440" t="n">
-        <v>560230.254048805</v>
+        <v>560230.2540488049</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>611485.4023741343</v>
+        <v>611485.4023741344</v>
       </c>
       <c r="BG268" s="442" t="n">
-        <v>1595.934018942289</v>
+        <v>1595.934018942287</v>
       </c>
       <c r="BH268" s="443" t="n">
-        <v>1569.022329063147</v>
+        <v>1569.022329063146</v>
       </c>
       <c r="BI268" s="443" t="n">
         <v>1706.589899976062</v>
       </c>
       <c r="BJ268" s="443" t="n">
-        <v>1883.427091547452</v>
+        <v>1883.427091547451</v>
       </c>
       <c r="BK268" s="444" t="n">
-        <v>2059.761192982156</v>
+        <v>2059.761192982157</v>
       </c>
       <c r="BR268" s="155" t="inlineStr">
         <is>
@@ -53080,34 +53080,34 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>500845.7947322577</v>
+        <v>500845.7947322576</v>
       </c>
       <c r="BT268" s="440" t="n">
-        <v>472219.6385785877</v>
+        <v>472219.6385785876</v>
       </c>
       <c r="BU268" s="440" t="n">
-        <v>517101.5044096495</v>
+        <v>517101.5044096496</v>
       </c>
       <c r="BV268" s="440" t="n">
-        <v>564300.9875857062</v>
+        <v>564300.9875857061</v>
       </c>
       <c r="BW268" s="441" t="n">
         <v>617393.3372501316</v>
       </c>
       <c r="BX268" s="442" t="n">
-        <v>1596.752449216726</v>
+        <v>1596.752449216724</v>
       </c>
       <c r="BY268" s="443" t="n">
-        <v>1570.164229810027</v>
+        <v>1570.164229810026</v>
       </c>
       <c r="BZ268" s="443" t="n">
         <v>1707.664593191015</v>
       </c>
       <c r="CA268" s="443" t="n">
-        <v>1884.523741338132</v>
+        <v>1884.523741338131</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>2060.705553828572</v>
+        <v>2060.705553828573</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53125,7 +53125,7 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>183894.2944744075</v>
+        <v>183894.2944744074</v>
       </c>
       <c r="DL268" s="440" t="n">
         <v>185270.0027580661</v>
@@ -53137,7 +53137,7 @@
         <v>244491.9258501469</v>
       </c>
       <c r="DO268" s="441" t="n">
-        <v>273672.1247263268</v>
+        <v>273672.1247263267</v>
       </c>
     </row>
     <row r="269">
@@ -54062,7 +54062,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="AQ276" s="179" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AR276" s="179" t="n">
         <v>39.06775910552674</v>
@@ -54077,7 +54077,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="AV276" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AW276" s="190" t="n">
         <v>39.06775910552674</v>
@@ -54112,7 +54112,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="BH276" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BI276" s="190" t="n">
         <v>39.06775910552674</v>
@@ -54127,7 +54127,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="BM276" s="200" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BN276" s="200" t="n">
         <v>39.06775910552674</v>
@@ -54162,7 +54162,7 @@
         <v>95.97568964536502</v>
       </c>
       <c r="BY276" s="190" t="n">
-        <v>75.09334929877637</v>
+        <v>75.09334929877639</v>
       </c>
       <c r="BZ276" s="190" t="n">
         <v>39.62531155453665</v>
@@ -54177,7 +54177,7 @@
         <v>95.97568964536502</v>
       </c>
       <c r="CD276" s="200" t="n">
-        <v>75.09334929877637</v>
+        <v>75.09334929877639</v>
       </c>
       <c r="CE276" s="200" t="n">
         <v>39.62531155453665</v>
@@ -54342,7 +54342,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="AQ277" s="179" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="AR277" s="179" t="n">
         <v>33.05225969113863</v>
@@ -54357,7 +54357,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="AV277" s="190" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="AW277" s="190" t="n">
         <v>33.05225969113863</v>
@@ -54392,7 +54392,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="BH277" s="190" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="BI277" s="190" t="n">
         <v>33.05225969113863</v>
@@ -54407,7 +54407,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="BM277" s="190" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="BN277" s="190" t="n">
         <v>33.05225969113863</v>
@@ -54442,7 +54442,7 @@
         <v>61.5553433025013</v>
       </c>
       <c r="BY277" s="190" t="n">
-        <v>47.28054258672603</v>
+        <v>47.28054258672604</v>
       </c>
       <c r="BZ277" s="190" t="n">
         <v>33.13520019411198</v>
@@ -54457,7 +54457,7 @@
         <v>61.5553433025013</v>
       </c>
       <c r="CD277" s="190" t="n">
-        <v>47.28054258672603</v>
+        <v>47.28054258672604</v>
       </c>
       <c r="CE277" s="190" t="n">
         <v>33.13520019411198</v>
@@ -54631,7 +54631,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="AT278" s="195" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="AU278" s="190" t="n">
         <v>116.3804435035016</v>
@@ -54646,7 +54646,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="AY278" s="196" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="BA278" s="111" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="BK278" s="198" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="BL278" s="197" t="n">
         <v>116.3804435035016</v>
@@ -54696,7 +54696,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="BP278" s="198" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="BR278" s="111" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>5.447342876795428</v>
       </c>
       <c r="AL279" s="207" t="n">
-        <v>7.015258528875048</v>
+        <v>7.015258528875047</v>
       </c>
       <c r="AM279" s="207" t="n">
         <v>13.59238996021135</v>
@@ -54905,10 +54905,10 @@
         <v>28.00612562612424</v>
       </c>
       <c r="AR279" s="207" t="n">
-        <v>22.54630249853269</v>
+        <v>22.54630249853268</v>
       </c>
       <c r="AS279" s="207" t="n">
-        <v>19.98850538056062</v>
+        <v>19.98850538056063</v>
       </c>
       <c r="AT279" s="208" t="n">
         <v>20.30610144505344</v>
@@ -54917,13 +54917,13 @@
         <v>33.28550242320334</v>
       </c>
       <c r="AV279" s="209" t="n">
-        <v>35.0213841549993</v>
+        <v>35.02138415499929</v>
       </c>
       <c r="AW279" s="209" t="n">
         <v>36.13869245874403</v>
       </c>
       <c r="AX279" s="209" t="n">
-        <v>37.10430664523566</v>
+        <v>37.10430664523567</v>
       </c>
       <c r="AY279" s="210" t="n">
         <v>38.17141369260739</v>
@@ -54937,7 +54937,7 @@
         <v>5.447342876795428</v>
       </c>
       <c r="BC279" s="212" t="n">
-        <v>7.015258528875048</v>
+        <v>7.015258528875047</v>
       </c>
       <c r="BD279" s="212" t="n">
         <v>13.59238996021135</v>
@@ -54955,10 +54955,10 @@
         <v>28.00612562612424</v>
       </c>
       <c r="BI279" s="212" t="n">
-        <v>22.54630249853269</v>
+        <v>22.54630249853268</v>
       </c>
       <c r="BJ279" s="212" t="n">
-        <v>19.98850538056062</v>
+        <v>19.98850538056063</v>
       </c>
       <c r="BK279" s="213" t="n">
         <v>20.30610144505344</v>
@@ -54967,13 +54967,13 @@
         <v>33.28550242320334</v>
       </c>
       <c r="BM279" s="212" t="n">
-        <v>35.0213841549993</v>
+        <v>35.02138415499929</v>
       </c>
       <c r="BN279" s="212" t="n">
         <v>36.13869245874403</v>
       </c>
       <c r="BO279" s="212" t="n">
-        <v>37.10430664523566</v>
+        <v>37.10430664523567</v>
       </c>
       <c r="BP279" s="213" t="n">
         <v>38.17141369260739</v>
@@ -55005,7 +55005,7 @@
         <v>28.11758592367503</v>
       </c>
       <c r="BZ279" s="212" t="n">
-        <v>22.69744779230261</v>
+        <v>22.6974477923026</v>
       </c>
       <c r="CA279" s="212" t="n">
         <v>20.18075109354715</v>
@@ -55079,7 +55079,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="H280" s="215" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="I280" s="215" t="n">
         <v>258.2717129066097</v>
@@ -55129,7 +55129,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="Y280" s="217" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="Z280" s="218" t="n">
         <v>258.2717129066097</v>
@@ -55167,7 +55167,7 @@
         <v>5.447342876795428</v>
       </c>
       <c r="AL280" s="207" t="n">
-        <v>7.015258528875048</v>
+        <v>7.015258528875047</v>
       </c>
       <c r="AM280" s="207" t="n">
         <v>13.59238996021135</v>
@@ -55179,13 +55179,13 @@
         <v>17.86531224755395</v>
       </c>
       <c r="AP280" s="206" t="n">
-        <v>301.0218825085427</v>
+        <v>301.0218825085428</v>
       </c>
       <c r="AQ280" s="207" t="n">
-        <v>259.9722993504571</v>
+        <v>259.972299350457</v>
       </c>
       <c r="AR280" s="207" t="n">
-        <v>195.9572318509365</v>
+        <v>195.9572318509364</v>
       </c>
       <c r="AS280" s="207" t="n">
         <v>184.5460315779278</v>
@@ -55217,7 +55217,7 @@
         <v>5.447342876795428</v>
       </c>
       <c r="BC280" s="222" t="n">
-        <v>7.015258528875048</v>
+        <v>7.015258528875047</v>
       </c>
       <c r="BD280" s="222" t="n">
         <v>13.59238996021135</v>
@@ -55229,13 +55229,13 @@
         <v>17.86531224755395</v>
       </c>
       <c r="BG280" s="221" t="n">
-        <v>301.0218825085427</v>
+        <v>301.0218825085428</v>
       </c>
       <c r="BH280" s="222" t="n">
-        <v>259.9722993504571</v>
+        <v>259.972299350457</v>
       </c>
       <c r="BI280" s="222" t="n">
-        <v>195.9572318509365</v>
+        <v>195.9572318509364</v>
       </c>
       <c r="BJ280" s="222" t="n">
         <v>184.5460315779278</v>
@@ -55285,7 +55285,7 @@
         <v>260.799224354792</v>
       </c>
       <c r="BZ280" s="222" t="n">
-        <v>196.8242093675346</v>
+        <v>196.8242093675345</v>
       </c>
       <c r="CA280" s="222" t="n">
         <v>185.4509482370725</v>
@@ -58309,7 +58309,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="AQ294" s="179" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AR294" s="179" t="n">
         <v>39.06775910552674</v>
@@ -58324,7 +58324,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="AV294" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AW294" s="190" t="n">
         <v>39.06775910552674</v>
@@ -58359,7 +58359,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="BH294" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BI294" s="190" t="n">
         <v>39.06775910552674</v>
@@ -58374,7 +58374,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="BM294" s="200" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BN294" s="200" t="n">
         <v>39.06775910552674</v>
@@ -58409,7 +58409,7 @@
         <v>95.97568964536502</v>
       </c>
       <c r="BY294" s="190" t="n">
-        <v>75.09334929877636</v>
+        <v>75.09334929877637</v>
       </c>
       <c r="BZ294" s="190" t="n">
         <v>39.62531155453665</v>
@@ -58424,7 +58424,7 @@
         <v>95.97568964536502</v>
       </c>
       <c r="CD294" s="200" t="n">
-        <v>75.09334929877636</v>
+        <v>75.09334929877637</v>
       </c>
       <c r="CE294" s="200" t="n">
         <v>39.62531155453665</v>
@@ -58463,19 +58463,19 @@
         <v>2844</v>
       </c>
       <c r="CW294" s="199" t="n">
-        <v>0.6305845188212781</v>
+        <v>0.6305845188212807</v>
       </c>
       <c r="CX294" s="200" t="n">
-        <v>0.5588274414376452</v>
+        <v>0.5588274414376472</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>0.5575524490099095</v>
+        <v>0.5575524490099116</v>
       </c>
       <c r="CZ294" s="200" t="n">
-        <v>0.5519744899569327</v>
+        <v>0.5519744899569347</v>
       </c>
       <c r="DA294" s="201" t="n">
-        <v>0.539746239388267</v>
+        <v>0.5397462393882688</v>
       </c>
     </row>
     <row r="295">
@@ -58604,7 +58604,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="AQ295" s="179" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="AR295" s="179" t="n">
         <v>33.05225969113863</v>
@@ -58619,7 +58619,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="AV295" s="190" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="AW295" s="190" t="n">
         <v>33.05225969113863</v>
@@ -58654,7 +58654,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="BH295" s="190" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="BI295" s="190" t="n">
         <v>33.05225969113863</v>
@@ -58669,7 +58669,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="BM295" s="190" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="BN295" s="190" t="n">
         <v>33.05225969113863</v>
@@ -58701,10 +58701,10 @@
         <v>0</v>
       </c>
       <c r="BX295" s="197" t="n">
-        <v>61.55534330250129</v>
+        <v>61.5553433025013</v>
       </c>
       <c r="BY295" s="190" t="n">
-        <v>47.28054258672603</v>
+        <v>47.28054258672604</v>
       </c>
       <c r="BZ295" s="190" t="n">
         <v>33.13520019411198</v>
@@ -58716,10 +58716,10 @@
         <v>30.60683374054721</v>
       </c>
       <c r="CC295" s="197" t="n">
-        <v>61.55534330250129</v>
+        <v>61.5553433025013</v>
       </c>
       <c r="CD295" s="190" t="n">
-        <v>47.28054258672603</v>
+        <v>47.28054258672604</v>
       </c>
       <c r="CE295" s="190" t="n">
         <v>33.13520019411198</v>
@@ -58758,19 +58758,19 @@
         <v>6366</v>
       </c>
       <c r="CW295" s="197" t="n">
-        <v>0.09716897041179687</v>
+        <v>0.09716897041179728</v>
       </c>
       <c r="CX295" s="190" t="n">
-        <v>0.08086620964934652</v>
+        <v>0.08086620964934688</v>
       </c>
       <c r="CY295" s="190" t="n">
-        <v>0.08294050297335381</v>
+        <v>0.0829405029733542</v>
       </c>
       <c r="CZ295" s="190" t="n">
-        <v>0.08529935814312077</v>
+        <v>0.0852993581431212</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>0.07434357734897762</v>
+        <v>0.07434357734897806</v>
       </c>
     </row>
     <row r="296">
@@ -58908,7 +58908,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="AT296" s="195" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="AU296" s="190" t="n">
         <v>116.3804435035016</v>
@@ -58923,7 +58923,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="AY296" s="196" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="BA296" s="111" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="BK296" s="198" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="BL296" s="197" t="n">
         <v>116.3804435035016</v>
@@ -58973,7 +58973,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="BP296" s="198" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="BR296" s="111" t="inlineStr">
         <is>
@@ -59053,19 +59053,19 @@
         <v>10888</v>
       </c>
       <c r="CW296" s="197" t="n">
-        <v>0.07538747908594198</v>
+        <v>0.07538747908594384</v>
       </c>
       <c r="CX296" s="190" t="n">
-        <v>0.07577105569712549</v>
+        <v>0.07577105569712757</v>
       </c>
       <c r="CY296" s="190" t="n">
-        <v>0.0753392708449033</v>
+        <v>0.07533927084490553</v>
       </c>
       <c r="CZ296" s="190" t="n">
-        <v>0.07539709805810332</v>
+        <v>0.07539709805810581</v>
       </c>
       <c r="DA296" s="198" t="n">
-        <v>0.0749527373991361</v>
+        <v>0.07495273739913856</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" thickBot="1">
@@ -59179,7 +59179,7 @@
         <v>5.447342876795428</v>
       </c>
       <c r="AL297" s="207" t="n">
-        <v>7.015258528875048</v>
+        <v>7.015258528875047</v>
       </c>
       <c r="AM297" s="207" t="n">
         <v>13.59238996021135</v>
@@ -59197,10 +59197,10 @@
         <v>28.00612562612424</v>
       </c>
       <c r="AR297" s="207" t="n">
-        <v>22.54630249853269</v>
+        <v>22.54630249853268</v>
       </c>
       <c r="AS297" s="207" t="n">
-        <v>19.98850538056062</v>
+        <v>19.98850538056063</v>
       </c>
       <c r="AT297" s="208" t="n">
         <v>20.30610144505344</v>
@@ -59209,13 +59209,13 @@
         <v>33.28550242320334</v>
       </c>
       <c r="AV297" s="209" t="n">
-        <v>35.0213841549993</v>
+        <v>35.02138415499929</v>
       </c>
       <c r="AW297" s="209" t="n">
         <v>36.13869245874403</v>
       </c>
       <c r="AX297" s="209" t="n">
-        <v>37.10430664523566</v>
+        <v>37.10430664523567</v>
       </c>
       <c r="AY297" s="210" t="n">
         <v>38.17141369260739</v>
@@ -59229,7 +59229,7 @@
         <v>5.447342876795428</v>
       </c>
       <c r="BC297" s="212" t="n">
-        <v>7.015258528875048</v>
+        <v>7.015258528875047</v>
       </c>
       <c r="BD297" s="212" t="n">
         <v>13.59238996021135</v>
@@ -59247,10 +59247,10 @@
         <v>28.00612562612424</v>
       </c>
       <c r="BI297" s="212" t="n">
-        <v>22.54630249853269</v>
+        <v>22.54630249853268</v>
       </c>
       <c r="BJ297" s="212" t="n">
-        <v>19.98850538056062</v>
+        <v>19.98850538056063</v>
       </c>
       <c r="BK297" s="213" t="n">
         <v>20.30610144505344</v>
@@ -59259,13 +59259,13 @@
         <v>33.28550242320334</v>
       </c>
       <c r="BM297" s="212" t="n">
-        <v>35.0213841549993</v>
+        <v>35.02138415499929</v>
       </c>
       <c r="BN297" s="212" t="n">
         <v>36.13869245874403</v>
       </c>
       <c r="BO297" s="212" t="n">
-        <v>37.10430664523566</v>
+        <v>37.10430664523567</v>
       </c>
       <c r="BP297" s="213" t="n">
         <v>38.17141369260739</v>
@@ -59297,7 +59297,7 @@
         <v>28.11758592367503</v>
       </c>
       <c r="BZ297" s="212" t="n">
-        <v>22.69744779230261</v>
+        <v>22.6974477923026</v>
       </c>
       <c r="CA297" s="212" t="n">
         <v>20.18075109354715</v>
@@ -59348,19 +59348,19 @@
         <v>2178</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>0.006234181061802671</v>
+        <v>0.006234181061802626</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.006396145085788257</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.00659052393494536</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760346054</v>
       </c>
       <c r="DA297" s="213" t="n">
-        <v>0.006860546125885923</v>
+        <v>0.006860546125885872</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" thickBot="1">
@@ -59386,7 +59386,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="H298" s="215" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="I298" s="215" t="n">
         <v>258.2717129066097</v>
@@ -59436,7 +59436,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="Y298" s="217" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="Z298" s="218" t="n">
         <v>258.2717129066097</v>
@@ -59474,7 +59474,7 @@
         <v>5.447342876795428</v>
       </c>
       <c r="AL298" s="207" t="n">
-        <v>7.015258528875048</v>
+        <v>7.015258528875047</v>
       </c>
       <c r="AM298" s="207" t="n">
         <v>13.59238996021135</v>
@@ -59486,13 +59486,13 @@
         <v>17.86531224755395</v>
       </c>
       <c r="AP298" s="206" t="n">
-        <v>301.0218825085427</v>
+        <v>301.0218825085428</v>
       </c>
       <c r="AQ298" s="207" t="n">
-        <v>259.9722993504571</v>
+        <v>259.972299350457</v>
       </c>
       <c r="AR298" s="207" t="n">
-        <v>195.9572318509365</v>
+        <v>195.9572318509364</v>
       </c>
       <c r="AS298" s="207" t="n">
         <v>184.5460315779278</v>
@@ -59524,7 +59524,7 @@
         <v>5.447342876795428</v>
       </c>
       <c r="BC298" s="222" t="n">
-        <v>7.015258528875048</v>
+        <v>7.015258528875047</v>
       </c>
       <c r="BD298" s="222" t="n">
         <v>13.59238996021135</v>
@@ -59536,13 +59536,13 @@
         <v>17.86531224755395</v>
       </c>
       <c r="BG298" s="221" t="n">
-        <v>301.0218825085427</v>
+        <v>301.0218825085428</v>
       </c>
       <c r="BH298" s="222" t="n">
-        <v>259.9722993504571</v>
+        <v>259.972299350457</v>
       </c>
       <c r="BI298" s="222" t="n">
-        <v>195.9572318509365</v>
+        <v>195.9572318509364</v>
       </c>
       <c r="BJ298" s="222" t="n">
         <v>184.5460315779278</v>
@@ -59589,10 +59589,10 @@
         <v>301.89782866277</v>
       </c>
       <c r="BY298" s="222" t="n">
-        <v>260.799224354792</v>
+        <v>260.7992243547919</v>
       </c>
       <c r="BZ298" s="222" t="n">
-        <v>196.8242093675346</v>
+        <v>196.8242093675345</v>
       </c>
       <c r="CA298" s="222" t="n">
         <v>185.4509482370725</v>
@@ -59643,19 +59643,19 @@
         <v>22276</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>0.8093751493808197</v>
+        <v>0.8093751493808246</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>0.7218608518699055</v>
+        <v>0.7218608518699099</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>0.722422746763112</v>
+        <v>0.7224227467631168</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>0.7193951259185029</v>
+        <v>0.7193951259185077</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>0.6959031002622666</v>
+        <v>0.6959031002622713</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -60440,7 +60440,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="AV303" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AW303" s="190" t="n">
         <v>39.06775910552674</v>
@@ -60490,7 +60490,7 @@
         <v>95.34510512654374</v>
       </c>
       <c r="BM303" s="200" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BN303" s="200" t="n">
         <v>39.06775910552674</v>
@@ -60522,34 +60522,34 @@
         <v>0</v>
       </c>
       <c r="BX303" s="462" t="n">
-        <v>0.08725993081426577</v>
+        <v>0.08725993081426575</v>
       </c>
       <c r="BY303" s="463" t="n">
-        <v>-0.007554203388694723</v>
+        <v>-0.007554203388694748</v>
       </c>
       <c r="BZ303" s="463" t="n">
-        <v>-0.01447804354785405</v>
+        <v>-0.0144780435478541</v>
       </c>
       <c r="CA303" s="463" t="n">
-        <v>-0.01724051582905627</v>
+        <v>-0.01724051582905633</v>
       </c>
       <c r="CB303" s="464" t="n">
-        <v>-0.01710261392903577</v>
+        <v>-0.01710261392903582</v>
       </c>
       <c r="CC303" s="199" t="n">
         <v>8.374832038305994</v>
       </c>
       <c r="CD303" s="200" t="n">
-        <v>-0.5672704337412529</v>
+        <v>-0.5672704337412549</v>
       </c>
       <c r="CE303" s="200" t="n">
-        <v>-0.5736969862838659</v>
+        <v>-0.573696986283868</v>
       </c>
       <c r="CF303" s="200" t="n">
-        <v>-0.5710071398196082</v>
+        <v>-0.5710071398196103</v>
       </c>
       <c r="CG303" s="201" t="n">
-        <v>-0.5582083824920799</v>
+        <v>-0.5582083824920819</v>
       </c>
     </row>
     <row r="304">
@@ -60692,7 +60692,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="AV304" s="190" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="AW304" s="190" t="n">
         <v>33.05225969113863</v>
@@ -60742,7 +60742,7 @@
         <v>61.4581743320895</v>
       </c>
       <c r="BM304" s="190" t="n">
-        <v>47.19967637707668</v>
+        <v>47.19967637707669</v>
       </c>
       <c r="BN304" s="190" t="n">
         <v>33.05225969113863</v>
@@ -60777,31 +60777,31 @@
         <v>0.08665162380508086</v>
       </c>
       <c r="BY304" s="463" t="n">
-        <v>-0.001716219262795569</v>
+        <v>-0.001716219262795576</v>
       </c>
       <c r="BZ304" s="463" t="n">
-        <v>-0.00251568746385052</v>
+        <v>-0.002515687463850532</v>
       </c>
       <c r="CA304" s="463" t="n">
-        <v>-0.002820435470910475</v>
+        <v>-0.002820435470910489</v>
       </c>
       <c r="CB304" s="464" t="n">
-        <v>-0.002440843770300763</v>
+        <v>-0.002440843770300778</v>
       </c>
       <c r="CC304" s="197" t="n">
         <v>5.333870451040946</v>
       </c>
       <c r="CD304" s="190" t="n">
-        <v>-0.08114377794276545</v>
+        <v>-0.08114377794276581</v>
       </c>
       <c r="CE304" s="190" t="n">
-        <v>-0.08335780774050484</v>
+        <v>-0.08335780774050523</v>
       </c>
       <c r="CF304" s="190" t="n">
-        <v>-0.08578052081382628</v>
+        <v>-0.08578052081382671</v>
       </c>
       <c r="CG304" s="198" t="n">
-        <v>-0.07470649946424586</v>
+        <v>-0.07470649946424632</v>
       </c>
     </row>
     <row r="305">
@@ -60953,7 +60953,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="AY305" s="196" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="BA305" s="111" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>101.6607994061495</v>
       </c>
       <c r="BP305" s="198" t="n">
-        <v>101.2016853030651</v>
+        <v>101.2016853030652</v>
       </c>
       <c r="BR305" s="111" t="inlineStr">
         <is>
@@ -61029,22 +61029,22 @@
         <v>0.152477692614416</v>
       </c>
       <c r="BY305" s="463" t="n">
-        <v>0.04912083905247052</v>
+        <v>0.04912083905247051</v>
       </c>
       <c r="BZ305" s="463" t="n">
-        <v>0.07514744396219603</v>
+        <v>0.07514744396219604</v>
       </c>
       <c r="CA305" s="463" t="n">
         <v>0.1051194925474117</v>
       </c>
       <c r="CB305" s="464" t="n">
-        <v>0.1481374028113323</v>
+        <v>0.1481374028113322</v>
       </c>
       <c r="CC305" s="197" t="n">
         <v>17.75691639971936</v>
       </c>
       <c r="CD305" s="190" t="n">
-        <v>5.418409064307842</v>
+        <v>5.41840906430784</v>
       </c>
       <c r="CE305" s="190" t="n">
         <v>7.617414578501133</v>
@@ -61202,7 +61202,7 @@
         <v>22.69085726836766</v>
       </c>
       <c r="AX306" s="209" t="n">
-        <v>20.1740269137868</v>
+        <v>20.17402691378681</v>
       </c>
       <c r="AY306" s="210" t="n">
         <v>20.53512992720909</v>
@@ -61252,7 +61252,7 @@
         <v>22.69085726836766</v>
       </c>
       <c r="BO306" s="212" t="n">
-        <v>20.1740269137868</v>
+        <v>20.17402691378681</v>
       </c>
       <c r="BP306" s="213" t="n">
         <v>20.53512992720909</v>
@@ -61278,34 +61278,34 @@
         <v>0</v>
       </c>
       <c r="BX306" s="466" t="n">
-        <v>-0.0002234593929034625</v>
+        <v>-0.0002234593929034609</v>
       </c>
       <c r="BY306" s="467" t="n">
-        <v>-0.0002275819979038565</v>
+        <v>-0.0002275819979038549</v>
       </c>
       <c r="BZ306" s="467" t="n">
-        <v>-0.0002905328177100054</v>
+        <v>-0.0002905328177100033</v>
       </c>
       <c r="CA306" s="467" t="n">
-        <v>-0.0003334198850995084</v>
+        <v>-0.0003334198850995059</v>
       </c>
       <c r="CB306" s="468" t="n">
-        <v>-0.0003341999268680639</v>
+        <v>-0.0003341999268680615</v>
       </c>
       <c r="CC306" s="212" t="n">
-        <v>-0.006236967234433312</v>
+        <v>-0.006236967234433267</v>
       </c>
       <c r="CD306" s="212" t="n">
-        <v>-0.006399056380743316</v>
+        <v>-0.00639905638074327</v>
       </c>
       <c r="CE306" s="212" t="n">
-        <v>-0.006594353461923418</v>
+        <v>-0.006594353461923369</v>
       </c>
       <c r="CF306" s="212" t="n">
-        <v>-0.006728663710832269</v>
+        <v>-0.006728663710832221</v>
       </c>
       <c r="CG306" s="213" t="n">
-        <v>-0.006865131713913014</v>
+        <v>-0.006865131713912964</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" thickBot="1">
@@ -61345,7 +61345,7 @@
         <v>0.2290284821556444</v>
       </c>
       <c r="M307" s="215" t="n">
-        <v>299.8251834757914</v>
+        <v>299.8251834757915</v>
       </c>
       <c r="N307" s="215" t="n">
         <v>258.3767770590746</v>
@@ -61395,7 +61395,7 @@
         <v>0.2290284821556444</v>
       </c>
       <c r="AD307" s="218" t="n">
-        <v>299.8251834757914</v>
+        <v>299.8251834757915</v>
       </c>
       <c r="AE307" s="218" t="n">
         <v>258.3767770590746</v>
@@ -61457,7 +61457,7 @@
         <v>184.731553111154</v>
       </c>
       <c r="AY307" s="208" t="n">
-        <v>184.3683350048556</v>
+        <v>184.3683350048557</v>
       </c>
       <c r="BA307" s="155" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>184.731553111154</v>
       </c>
       <c r="BP307" s="214" t="n">
-        <v>184.3683350048556</v>
+        <v>184.3683350048557</v>
       </c>
       <c r="BR307" s="155" t="inlineStr">
         <is>
@@ -61533,28 +61533,28 @@
         <v>0.1042053931330955</v>
       </c>
       <c r="BY307" s="467" t="n">
-        <v>0.01826537562766165</v>
+        <v>0.01826537562766163</v>
       </c>
       <c r="BZ307" s="467" t="n">
-        <v>0.03532982783652344</v>
+        <v>0.03532982783652343</v>
       </c>
       <c r="CA307" s="467" t="n">
-        <v>0.05408945665275691</v>
+        <v>0.05408945665275687</v>
       </c>
       <c r="CB307" s="468" t="n">
-        <v>0.07761131085169018</v>
+        <v>0.07761131085169017</v>
       </c>
       <c r="CC307" s="212" t="n">
         <v>31.45938192183187</v>
       </c>
       <c r="CD307" s="212" t="n">
-        <v>4.76359579624308</v>
+        <v>4.763595796243075</v>
       </c>
       <c r="CE307" s="212" t="n">
-        <v>6.95376543101484</v>
+        <v>6.953765431014837</v>
       </c>
       <c r="CF307" s="212" t="n">
-        <v>10.0309410258818</v>
+        <v>10.03094102588179</v>
       </c>
       <c r="CG307" s="213" t="n">
         <v>14.36307811110751</v>
@@ -63081,13 +63081,13 @@
         <v>0.1636551195032611</v>
       </c>
       <c r="AQ315" s="490" t="n">
-        <v>0.2003135712119939</v>
+        <v>0.200313571211994</v>
       </c>
       <c r="AR315" s="490" t="n">
         <v>0.3761173699277701</v>
       </c>
       <c r="AS315" s="490" t="n">
-        <v>0.4612888047827939</v>
+        <v>0.4612888047827938</v>
       </c>
       <c r="AT315" s="491" t="n">
         <v>0.4680285721514659</v>
@@ -63096,13 +63096,13 @@
         <v>0.1616551195032611</v>
       </c>
       <c r="AV315" s="490" t="n">
-        <v>0.1973135712119939</v>
+        <v>0.197313571211994</v>
       </c>
       <c r="AW315" s="490" t="n">
         <v>0.3721173699277702</v>
       </c>
       <c r="AX315" s="490" t="n">
-        <v>0.4562888047827939</v>
+        <v>0.4562888047827938</v>
       </c>
       <c r="AY315" s="491" t="n">
         <v>0.4620285721514659</v>
@@ -63131,13 +63131,13 @@
         <v>0.1636551195032611</v>
       </c>
       <c r="BH315" s="467" t="n">
-        <v>0.2003135712119939</v>
+        <v>0.200313571211994</v>
       </c>
       <c r="BI315" s="467" t="n">
         <v>0.3761173699277701</v>
       </c>
       <c r="BJ315" s="467" t="n">
-        <v>0.4612888047827939</v>
+        <v>0.4612888047827938</v>
       </c>
       <c r="BK315" s="468" t="n">
         <v>0.4680285721514659</v>
@@ -63146,13 +63146,13 @@
         <v>0.1616551195032611</v>
       </c>
       <c r="BM315" s="467" t="n">
-        <v>0.1973135712119939</v>
+        <v>0.197313571211994</v>
       </c>
       <c r="BN315" s="467" t="n">
         <v>0.3721173699277702</v>
       </c>
       <c r="BO315" s="467" t="n">
-        <v>0.4562888047827939</v>
+        <v>0.4562888047827938</v>
       </c>
       <c r="BP315" s="468" t="n">
         <v>0.4620285721514659</v>
@@ -63248,7 +63248,7 @@
         <v>0.08911974768298138</v>
       </c>
       <c r="M316" s="495" t="n">
-        <v>0.01762997011581366</v>
+        <v>0.01762997011581365</v>
       </c>
       <c r="N316" s="495" t="n">
         <v>0.02604799752893461</v>
@@ -63298,7 +63298,7 @@
         <v>0.08911974768298138</v>
       </c>
       <c r="AD316" s="498" t="n">
-        <v>0.01762997011581366</v>
+        <v>0.01762997011581365</v>
       </c>
       <c r="AE316" s="498" t="n">
         <v>0.02604799752893461</v>
@@ -63336,7 +63336,7 @@
         <v>0.01777451837112267</v>
       </c>
       <c r="AQ316" s="501" t="n">
-        <v>0.02627560094783768</v>
+        <v>0.02627560094783769</v>
       </c>
       <c r="AR316" s="501" t="n">
         <v>0.06486477924766289</v>
@@ -63386,7 +63386,7 @@
         <v>0.01777451837112267</v>
       </c>
       <c r="BH316" s="504" t="n">
-        <v>0.02627560094783768</v>
+        <v>0.02627560094783769</v>
       </c>
       <c r="BI316" s="504" t="n">
         <v>0.06486477924766289</v>
@@ -63445,7 +63445,7 @@
         <v>0.08365538593373004</v>
       </c>
       <c r="CB316" s="505" t="n">
-        <v>0.08700660266017594</v>
+        <v>0.08700660266017593</v>
       </c>
       <c r="CC316" s="492" t="n">
         <v>0</v>
@@ -64692,7 +64692,7 @@
         </is>
       </c>
       <c r="AK326" s="435" t="n">
-        <v>98753.8328039909</v>
+        <v>98753.83280399092</v>
       </c>
       <c r="AL326" s="408" t="n">
         <v>182926.8615295583</v>
@@ -64727,7 +64727,7 @@
         </is>
       </c>
       <c r="BB326" s="419" t="n">
-        <v>98753.8328039909</v>
+        <v>98753.83280399092</v>
       </c>
       <c r="BC326" s="420" t="n">
         <v>182926.8615295583</v>
@@ -64762,7 +64762,7 @@
         </is>
       </c>
       <c r="BS326" s="419" t="n">
-        <v>97546.97984266911</v>
+        <v>97546.97984266913</v>
       </c>
       <c r="BT326" s="420" t="n">
         <v>180187.2539170122</v>
@@ -64774,7 +64774,7 @@
         <v>411900.329347305</v>
       </c>
       <c r="BW326" s="421" t="n">
-        <v>445550.1184239215</v>
+        <v>445550.1184239214</v>
       </c>
       <c r="BX326" s="416" t="n">
         <v>18128.807941329</v>
@@ -64887,7 +64887,7 @@
         </is>
       </c>
       <c r="AK327" s="435" t="n">
-        <v>98753.8328039909</v>
+        <v>98753.83280399092</v>
       </c>
       <c r="AL327" s="408" t="n">
         <v>182926.8615295583</v>
@@ -64922,7 +64922,7 @@
         </is>
       </c>
       <c r="BB327" s="439" t="n">
-        <v>98753.8328039909</v>
+        <v>98753.83280399092</v>
       </c>
       <c r="BC327" s="440" t="n">
         <v>182926.8615295583</v>
@@ -64957,7 +64957,7 @@
         </is>
       </c>
       <c r="BS327" s="439" t="n">
-        <v>97546.97984266911</v>
+        <v>97546.97984266913</v>
       </c>
       <c r="BT327" s="440" t="n">
         <v>180187.2539170122</v>
@@ -64969,7 +64969,7 @@
         <v>411900.329347305</v>
       </c>
       <c r="BW327" s="441" t="n">
-        <v>445550.1184239215</v>
+        <v>445550.1184239214</v>
       </c>
       <c r="BX327" s="442" t="n">
         <v>18128.807941329</v>
@@ -67590,7 +67590,7 @@
         </is>
       </c>
       <c r="AK344" s="435" t="n">
-        <v>98753.8328039909</v>
+        <v>98753.83280399092</v>
       </c>
       <c r="AL344" s="408" t="n">
         <v>182926.8615295583</v>
@@ -67625,7 +67625,7 @@
         </is>
       </c>
       <c r="BB344" s="419" t="n">
-        <v>98753.8328039909</v>
+        <v>98753.83280399092</v>
       </c>
       <c r="BC344" s="420" t="n">
         <v>182926.8615295583</v>
@@ -67660,7 +67660,7 @@
         </is>
       </c>
       <c r="BS344" s="419" t="n">
-        <v>97546.97984266911</v>
+        <v>97546.97984266913</v>
       </c>
       <c r="BT344" s="420" t="n">
         <v>180187.2539170122</v>
@@ -67672,7 +67672,7 @@
         <v>411900.329347305</v>
       </c>
       <c r="BW344" s="421" t="n">
-        <v>445550.1184239215</v>
+        <v>445550.1184239214</v>
       </c>
       <c r="BX344" s="416" t="n">
         <v>18128.807941329</v>
@@ -67785,7 +67785,7 @@
         </is>
       </c>
       <c r="AK345" s="435" t="n">
-        <v>98753.8328039909</v>
+        <v>98753.83280399092</v>
       </c>
       <c r="AL345" s="408" t="n">
         <v>182926.8615295583</v>
@@ -67820,7 +67820,7 @@
         </is>
       </c>
       <c r="BB345" s="439" t="n">
-        <v>98753.8328039909</v>
+        <v>98753.83280399092</v>
       </c>
       <c r="BC345" s="440" t="n">
         <v>182926.8615295583</v>
@@ -67855,7 +67855,7 @@
         </is>
       </c>
       <c r="BS345" s="439" t="n">
-        <v>97546.97984266911</v>
+        <v>97546.97984266913</v>
       </c>
       <c r="BT345" s="440" t="n">
         <v>180187.2539170122</v>
@@ -67867,7 +67867,7 @@
         <v>411900.329347305</v>
       </c>
       <c r="BW345" s="441" t="n">
-        <v>445550.1184239215</v>
+        <v>445550.1184239214</v>
       </c>
       <c r="BX345" s="442" t="n">
         <v>18128.807941329</v>
@@ -68434,13 +68434,13 @@
         <v>17007.40266602565</v>
       </c>
       <c r="AO350" s="380" t="n">
-        <v>15461.55643869437</v>
+        <v>15461.55643869438</v>
       </c>
       <c r="AP350" s="381" t="n">
         <v>643.7953722573421</v>
       </c>
       <c r="AQ350" s="372" t="n">
-        <v>633.1527952982868</v>
+        <v>633.1527952982867</v>
       </c>
       <c r="AR350" s="372" t="n">
         <v>594.4466704358538</v>
@@ -68449,7 +68449,7 @@
         <v>522.2104923178402</v>
       </c>
       <c r="AT350" s="382" t="n">
-        <v>481.682986242403</v>
+        <v>481.6829862424031</v>
       </c>
       <c r="BA350" s="83" t="inlineStr">
         <is>
@@ -68469,13 +68469,13 @@
         <v>17007.40266602565</v>
       </c>
       <c r="BF350" s="392" t="n">
-        <v>15461.55643869437</v>
+        <v>15461.55643869438</v>
       </c>
       <c r="BG350" s="386" t="n">
         <v>643.7953722573421</v>
       </c>
       <c r="BH350" s="372" t="n">
-        <v>633.1527952982868</v>
+        <v>633.1527952982867</v>
       </c>
       <c r="BI350" s="372" t="n">
         <v>594.4466704358538</v>
@@ -68484,7 +68484,7 @@
         <v>522.2104923178402</v>
       </c>
       <c r="BK350" s="387" t="n">
-        <v>481.682986242403</v>
+        <v>481.6829862424031</v>
       </c>
       <c r="BR350" s="83" t="inlineStr">
         <is>
@@ -68495,7 +68495,7 @@
         <v>61852.87009948627</v>
       </c>
       <c r="BT350" s="375" t="n">
-        <v>47638.89476372442</v>
+        <v>47638.89476372443</v>
       </c>
       <c r="BU350" s="375" t="n">
         <v>23699.5880807438</v>
@@ -68510,7 +68510,7 @@
         <v>644.4639296475568</v>
       </c>
       <c r="BY350" s="372" t="n">
-        <v>634.3956583183151</v>
+        <v>634.395658318315</v>
       </c>
       <c r="BZ350" s="372" t="n">
         <v>598.0921575373826</v>
@@ -68604,13 +68604,13 @@
         <v>108380.2030459262</v>
       </c>
       <c r="AL351" s="368" t="n">
-        <v>78708.23701776557</v>
+        <v>78708.23701776558</v>
       </c>
       <c r="AM351" s="368" t="n">
-        <v>49459.40567574815</v>
+        <v>49459.40567574816</v>
       </c>
       <c r="AN351" s="368" t="n">
-        <v>45316.76404209326</v>
+        <v>45316.76404209325</v>
       </c>
       <c r="AO351" s="380" t="n">
         <v>47037.26825462953</v>
@@ -68619,7 +68619,7 @@
         <v>1763.479052604025</v>
       </c>
       <c r="AQ351" s="372" t="n">
-        <v>1667.558827924327</v>
+        <v>1667.558827924328</v>
       </c>
       <c r="AR351" s="372" t="n">
         <v>1496.400129308203</v>
@@ -68639,13 +68639,13 @@
         <v>108380.2030459262</v>
       </c>
       <c r="BC351" s="375" t="n">
-        <v>78708.23701776557</v>
+        <v>78708.23701776558</v>
       </c>
       <c r="BD351" s="375" t="n">
-        <v>49459.40567574815</v>
+        <v>49459.40567574816</v>
       </c>
       <c r="BE351" s="375" t="n">
-        <v>45316.76404209326</v>
+        <v>45316.76404209325</v>
       </c>
       <c r="BF351" s="392" t="n">
         <v>47037.26825462953</v>
@@ -68654,7 +68654,7 @@
         <v>1763.479052604025</v>
       </c>
       <c r="BH351" s="372" t="n">
-        <v>1667.558827924327</v>
+        <v>1667.558827924328</v>
       </c>
       <c r="BI351" s="372" t="n">
         <v>1496.400129308203</v>
@@ -68671,28 +68671,28 @@
         </is>
       </c>
       <c r="BS351" s="391" t="n">
-        <v>108585.6923770446</v>
+        <v>108585.6923770447</v>
       </c>
       <c r="BT351" s="375" t="n">
-        <v>78890.61125065039</v>
+        <v>78890.6112506504</v>
       </c>
       <c r="BU351" s="375" t="n">
-        <v>49657.28648921575</v>
+        <v>49657.28648921576</v>
       </c>
       <c r="BV351" s="375" t="n">
-        <v>45532.10633539765</v>
+        <v>45532.10633539764</v>
       </c>
       <c r="BW351" s="392" t="n">
-        <v>47236.43957443789</v>
+        <v>47236.4395744379</v>
       </c>
       <c r="BX351" s="386" t="n">
-        <v>1764.033576149875</v>
+        <v>1764.033576149876</v>
       </c>
       <c r="BY351" s="372" t="n">
         <v>1668.563999787914</v>
       </c>
       <c r="BZ351" s="372" t="n">
-        <v>1498.626421398223</v>
+        <v>1498.626421398224</v>
       </c>
       <c r="CA351" s="372" t="n">
         <v>1497.080765601087</v>
@@ -68795,19 +68795,19 @@
         <v>111813.7515740478</v>
       </c>
       <c r="AP352" s="381" t="n">
-        <v>927.1777229284534</v>
+        <v>927.1777229284532</v>
       </c>
       <c r="AQ352" s="372" t="n">
-        <v>944.3613432519763</v>
+        <v>944.3613432519765</v>
       </c>
       <c r="AR352" s="372" t="n">
-        <v>932.633499446154</v>
+        <v>932.6334994461541</v>
       </c>
       <c r="AS352" s="372" t="n">
         <v>1026.946673068109</v>
       </c>
       <c r="AT352" s="382" t="n">
-        <v>1104.86056866744</v>
+        <v>1104.860568667439</v>
       </c>
       <c r="BA352" s="111" t="inlineStr">
         <is>
@@ -68830,19 +68830,19 @@
         <v>111813.7515740478</v>
       </c>
       <c r="BG352" s="386" t="n">
-        <v>927.1777229284534</v>
+        <v>927.1777229284532</v>
       </c>
       <c r="BH352" s="372" t="n">
-        <v>944.3613432519763</v>
+        <v>944.3613432519765</v>
       </c>
       <c r="BI352" s="372" t="n">
-        <v>932.633499446154</v>
+        <v>932.6334994461541</v>
       </c>
       <c r="BJ352" s="372" t="n">
         <v>1026.946673068109</v>
       </c>
       <c r="BK352" s="387" t="n">
-        <v>1104.86056866744</v>
+        <v>1104.860568667439</v>
       </c>
       <c r="BR352" s="111" t="inlineStr">
         <is>
@@ -68865,16 +68865,16 @@
         <v>112035.7360731496</v>
       </c>
       <c r="BX352" s="386" t="n">
-        <v>927.914885600156</v>
+        <v>927.9148856001559</v>
       </c>
       <c r="BY352" s="372" t="n">
-        <v>945.2241020436829</v>
+        <v>945.224102043683</v>
       </c>
       <c r="BZ352" s="372" t="n">
-        <v>933.73154481584</v>
+        <v>933.7315448158402</v>
       </c>
       <c r="CA352" s="372" t="n">
-        <v>1028.228235047076</v>
+        <v>1028.228235047077</v>
       </c>
       <c r="CB352" s="387" t="n">
         <v>1106.234747132765</v>
@@ -68962,10 +68962,10 @@
         <v>639795.8635083811</v>
       </c>
       <c r="AL353" s="408" t="n">
-        <v>651120.244689472</v>
+        <v>651120.2446894721</v>
       </c>
       <c r="AM353" s="408" t="n">
-        <v>556536.3509597492</v>
+        <v>556536.3509597491</v>
       </c>
       <c r="AN353" s="408" t="n">
         <v>513942.9923042685</v>
@@ -68977,13 +68977,13 @@
         <v>22982.69260371909</v>
       </c>
       <c r="AQ353" s="411" t="n">
-        <v>23249.20816901942</v>
+        <v>23249.20816901943</v>
       </c>
       <c r="AR353" s="411" t="n">
         <v>24684.15169165625</v>
       </c>
       <c r="AS353" s="411" t="n">
-        <v>25711.92705604154</v>
+        <v>25711.92705604153</v>
       </c>
       <c r="AT353" s="412" t="n">
         <v>26571.77633515474</v>
@@ -68997,10 +68997,10 @@
         <v>639795.8635083811</v>
       </c>
       <c r="BC353" s="420" t="n">
-        <v>651120.244689472</v>
+        <v>651120.2446894721</v>
       </c>
       <c r="BD353" s="420" t="n">
-        <v>556536.3509597492</v>
+        <v>556536.3509597491</v>
       </c>
       <c r="BE353" s="420" t="n">
         <v>513942.9923042685</v>
@@ -69012,13 +69012,13 @@
         <v>22982.69260371909</v>
       </c>
       <c r="BH353" s="417" t="n">
-        <v>23249.20816901942</v>
+        <v>23249.20816901943</v>
       </c>
       <c r="BI353" s="417" t="n">
         <v>24684.15169165625</v>
       </c>
       <c r="BJ353" s="417" t="n">
-        <v>25711.92705604154</v>
+        <v>25711.92705604153</v>
       </c>
       <c r="BK353" s="418" t="n">
         <v>26571.77633515474</v>
@@ -69032,10 +69032,10 @@
         <v>641442.9563073047</v>
       </c>
       <c r="BT353" s="420" t="n">
-        <v>653579.5666507614</v>
+        <v>653579.5666507615</v>
       </c>
       <c r="BU353" s="420" t="n">
-        <v>560122.591343562</v>
+        <v>560122.5913435619</v>
       </c>
       <c r="BV353" s="420" t="n">
         <v>518732.4222764822</v>
@@ -69083,7 +69083,7 @@
         <v>711031.5138816028</v>
       </c>
       <c r="H354" s="427" t="n">
-        <v>3049.699233174205</v>
+        <v>3049.699233174204</v>
       </c>
       <c r="I354" s="427" t="n">
         <v>3395.734214293858</v>
@@ -69118,7 +69118,7 @@
         <v>711031.5138816028</v>
       </c>
       <c r="Y354" s="432" t="n">
-        <v>3049.699233174205</v>
+        <v>3049.699233174204</v>
       </c>
       <c r="Z354" s="433" t="n">
         <v>3395.734214293858</v>
@@ -69141,10 +69141,10 @@
         <v>917464.158603146</v>
       </c>
       <c r="AL354" s="408" t="n">
-        <v>881119.0390104101</v>
+        <v>881119.0390104103</v>
       </c>
       <c r="AM354" s="408" t="n">
-        <v>723686.7523308534</v>
+        <v>723686.7523308533</v>
       </c>
       <c r="AN354" s="408" t="n">
         <v>680667.3787439772</v>
@@ -69156,7 +69156,7 @@
         <v>3047.832107611343</v>
       </c>
       <c r="AQ354" s="437" t="n">
-        <v>3389.280478004361</v>
+        <v>3389.280478004363</v>
       </c>
       <c r="AR354" s="437" t="n">
         <v>3693.085197699454</v>
@@ -69176,10 +69176,10 @@
         <v>917464.158603146</v>
       </c>
       <c r="BC354" s="440" t="n">
-        <v>881119.0390104101</v>
+        <v>881119.0390104103</v>
       </c>
       <c r="BD354" s="440" t="n">
-        <v>723686.7523308534</v>
+        <v>723686.7523308533</v>
       </c>
       <c r="BE354" s="440" t="n">
         <v>680667.3787439772</v>
@@ -69191,7 +69191,7 @@
         <v>3047.832107611343</v>
       </c>
       <c r="BH354" s="443" t="n">
-        <v>3389.280478004361</v>
+        <v>3389.280478004363</v>
       </c>
       <c r="BI354" s="443" t="n">
         <v>3693.085197699454</v>
@@ -69208,13 +69208,13 @@
         </is>
       </c>
       <c r="BS354" s="439" t="n">
-        <v>919942.6178675144</v>
+        <v>919942.6178675145</v>
       </c>
       <c r="BT354" s="440" t="n">
-        <v>884374.6133421769</v>
+        <v>884374.613342177</v>
       </c>
       <c r="BU354" s="440" t="n">
-        <v>728128.3309562856</v>
+        <v>728128.3309562855</v>
       </c>
       <c r="BV354" s="440" t="n">
         <v>686380.9942284029</v>
@@ -69223,7 +69223,7 @@
         <v>720938.767404718</v>
       </c>
       <c r="BX354" s="442" t="n">
-        <v>3047.198523892403</v>
+        <v>3047.198523892404</v>
       </c>
       <c r="BY354" s="443" t="n">
         <v>3391.017038221982</v>
@@ -69235,7 +69235,7 @@
         <v>3701.145778726151</v>
       </c>
       <c r="CB354" s="444" t="n">
-        <v>3895.613624687549</v>
+        <v>3895.613624687548</v>
       </c>
       <c r="CI354" s="225" t="n"/>
       <c r="CJ354" s="225" t="n"/>
@@ -71125,13 +71125,13 @@
         <v>17007.40266602565</v>
       </c>
       <c r="AO368" s="380" t="n">
-        <v>15461.55643869437</v>
+        <v>15461.55643869438</v>
       </c>
       <c r="AP368" s="381" t="n">
         <v>643.7953722573421</v>
       </c>
       <c r="AQ368" s="372" t="n">
-        <v>633.1527952982868</v>
+        <v>633.1527952982867</v>
       </c>
       <c r="AR368" s="372" t="n">
         <v>594.4466704358538</v>
@@ -71140,7 +71140,7 @@
         <v>522.2104923178402</v>
       </c>
       <c r="AT368" s="382" t="n">
-        <v>481.682986242403</v>
+        <v>481.6829862424031</v>
       </c>
       <c r="BA368" s="83" t="inlineStr">
         <is>
@@ -71160,13 +71160,13 @@
         <v>17007.40266602565</v>
       </c>
       <c r="BF368" s="392" t="n">
-        <v>15461.55643869437</v>
+        <v>15461.55643869438</v>
       </c>
       <c r="BG368" s="386" t="n">
         <v>643.7953722573421</v>
       </c>
       <c r="BH368" s="372" t="n">
-        <v>633.1527952982868</v>
+        <v>633.1527952982867</v>
       </c>
       <c r="BI368" s="372" t="n">
         <v>594.4466704358538</v>
@@ -71175,7 +71175,7 @@
         <v>522.2104923178402</v>
       </c>
       <c r="BK368" s="387" t="n">
-        <v>481.682986242403</v>
+        <v>481.6829862424031</v>
       </c>
       <c r="BR368" s="83" t="inlineStr">
         <is>
@@ -71213,19 +71213,19 @@
         <v>489.9393772435288</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>470.1326516276238</v>
+        <v>470.1326516276255</v>
       </c>
       <c r="CX368" s="512" t="n">
-        <v>447.1539035291422</v>
+        <v>447.1539035291436</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>475.8887590734226</v>
+        <v>475.8887590734239</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>501.0331785734001</v>
+        <v>501.0331785734019</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>529.4650756237152</v>
+        <v>529.4650756237174</v>
       </c>
     </row>
     <row r="369">
@@ -71308,13 +71308,13 @@
         <v>108380.2030459262</v>
       </c>
       <c r="AL369" s="368" t="n">
-        <v>78708.23701776557</v>
+        <v>78708.23701776558</v>
       </c>
       <c r="AM369" s="368" t="n">
-        <v>49459.40567574815</v>
+        <v>49459.40567574816</v>
       </c>
       <c r="AN369" s="368" t="n">
-        <v>45316.76404209326</v>
+        <v>45316.76404209325</v>
       </c>
       <c r="AO369" s="380" t="n">
         <v>47037.26825462953</v>
@@ -71323,7 +71323,7 @@
         <v>1763.479052604025</v>
       </c>
       <c r="AQ369" s="372" t="n">
-        <v>1667.558827924327</v>
+        <v>1667.558827924328</v>
       </c>
       <c r="AR369" s="372" t="n">
         <v>1496.400129308203</v>
@@ -71343,13 +71343,13 @@
         <v>108380.2030459262</v>
       </c>
       <c r="BC369" s="375" t="n">
-        <v>78708.23701776557</v>
+        <v>78708.23701776558</v>
       </c>
       <c r="BD369" s="375" t="n">
-        <v>49459.40567574815</v>
+        <v>49459.40567574816</v>
       </c>
       <c r="BE369" s="375" t="n">
-        <v>45316.76404209326</v>
+        <v>45316.76404209325</v>
       </c>
       <c r="BF369" s="392" t="n">
         <v>47037.26825462953</v>
@@ -71358,7 +71358,7 @@
         <v>1763.479052604025</v>
       </c>
       <c r="BH369" s="372" t="n">
-        <v>1667.558827924327</v>
+        <v>1667.558827924328</v>
       </c>
       <c r="BI369" s="372" t="n">
         <v>1496.400129308203</v>
@@ -71375,13 +71375,13 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>108585.6923770446</v>
+        <v>108585.6923770447</v>
       </c>
       <c r="BT369" s="375" t="n">
-        <v>78890.61125065039</v>
+        <v>78890.6112506504</v>
       </c>
       <c r="BU369" s="375" t="n">
-        <v>49657.28648921575</v>
+        <v>49657.28648921576</v>
       </c>
       <c r="BV369" s="375" t="n">
         <v>45532.10633539764</v>
@@ -71390,13 +71390,13 @@
         <v>47236.43957443789</v>
       </c>
       <c r="BX369" s="386" t="n">
-        <v>1764.033576149875</v>
+        <v>1764.033576149876</v>
       </c>
       <c r="BY369" s="372" t="n">
         <v>1668.563999787914</v>
       </c>
       <c r="BZ369" s="372" t="n">
-        <v>1498.626421398223</v>
+        <v>1498.626421398224</v>
       </c>
       <c r="CA369" s="372" t="n">
         <v>1497.080765601087</v>
@@ -71405,19 +71405,19 @@
         <v>1543.329831986514</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>205.4893311184614</v>
+        <v>205.4893311184623</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>182.3742328848221</v>
+        <v>182.3742328848228</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>197.8808134675972</v>
+        <v>197.8808134675982</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>215.3422933043808</v>
+        <v>215.3422933043818</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>199.1713198083628</v>
+        <v>199.171319808364</v>
       </c>
     </row>
     <row r="370">
@@ -71512,19 +71512,19 @@
         <v>111813.7515740478</v>
       </c>
       <c r="AP370" s="381" t="n">
-        <v>927.1777229284534</v>
+        <v>927.1777229284532</v>
       </c>
       <c r="AQ370" s="372" t="n">
-        <v>944.3613432519763</v>
+        <v>944.3613432519765</v>
       </c>
       <c r="AR370" s="372" t="n">
-        <v>932.633499446154</v>
+        <v>932.6334994461541</v>
       </c>
       <c r="AS370" s="372" t="n">
         <v>1026.946673068109</v>
       </c>
       <c r="AT370" s="382" t="n">
-        <v>1104.86056866744</v>
+        <v>1104.860568667439</v>
       </c>
       <c r="BA370" s="111" t="inlineStr">
         <is>
@@ -71547,19 +71547,19 @@
         <v>111813.7515740478</v>
       </c>
       <c r="BG370" s="386" t="n">
-        <v>927.1777229284534</v>
+        <v>927.1777229284532</v>
       </c>
       <c r="BH370" s="372" t="n">
-        <v>944.3613432519763</v>
+        <v>944.3613432519765</v>
       </c>
       <c r="BI370" s="372" t="n">
-        <v>932.633499446154</v>
+        <v>932.6334994461541</v>
       </c>
       <c r="BJ370" s="372" t="n">
         <v>1026.946673068109</v>
       </c>
       <c r="BK370" s="387" t="n">
-        <v>1104.86056866744</v>
+        <v>1104.860568667439</v>
       </c>
       <c r="BR370" s="111" t="inlineStr">
         <is>
@@ -71582,34 +71582,34 @@
         <v>112035.7360731496</v>
       </c>
       <c r="BX370" s="386" t="n">
-        <v>927.914885600156</v>
+        <v>927.9148856001559</v>
       </c>
       <c r="BY370" s="372" t="n">
-        <v>945.2241020436829</v>
+        <v>945.224102043683</v>
       </c>
       <c r="BZ370" s="372" t="n">
-        <v>933.73154481584</v>
+        <v>933.7315448158402</v>
       </c>
       <c r="CA370" s="372" t="n">
-        <v>1028.228235047076</v>
+        <v>1028.228235047077</v>
       </c>
       <c r="CB370" s="387" t="n">
         <v>1106.234747132765</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>155.7444826987019</v>
+        <v>155.7444826987056</v>
       </c>
       <c r="CX370" s="375" t="n">
-        <v>166.7242340633324</v>
+        <v>166.7242340633369</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>181.5686690783152</v>
+        <v>181.5686690783207</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>207.8100403343033</v>
+        <v>207.8100403343101</v>
       </c>
       <c r="DA370" s="392" t="n">
-        <v>221.9844991017722</v>
+        <v>221.9844991017795</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" thickBot="1">
@@ -71692,10 +71692,10 @@
         <v>639795.8635083811</v>
       </c>
       <c r="AL371" s="408" t="n">
-        <v>651120.244689472</v>
+        <v>651120.2446894721</v>
       </c>
       <c r="AM371" s="408" t="n">
-        <v>556536.3509597492</v>
+        <v>556536.3509597491</v>
       </c>
       <c r="AN371" s="408" t="n">
         <v>513942.9923042685</v>
@@ -71707,13 +71707,13 @@
         <v>22982.69260371909</v>
       </c>
       <c r="AQ371" s="411" t="n">
-        <v>23249.20816901942</v>
+        <v>23249.20816901943</v>
       </c>
       <c r="AR371" s="411" t="n">
         <v>24684.15169165625</v>
       </c>
       <c r="AS371" s="411" t="n">
-        <v>25711.92705604154</v>
+        <v>25711.92705604153</v>
       </c>
       <c r="AT371" s="412" t="n">
         <v>26571.77633515474</v>
@@ -71727,10 +71727,10 @@
         <v>639795.8635083811</v>
       </c>
       <c r="BC371" s="420" t="n">
-        <v>651120.244689472</v>
+        <v>651120.2446894721</v>
       </c>
       <c r="BD371" s="420" t="n">
-        <v>556536.3509597492</v>
+        <v>556536.3509597491</v>
       </c>
       <c r="BE371" s="420" t="n">
         <v>513942.9923042685</v>
@@ -71742,13 +71742,13 @@
         <v>22982.69260371909</v>
       </c>
       <c r="BH371" s="417" t="n">
-        <v>23249.20816901942</v>
+        <v>23249.20816901943</v>
       </c>
       <c r="BI371" s="417" t="n">
         <v>24684.15169165625</v>
       </c>
       <c r="BJ371" s="417" t="n">
-        <v>25711.92705604154</v>
+        <v>25711.92705604153</v>
       </c>
       <c r="BK371" s="418" t="n">
         <v>26571.77633515474</v>
@@ -71762,10 +71762,10 @@
         <v>641442.9563073047</v>
       </c>
       <c r="BT371" s="420" t="n">
-        <v>653579.5666507614</v>
+        <v>653579.5666507615</v>
       </c>
       <c r="BU371" s="420" t="n">
-        <v>560122.591343562</v>
+        <v>560122.5913435619</v>
       </c>
       <c r="BV371" s="420" t="n">
         <v>518732.4222764822</v>
@@ -71789,19 +71789,19 @@
         <v>26563.90922540538</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>117.1118582179325</v>
+        <v>117.1118582179315</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>16.66360952908236</v>
+        <v>16.66360952908222</v>
       </c>
       <c r="CY371" s="420" t="n">
-        <v>18.02851745380385</v>
+        <v>18.02851745380405</v>
       </c>
       <c r="CZ371" s="420" t="n">
-        <v>19.31384257715607</v>
+        <v>19.31384257715563</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>20.69080366985162</v>
+        <v>20.69080366985143</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71826,7 +71826,7 @@
         <v>711031.5138816028</v>
       </c>
       <c r="H372" s="427" t="n">
-        <v>3049.699233174205</v>
+        <v>3049.699233174204</v>
       </c>
       <c r="I372" s="427" t="n">
         <v>3395.734214293858</v>
@@ -71861,7 +71861,7 @@
         <v>711031.5138816028</v>
       </c>
       <c r="Y372" s="432" t="n">
-        <v>3049.699233174205</v>
+        <v>3049.699233174204</v>
       </c>
       <c r="Z372" s="433" t="n">
         <v>3395.734214293858</v>
@@ -71884,10 +71884,10 @@
         <v>917464.158603146</v>
       </c>
       <c r="AL372" s="408" t="n">
-        <v>881119.0390104101</v>
+        <v>881119.0390104103</v>
       </c>
       <c r="AM372" s="408" t="n">
-        <v>723686.7523308534</v>
+        <v>723686.7523308533</v>
       </c>
       <c r="AN372" s="408" t="n">
         <v>680667.3787439772</v>
@@ -71899,7 +71899,7 @@
         <v>3047.832107611343</v>
       </c>
       <c r="AQ372" s="437" t="n">
-        <v>3389.280478004361</v>
+        <v>3389.280478004363</v>
       </c>
       <c r="AR372" s="437" t="n">
         <v>3693.085197699454</v>
@@ -71919,10 +71919,10 @@
         <v>917464.158603146</v>
       </c>
       <c r="BC372" s="440" t="n">
-        <v>881119.0390104101</v>
+        <v>881119.0390104103</v>
       </c>
       <c r="BD372" s="440" t="n">
-        <v>723686.7523308534</v>
+        <v>723686.7523308533</v>
       </c>
       <c r="BE372" s="440" t="n">
         <v>680667.3787439772</v>
@@ -71934,7 +71934,7 @@
         <v>3047.832107611343</v>
       </c>
       <c r="BH372" s="443" t="n">
-        <v>3389.280478004361</v>
+        <v>3389.280478004363</v>
       </c>
       <c r="BI372" s="443" t="n">
         <v>3693.085197699454</v>
@@ -71951,13 +71951,13 @@
         </is>
       </c>
       <c r="BS372" s="439" t="n">
-        <v>919942.6178675144</v>
+        <v>919942.6178675145</v>
       </c>
       <c r="BT372" s="440" t="n">
-        <v>884374.6133421769</v>
+        <v>884374.613342177</v>
       </c>
       <c r="BU372" s="440" t="n">
-        <v>728128.3309562856</v>
+        <v>728128.3309562855</v>
       </c>
       <c r="BV372" s="440" t="n">
         <v>686380.9942284029</v>
@@ -71966,10 +71966,10 @@
         <v>720938.7674047179</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>3047.198523892403</v>
+        <v>3047.198523892404</v>
       </c>
       <c r="BY372" s="443" t="n">
-        <v>3391.017038221982</v>
+        <v>3391.017038221983</v>
       </c>
       <c r="BZ372" s="443" t="n">
         <v>3699.384000047647</v>
@@ -71981,19 +71981,19 @@
         <v>3895.613624687548</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>948.4783236627197</v>
+        <v>948.4783236627248</v>
       </c>
       <c r="CX372" s="420" t="n">
-        <v>812.9159800063791</v>
+        <v>812.9159800063856</v>
       </c>
       <c r="CY372" s="420" t="n">
-        <v>873.3667590731388</v>
+        <v>873.3667590731468</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>943.4993547892402</v>
+        <v>943.4993547892494</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>971.3116982037018</v>
+        <v>971.3116982037124</v>
       </c>
     </row>
     <row r="375">
